--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iborras\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D9CD9F-F628-41D4-9E4A-B99D9C340210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90AC404-438D-45EE-BBB3-63BB08F6F95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pendientes" sheetId="4" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="166">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -339,9 +339,6 @@
     <t>8.9</t>
   </si>
   <si>
-    <t>Misterio</t>
-  </si>
-  <si>
     <t>8.3</t>
   </si>
   <si>
@@ -367,6 +364,174 @@
   </si>
   <si>
     <t>https://www.abduction.es/badalona/abduction4.html</t>
+  </si>
+  <si>
+    <t>WHITECHAPEL</t>
+  </si>
+  <si>
+    <t>Catacumbas</t>
+  </si>
+  <si>
+    <t>Exorcista</t>
+  </si>
+  <si>
+    <t>Jaipur</t>
+  </si>
+  <si>
+    <t>encryptroom</t>
+  </si>
+  <si>
+    <t>Room Whitechapel</t>
+  </si>
+  <si>
+    <t>Jack el Destripador</t>
+  </si>
+  <si>
+    <t>Terror / Inmersivo</t>
+  </si>
+  <si>
+    <t>roomwhitechapel.com</t>
+  </si>
+  <si>
+    <t>Alquimia / Aventuras</t>
+  </si>
+  <si>
+    <t>goldenpop.es/catacumbas/</t>
+  </si>
+  <si>
+    <t>Terror Stories</t>
+  </si>
+  <si>
+    <t>Exorcismo / Posesión</t>
+  </si>
+  <si>
+    <t>Terror</t>
+  </si>
+  <si>
+    <t>terrorstories.com</t>
+  </si>
+  <si>
+    <t>Kadabra</t>
+  </si>
+  <si>
+    <t>Mataró</t>
+  </si>
+  <si>
+    <t>Bollywood / India</t>
+  </si>
+  <si>
+    <t>kadabraescape.com</t>
+  </si>
+  <si>
+    <t>Encrypt</t>
+  </si>
+  <si>
+    <t>Asesino en serie</t>
+  </si>
+  <si>
+    <t>Tensión / Inmersivo</t>
+  </si>
+  <si>
+    <t>encryptroom.com</t>
+  </si>
+  <si>
+    <t>Bank of Thaqar</t>
+  </si>
+  <si>
+    <t>MissionLeak</t>
+  </si>
+  <si>
+    <t>Atraco / Acción</t>
+  </si>
+  <si>
+    <t>Acción</t>
+  </si>
+  <si>
+    <t>missionleak.com</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>Intracorpus</t>
+  </si>
+  <si>
+    <t>Vortexescape</t>
+  </si>
+  <si>
+    <t>Terrassa</t>
+  </si>
+  <si>
+    <t>Tomb Hunter</t>
+  </si>
+  <si>
+    <t>Arqueología</t>
+  </si>
+  <si>
+    <t>Aventura / Agilidad</t>
+  </si>
+  <si>
+    <t>Alien: El Origen</t>
+  </si>
+  <si>
+    <t>Alien / Espacio</t>
+  </si>
+  <si>
+    <t>Sci-Fi / Acción</t>
+  </si>
+  <si>
+    <t>9.5</t>
+  </si>
+  <si>
+    <t>Criogenic 500</t>
+  </si>
+  <si>
+    <t>Criogenic</t>
+  </si>
+  <si>
+    <t>Futuro / Criogenia</t>
+  </si>
+  <si>
+    <t>Sci-Fi</t>
+  </si>
+  <si>
+    <t>9.6</t>
+  </si>
+  <si>
+    <t>https://www.escapebarcelona.com/tomb-hunter-la-leyenda-de-akasha.php</t>
+  </si>
+  <si>
+    <t>https://www.escapebarcelona.com/alien-el-origen.php</t>
+  </si>
+  <si>
+    <t>https://criogenicescaperoom.com/barcelona</t>
+  </si>
+  <si>
+    <t>Viaje al cuerpo humano</t>
+  </si>
+  <si>
+    <t>Sci-Fi / Inmersivo</t>
+  </si>
+  <si>
+    <t>vortexescape.com</t>
+  </si>
+  <si>
+    <t>Abduction</t>
+  </si>
+  <si>
+    <t>L'Hospitalet de Llobregat</t>
+  </si>
+  <si>
+    <t>Vilanova i la Geltrú</t>
+  </si>
+  <si>
+    <t>Santa Coloma de Gramenet</t>
+  </si>
+  <si>
+    <t>Maximum Escape</t>
   </si>
 </sst>
 </file>
@@ -732,11 +897,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89A95D8-33A2-48B9-A166-E285F092AAAF}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -809,7 +975,7 @@
         <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>164</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
@@ -867,7 +1033,7 @@
         <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>162</v>
       </c>
       <c r="D5" t="s">
         <v>44</v>
@@ -882,7 +1048,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -972,7 +1138,7 @@
         <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -983,7 +1149,7 @@
         <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>163</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1027,10 +1193,10 @@
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" t="s">
         <v>103</v>
-      </c>
-      <c r="I10" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -1067,7 +1233,7 @@
         <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -1125,7 +1291,7 @@
         <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -1180,77 +1346,167 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
       <c r="F16">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="I16" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>159</v>
       </c>
       <c r="F17">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18" t="s">
+        <v>145</v>
+      </c>
+      <c r="F18">
+        <v>90</v>
+      </c>
+      <c r="G18" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I17" t="s">
-        <v>109</v>
+      <c r="H18">
+        <v>10</v>
+      </c>
+      <c r="I18" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" t="s">
+        <v>164</v>
+      </c>
+      <c r="D19" t="s">
+        <v>147</v>
+      </c>
+      <c r="E19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F19">
+        <v>90</v>
+      </c>
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I19" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>152</v>
+      </c>
+      <c r="E20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F20">
+        <v>120</v>
+      </c>
+      <c r="G20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I17" r:id="rId1" display="https://vortexescape.com/intracorpus" xr:uid="{4D425B74-4A8C-40D8-9B1E-C35D3D7DA1EE}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
@@ -1315,18 +1571,11 @@
       <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>8</v>
+      <c r="H2" s="2">
+        <v>9</v>
       </c>
       <c r="I2" t="s">
         <v>22</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
-      </c>
-      <c r="K2">
-        <f>_xlfn.RANK.EQ(J2,$J$2:$J$200,0)</f>
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1351,18 +1600,11 @@
       <c r="G3" t="s">
         <v>21</v>
       </c>
-      <c r="H3">
-        <v>7</v>
+      <c r="H3" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="I3" t="s">
         <v>24</v>
-      </c>
-      <c r="J3">
-        <v>7</v>
-      </c>
-      <c r="K3">
-        <f t="shared" ref="K3:K37" si="0">_xlfn.RANK.EQ(J3,$J$2:$J$200,0)</f>
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1387,18 +1629,11 @@
       <c r="G4" t="s">
         <v>37</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>9</v>
       </c>
       <c r="I4" t="s">
         <v>26</v>
-      </c>
-      <c r="J4">
-        <v>8</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1423,213 +1658,196 @@
       <c r="G5" t="s">
         <v>21</v>
       </c>
-      <c r="H5">
-        <v>7</v>
+      <c r="H5" s="2">
+        <v>8</v>
       </c>
       <c r="I5" t="s">
         <v>28</v>
       </c>
-      <c r="J5">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6">
+        <v>90</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2">
+        <v>9</v>
+      </c>
+      <c r="I6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" t="s">
         <v>8</v>
       </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K6" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K7" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
+      <c r="F7">
+        <v>90</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K8" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
+      <c r="A8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8">
+        <v>90</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I8" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K9" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
+      <c r="A9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>80</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K10" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
+      <c r="A10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" t="s">
+        <v>131</v>
+      </c>
+      <c r="F10">
+        <v>70</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I10" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K11" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K12" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K13" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K14" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K15" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="K16" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K17" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="18" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K18" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="19" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K19" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="20" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K20" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="21" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K21" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="22" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K22" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="23" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K23" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="24" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K24" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="25" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K25" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="26" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K26" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="27" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K27" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="28" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K28" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="29" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K29" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="30" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K30" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="31" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K31" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="32" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K32" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="33" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K33" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="34" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K34" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="35" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K35" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="36" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K36" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
-      </c>
-    </row>
-    <row r="37" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K37" t="e">
-        <f t="shared" si="0"/>
-        <v>#N/A</v>
+      <c r="A11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B11" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>135</v>
+      </c>
+      <c r="E11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11">
+        <v>60</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I11" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I6" r:id="rId1" display="https://roomwhitechapel.com/" xr:uid="{517CBA65-B4F3-4CA9-9CF7-155319F783C8}"/>
+    <hyperlink ref="I7" r:id="rId2" display="https://goldenpop.es/catacumbas/" xr:uid="{371F8B04-8FE5-4C05-B6C0-4EE0EB24D86D}"/>
+    <hyperlink ref="I8" r:id="rId3" display="https://terrorstories.com/barcelona" xr:uid="{C70304D7-A2A3-4447-B6B2-3C9B802F3F37}"/>
+    <hyperlink ref="I9" r:id="rId4" display="https://www.kadabraescape.com/el-secreto-de-jaipur/" xr:uid="{D08C77D6-9864-4AFA-B329-3A7FFA00E250}"/>
+    <hyperlink ref="I10" r:id="rId5" display="https://www.encryptroom.com/" xr:uid="{DB693932-D951-43FF-B2B5-FFA8321AA67C}"/>
+    <hyperlink ref="I11" r:id="rId6" display="https://www.missionleak.com/bankofthaqar" xr:uid="{CDF3D7AB-4CAD-401C-B645-5F3309B27FA4}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iborras\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90AC404-438D-45EE-BBB3-63BB08F6F95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FD76C2-F350-4361-BB4D-C6763733266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pendientes" sheetId="4" r:id="rId1"/>
-    <sheet name="Hechos" sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja2" sheetId="6" r:id="rId2"/>
+    <sheet name="Hechos" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="187">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -532,13 +533,116 @@
   </si>
   <si>
     <t>Maximum Escape</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Descripción Breve</t>
+  </si>
+  <si>
+    <t>Una aventura pirata de película donde te sumerges en la búsqueda del tesoro de uno de los piratas más famosos. Destaca por su escenografía espectacular que recuerda a atracciones temáticas de grandes parques.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Experiencia de estilo Cyberpunk inspirada en clásicos como </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Blade Runner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> o </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Matrix</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>. Te traslada a un mundo decadente y futurista donde la toma de decisiones y la inmersión son los pilares centrales.</t>
+    </r>
+  </si>
+  <si>
+    <t>Una odisea de ciencia ficción post-apocalíptica en la que la humanidad debe abandonar la Tierra tras un virus global. Es muy valorada por su narrativa, el papel del Game Master y su ambientación "calma-tensa".</t>
+  </si>
+  <si>
+    <t>Ambientada en la centenaria Mina de St. Louis, donde los jugadores deben investigar una extraña fuente de minerales tras una explosión. Es una sala clásica de aventura con una ambientación minera muy lograda.</t>
+  </si>
+  <si>
+    <t>Un thriller de supervivencia en un mundo al borde del colapso total. Con una atmósfera de cine y estética post-apocalíptica, los jugadores deben cumplir una misión crítica en un entorno hostil y caótico.</t>
+  </si>
+  <si>
+    <t>Un misterio trepidante de 80 minutos donde el trabajo en equipo es vital. Los jugadores deben resolver enigmas y acertijos para completar una misión de la que solo podrán salir "gritando su nombre tres veces".</t>
+  </si>
+  <si>
+    <t>Una aventura tecnológica ambientada en una nave espacial. Destaca por requerir agilidad física y por integrar tecnología avanzada en sus puzzles, alejándose de los candados tradicionales para ofrecer una experiencia de adrenalina.</t>
+  </si>
+  <si>
+    <t>Experiencia de estética Steampunk inspirada en las novelas de Julio Verne. Los jugadores deben explorar un submarino fantástico, resolviendo acertijos que combinan la mecánica clásica con una narrativa inmersiva.</t>
+  </si>
+  <si>
+    <t>Una aventura de fantasía medieval y épica donde los jugadores deben ascender por una montaña remota. Es conocida por sus retos de alta calidad y una ambientación que transporta totalmente a un mundo de leyendas.</t>
+  </si>
+  <si>
+    <t>Una experiencia inmersiva que mezcla fantasía y magia. Los jugadores se convierten en protagonistas de una "película" donde el ingenio es la clave para superar pruebas diseñadas para fomentar la adrenalina y el trabajo en equipo.</t>
+  </si>
+  <si>
+    <t>Un test de acción y aventura que pone a prueba tanto la mente como la agilidad física (subir escaleras, trepar). Es un juego dinámico y divertido, diseñado para que los adultos vuelvan a sentirse como niños.</t>
+  </si>
+  <si>
+    <t>Una expedición de exploración inmersiva dividida en varias etapas. Ofrece la particularidad de vivir "3 experiencias en 1", donde la historia evoluciona conforme los jugadores se adentran en las profundidades de la cueva.</t>
+  </si>
+  <si>
+    <t>En esta misión de investigación, los jugadores son reclutados como agentes para resolver una serie de acertijos en el Londres victoriano y devolver la seguridad a la ciudad antes de que fuerzas oscuras ataquen.</t>
+  </si>
+  <si>
+    <t>Un juego de aventura clásica ideal para familias y grupos grandes. Los jugadores deben actuar bajo la presión del tiempo para encontrar un antiguo botín escondido antes de que otros bucaneros les pisen los talones.</t>
+  </si>
+  <si>
+    <t>Un "hall escape" diseñado para grupos grandes donde el objetivo es descifrar los enigmas de una civilización sumergida. A diferencia de las salas estándar, el foco está en los puzzles y la comunicación del equipo.</t>
+  </si>
+  <si>
+    <t>Una aventura inmersiva única de 120 minutos (2 horas) donde los jugadores realizan un viaje al interior del cuerpo humano. Es extremadamente tecnológica, de gran formato y requiere calzado cómodo para moverse.</t>
+  </si>
+  <si>
+    <t>Aventura de arqueología pura al estilo Indiana Jones. Con efectos especiales que hacen "vibrar el suelo" y una escenografía de templo antiguo, combina puzzles lógicos con pruebas físicas de agilidad y tensión.</t>
+  </si>
+  <si>
+    <t>Un thriller de ciencia ficción ambientado en la nave USCSS Escape. Tras despertar de un coma inducido, los jugadores deben sobrevivir a una amenaza espacial en una sala que destaca por su opresiva y espectacular ambientación.</t>
+  </si>
+  <si>
+    <t>Experiencia de larga duración (2 horas) en la que los jugadores despiertan 500 años en el futuro tras ser criogenizados. Ofrece más de 140 metros cuadrados de ciencia ficción con instalaciones galardonadas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -551,6 +655,26 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -560,7 +684,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -583,17 +707,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -897,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E89A95D8-33A2-48B9-A166-E285F092AAAF}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -906,10 +1051,11 @@
     <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="46.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="70" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="255.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -937,8 +1083,11 @@
       <c r="I1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -966,8 +1115,11 @@
       <c r="I2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -995,8 +1147,11 @@
       <c r="I3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1024,8 +1179,11 @@
       <c r="I4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>42</v>
       </c>
@@ -1053,8 +1211,11 @@
       <c r="I5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1082,8 +1243,11 @@
       <c r="I6" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1111,8 +1275,11 @@
       <c r="I7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>49</v>
       </c>
@@ -1140,8 +1307,11 @@
       <c r="I8" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>54</v>
       </c>
@@ -1169,8 +1339,11 @@
       <c r="I9" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -1198,8 +1371,11 @@
       <c r="I10" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>70</v>
       </c>
@@ -1227,8 +1403,11 @@
       <c r="I11" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -1256,8 +1435,11 @@
       <c r="I12" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>72</v>
       </c>
@@ -1285,8 +1467,11 @@
       <c r="I13" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -1314,8 +1499,11 @@
       <c r="I14" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -1343,8 +1531,11 @@
       <c r="I15" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>104</v>
       </c>
@@ -1372,8 +1563,11 @@
       <c r="I16" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>140</v>
       </c>
@@ -1401,8 +1595,11 @@
       <c r="I17" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>143</v>
       </c>
@@ -1425,13 +1622,16 @@
         <v>21</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I18" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>146</v>
       </c>
@@ -1459,8 +1659,11 @@
       <c r="I19" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>150</v>
       </c>
@@ -1487,6 +1690,9 @@
       </c>
       <c r="I20" t="s">
         <v>157</v>
+      </c>
+      <c r="J20" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -1498,6 +1704,119 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A119E29-BAF7-45C0-BF8A-A94827405548}">
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="176.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iborras\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FD76C2-F350-4361-BB4D-C6763733266F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25756328-9DC9-4C49-B69F-88DFB20D8E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="185">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -280,9 +280,6 @@
     <t>Misterio / tensión</t>
   </si>
   <si>
-    <t>9.2</t>
-  </si>
-  <si>
     <t>https://enigmaroom.es/the-exam/</t>
   </si>
   <si>
@@ -484,9 +481,6 @@
     <t>Sci-Fi / Acción</t>
   </si>
   <si>
-    <t>9.5</t>
-  </si>
-  <si>
     <t>Criogenic 500</t>
   </si>
   <si>
@@ -499,9 +493,6 @@
     <t>Sci-Fi</t>
   </si>
   <si>
-    <t>9.6</t>
-  </si>
-  <si>
     <t>https://www.escapebarcelona.com/tomb-hunter-la-leyenda-de-akasha.php</t>
   </si>
   <si>
@@ -533,9 +524,6 @@
   </si>
   <si>
     <t>Maximum Escape</t>
-  </si>
-  <si>
-    <t>Descripcion</t>
   </si>
   <si>
     <t>Descripción Breve</t>
@@ -636,6 +624,12 @@
   </si>
   <si>
     <t>Experiencia de larga duración (2 horas) en la que los jugadores despiertan 500 años en el futuro tras ser criogenizados. Ofrece más de 140 metros cuadrados de ciencia ficción con instalaciones galardonadas.</t>
+  </si>
+  <si>
+    <t>8.6</t>
+  </si>
+  <si>
+    <t>Descripción</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1078,7 @@
         <v>30</v>
       </c>
       <c r="J1" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1110,13 +1104,13 @@
         <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I2" t="s">
         <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1127,7 +1121,7 @@
         <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
         <v>35</v>
@@ -1142,13 +1136,13 @@
         <v>37</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I3" t="s">
         <v>38</v>
       </c>
       <c r="J3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1173,14 +1167,14 @@
       <c r="G4" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="2">
-        <v>8</v>
+      <c r="H4" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="I4" t="s">
         <v>14</v>
       </c>
       <c r="J4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1191,7 +1185,7 @@
         <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D5" t="s">
         <v>44</v>
@@ -1206,13 +1200,13 @@
         <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1238,13 +1232,13 @@
         <v>37</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J6" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1276,7 +1270,7 @@
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1302,13 +1296,13 @@
         <v>53</v>
       </c>
       <c r="H8" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J8" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1319,7 +1313,7 @@
         <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>
@@ -1334,13 +1328,13 @@
         <v>37</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="I9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1366,13 +1360,13 @@
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10" t="s">
         <v>102</v>
       </c>
-      <c r="I10" t="s">
-        <v>103</v>
-      </c>
       <c r="J10" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1404,7 +1398,7 @@
         <v>78</v>
       </c>
       <c r="J11" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1412,7 +1406,7 @@
         <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -1430,13 +1424,13 @@
         <v>53</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I12" t="s">
         <v>81</v>
       </c>
-      <c r="I12" t="s">
-        <v>82</v>
-      </c>
       <c r="J12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1444,13 +1438,13 @@
         <v>72</v>
       </c>
       <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="s">
         <v>83</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
       </c>
       <c r="E13" t="s">
         <v>33</v>
@@ -1462,13 +1456,13 @@
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I13" t="s">
         <v>86</v>
       </c>
-      <c r="I13" t="s">
-        <v>87</v>
-      </c>
       <c r="J13" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1476,16 +1470,16 @@
         <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" t="s">
         <v>88</v>
-      </c>
-      <c r="E14" t="s">
-        <v>89</v>
       </c>
       <c r="F14">
         <v>60</v>
@@ -1494,13 +1488,13 @@
         <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" t="s">
         <v>90</v>
       </c>
-      <c r="I14" t="s">
-        <v>91</v>
-      </c>
       <c r="J14" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1508,13 +1502,13 @@
         <v>74</v>
       </c>
       <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
         <v>92</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>94</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1526,27 +1520,27 @@
         <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15" t="s">
         <v>95</v>
       </c>
-      <c r="I15" t="s">
-        <v>96</v>
-      </c>
       <c r="J15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" t="s">
         <v>104</v>
-      </c>
-      <c r="B16" t="s">
-        <v>105</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1558,30 +1552,30 @@
         <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I16" t="s">
         <v>107</v>
       </c>
-      <c r="I16" t="s">
-        <v>108</v>
-      </c>
       <c r="J16" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>139</v>
+      </c>
+      <c r="B17" t="s">
         <v>140</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>141</v>
       </c>
-      <c r="C17" t="s">
-        <v>142</v>
-      </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F17">
         <v>80</v>
@@ -1590,18 +1584,18 @@
         <v>37</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I17" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="J17" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B18" t="s">
         <v>34</v>
@@ -1610,10 +1604,10 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" t="s">
         <v>144</v>
-      </c>
-      <c r="E18" t="s">
-        <v>145</v>
       </c>
       <c r="F18">
         <v>90</v>
@@ -1625,27 +1619,27 @@
         <v>7</v>
       </c>
       <c r="I18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J18" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s">
         <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D19" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" t="s">
         <v>147</v>
-      </c>
-      <c r="E19" t="s">
-        <v>148</v>
       </c>
       <c r="F19">
         <v>90</v>
@@ -1654,30 +1648,30 @@
         <v>21</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="I19" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J19" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
       </c>
       <c r="D20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F20">
         <v>120</v>
@@ -1686,13 +1680,13 @@
         <v>53</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I20" t="s">
         <v>154</v>
       </c>
-      <c r="I20" t="s">
-        <v>157</v>
-      </c>
       <c r="J20" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -1713,102 +1707,102 @@
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -1920,7 +1914,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I3" t="s">
         <v>24</v>
@@ -1986,19 +1980,19 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E6" t="s">
         <v>116</v>
-      </c>
-      <c r="E6" t="s">
-        <v>117</v>
       </c>
       <c r="F6">
         <v>90</v>
@@ -2010,12 +2004,12 @@
         <v>9</v>
       </c>
       <c r="I6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B7" t="s">
         <v>63</v>
@@ -2024,7 +2018,7 @@
         <v>13</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -2036,27 +2030,27 @@
         <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" t="s">
         <v>122</v>
-      </c>
-      <c r="E8" t="s">
-        <v>123</v>
       </c>
       <c r="F8">
         <v>90</v>
@@ -2065,24 +2059,24 @@
         <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" t="s">
         <v>125</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>126</v>
-      </c>
-      <c r="D9" t="s">
-        <v>127</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -2094,27 +2088,27 @@
         <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="s">
+        <v>129</v>
+      </c>
+      <c r="E10" t="s">
         <v>130</v>
-      </c>
-      <c r="E10" t="s">
-        <v>131</v>
       </c>
       <c r="F10">
         <v>70</v>
@@ -2123,27 +2117,27 @@
         <v>37</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
         <v>133</v>
-      </c>
-      <c r="B11" t="s">
-        <v>134</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E11" t="s">
         <v>135</v>
-      </c>
-      <c r="E11" t="s">
-        <v>136</v>
       </c>
       <c r="F11">
         <v>60</v>
@@ -2152,10 +2146,10 @@
         <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="176">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -420,6 +420,9 @@
   </si>
   <si>
     <t>https://sagaescaperoom.com/</t>
+  </si>
+  <si>
+    <t>Esto es un review de pruebas, muy muy chulo guay guay perfecto</t>
   </si>
   <si>
     <t>La Taberna</t>
@@ -1613,6 +1616,7 @@
     <col customWidth="1" min="9" max="9" width="23.5"/>
     <col customWidth="1" min="10" max="10" width="14.25"/>
     <col customWidth="1" min="11" max="11" width="21.13"/>
+    <col customWidth="1" min="12" max="12" width="166.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1649,6 +1653,9 @@
       <c r="K1" s="7" t="s">
         <v>131</v>
       </c>
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -1685,19 +1692,22 @@
         <f t="shared" ref="K2:K11" si="1">RANK(J2, $J$2:$J$22)</f>
         <v>3</v>
       </c>
+      <c r="L2" s="2" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -1712,7 +1722,7 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J3" s="1">
         <v>9.0</v>
@@ -1724,7 +1734,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>20</v>
@@ -1748,7 +1758,7 @@
         <v>9.0</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J4" s="8">
         <v>46062.0</v>
@@ -1760,19 +1770,19 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -1784,7 +1794,7 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J5" s="8">
         <v>46090.0</v>
@@ -1796,19 +1806,19 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -1820,7 +1830,7 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J6" s="8">
         <v>46243.0</v>
@@ -1832,16 +1842,16 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -1856,7 +1866,7 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J7" s="4">
         <v>46211.0</v>
@@ -1868,19 +1878,19 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
@@ -1892,7 +1902,7 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J8" s="8">
         <v>46149.0</v>
@@ -1904,16 +1914,16 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -1928,7 +1938,7 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J9" s="8">
         <v>46149.0</v>
@@ -1940,19 +1950,19 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
@@ -1964,7 +1974,7 @@
         <v>46149.0</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J10" s="1">
         <v>7.0</v>
@@ -1976,19 +1986,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2000,7 +2010,7 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J11" s="1">
         <v>6.0</v>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="164">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -89,15 +89,12 @@
     <t>Media-Alta</t>
   </si>
   <si>
-    <t>https://www.escapebarcelona.com/cybercity-2049</t>
+    <t>https://www.escapebarcelona.com/cybercity-2049.php</t>
   </si>
   <si>
     <t>Experiencia de estilo Cyberpunk inspirada en clásicos como Blade Runner o Matrix. Te traslada a un mundo decadente y futurista donde la toma de decisiones y la inmersión son los pilares centrales.</t>
   </si>
   <si>
-    <t>https://www.escapebarcelona.com/cybercity-2049.php</t>
-  </si>
-  <si>
     <t>Exodus</t>
   </si>
   <si>
@@ -212,21 +209,6 @@
     <t>Experiencia de estética Steampunk inspirada en las novelas de Julio Verne. Los jugadores deben explorar un submarino fantástico, resolviendo acertijos que combinan la mecánica clásica con una narrativa inmersiva.</t>
   </si>
   <si>
-    <t>Dragonborn</t>
-  </si>
-  <si>
-    <t>Quest Factory</t>
-  </si>
-  <si>
-    <t>Fantasía medieval</t>
-  </si>
-  <si>
-    <t>https://questfactory.es/</t>
-  </si>
-  <si>
-    <t>Una aventura de fantasía medieval y épica donde los jugadores deben ascender por una montaña remota. Es conocida por sus retos de alta calidad y una ambientación que transporta totalmente a un mundo de leyendas.</t>
-  </si>
-  <si>
     <t>Awaken</t>
   </si>
   <si>
@@ -236,7 +218,7 @@
     <t>Fantasía / magia</t>
   </si>
   <si>
-    <t>https://enigmaroom.es/</t>
+    <t>https://www.reddopamine.com/landing-aventura</t>
   </si>
   <si>
     <t>Una experiencia inmersiva que mezcla fantasía y magia. Los jugadores se convierten en protagonistas de una "película" donde el ingenio es la clave para superar pruebas diseñadas para fomentar la adrenalina y el trabajo en equipo.</t>
@@ -254,33 +236,12 @@
     <t>Misterio / tensión</t>
   </si>
   <si>
-    <t>https://enigmaroom.es/the-exam/</t>
+    <t>https://www.abduction.es/badalona/abduction3.html</t>
   </si>
   <si>
     <t>Un test de acción y aventura que pone a prueba tanto la mente como la agilidad física (subir escaleras, trepar). Es un juego dinámico y divertido, diseñado para que los adultos vuelvan a sentirse como niños.</t>
   </si>
   <si>
-    <t>La Cueva</t>
-  </si>
-  <si>
-    <t>La Cova Escape Room</t>
-  </si>
-  <si>
-    <t>Manresa</t>
-  </si>
-  <si>
-    <t>Aventura / exploración</t>
-  </si>
-  <si>
-    <t>8.0</t>
-  </si>
-  <si>
-    <t>https://lacovaescaperoom.com/</t>
-  </si>
-  <si>
-    <t>Una expedición de exploración inmersiva dividida en varias etapas. Ofrece la particularidad de vivir "3 experiencias en 1", donde la historia evoluciona conforme los jugadores se adentran en las profundidades de la cueva.</t>
-  </si>
-  <si>
     <t>Sherlock Holmes</t>
   </si>
   <si>
@@ -296,24 +257,6 @@
     <t>En esta misión de investigación, los jugadores son reclutados como agentes para resolver una serie de acertijos en el Londres victoriano y devolver la seguridad a la ciudad antes de que fuerzas oscuras ataquen.</t>
   </si>
   <si>
-    <t>El Tesoro del Pirata</t>
-  </si>
-  <si>
-    <t>Escape Sitges</t>
-  </si>
-  <si>
-    <t>Sitges</t>
-  </si>
-  <si>
-    <t>Piratas / búsqueda de tesoro</t>
-  </si>
-  <si>
-    <t>https://escapesitges.com/</t>
-  </si>
-  <si>
-    <t>Un juego de aventura clásica ideal para familias y grupos grandes. Los jugadores deben actuar bajo la presión del tiempo para encontrar un antiguo botín escondido antes de que otros bucaneros les pisen los talones.</t>
-  </si>
-  <si>
     <t>Atlantis</t>
   </si>
   <si>
@@ -323,7 +266,7 @@
     <t>Ciudad perdida</t>
   </si>
   <si>
-    <t>https://escapeworldbarcelona.com/</t>
+    <t>https://www.elementsescaperoom.com/atlantis/</t>
   </si>
   <si>
     <t>Un "hall escape" diseñado para grupos grandes donde el objetivo es descifrar los enigmas de una civilización sumergida. A diferencia de las salas estándar, el foco está en los puzzles y la comunicación del equipo.</t>
@@ -396,6 +339,27 @@
   </si>
   <si>
     <t>Experiencia de larga duración (2 horas) en la que los jugadores despiertan 500 años en el futuro tras ser criogenizados. Ofrece más de 140 metros cuadrados de ciencia ficción con instalaciones galardonadas.</t>
+  </si>
+  <si>
+    <t>Katrina</t>
+  </si>
+  <si>
+    <t>Elements</t>
+  </si>
+  <si>
+    <t>Esplugues</t>
+  </si>
+  <si>
+    <t>Azteca / Aventura</t>
+  </si>
+  <si>
+    <t>Inmersivo / Aventura</t>
+  </si>
+  <si>
+    <t>https://www.elementsescaperoom.com/katrina/</t>
+  </si>
+  <si>
+    <t>Una expedición arqueológica de gran formato (120 minutos) en busca del oro maldito de Moctezuma. Destaca por una ambientación selvática impresionante, dimensiones muy amplias y pruebas que requieren agilidad física. Es una experiencia de 'nueva generación' donde la escenografía y los mecanismos electrónicos sustituyen por completo a los candados tradicionales</t>
   </si>
   <si>
     <t>Duración (min)</t>
@@ -597,7 +561,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d.m"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -625,6 +589,20 @@
       <sz val="11.0"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+      <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
       <b/>
@@ -661,7 +639,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -683,7 +661,19 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -914,7 +904,7 @@
     <col customWidth="1" min="1" max="1" width="15.75"/>
     <col customWidth="1" min="2" max="2" width="21.75"/>
     <col customWidth="1" min="3" max="3" width="19.0"/>
-    <col customWidth="1" min="4" max="4" width="10.13"/>
+    <col customWidth="1" min="4" max="4" width="25.0"/>
     <col customWidth="1" min="8" max="8" width="16.0"/>
     <col customWidth="1" min="9" max="9" width="57.13"/>
     <col customWidth="1" min="10" max="10" width="172.5"/>
@@ -1023,24 +1013,24 @@
         <v>26</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="F4" s="3">
         <v>70.0</v>
@@ -1052,30 +1042,30 @@
         <v>46273.0</v>
       </c>
       <c r="I4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="K4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="F5" s="3">
         <v>70.0</v>
@@ -1087,27 +1077,27 @@
         <v>46089.0</v>
       </c>
       <c r="I5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="K5" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>15</v>
@@ -1119,33 +1109,33 @@
         <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="K6" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="F7" s="3">
         <v>60.0</v>
@@ -1157,56 +1147,56 @@
         <v>7.0</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H8" s="3">
         <v>8.0</v>
       </c>
       <c r="I8" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>15</v>
@@ -1221,68 +1211,68 @@
         <v>46181.0</v>
       </c>
       <c r="I9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="3">
+        <v>75.0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="4">
+        <v>46242.0</v>
+      </c>
+      <c r="I10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="3">
-        <v>70.0</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="4">
-        <v>46120.0</v>
-      </c>
-      <c r="I10" s="5" t="s">
+      <c r="J10" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="F11" s="3">
-        <v>75.0</v>
+        <v>90.0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="H11" s="4">
-        <v>46242.0</v>
+        <v>46150.0</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>74</v>
@@ -1299,7 +1289,7 @@
         <v>77</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>78</v>
@@ -1308,275 +1298,211 @@
         <v>79</v>
       </c>
       <c r="F12" s="3">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="H12" s="4">
-        <v>46150.0</v>
+        <v>46149.0</v>
       </c>
       <c r="I12" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3">
-        <v>70.0</v>
+        <v>75.0</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>86</v>
+      <c r="H13" s="4">
+        <v>46061.0</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="3">
+        <v>80.0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="4">
+        <v>46090.0</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="F14" s="3">
-        <v>60.0</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="4">
-        <v>46149.0</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F15" s="3">
-        <v>60.0</v>
+        <v>90.0</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="4">
-        <v>46241.0</v>
+      <c r="H15" s="3">
+        <v>7.0</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F16" s="3">
-        <v>75.0</v>
+        <v>90.0</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H16" s="4">
-        <v>46061.0</v>
+        <v>46150.0</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="F17" s="3">
+        <v>120.0</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="4">
+        <v>46150.0</v>
+      </c>
+      <c r="I17" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E17" s="1" t="s">
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="F17" s="3">
-        <v>80.0</v>
-      </c>
-      <c r="G17" s="1" t="s">
+      <c r="B18" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="8">
+        <v>120.0</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="4">
-        <v>46090.0</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="1" t="s">
+      <c r="H18" s="9">
+        <v>46243.0</v>
+      </c>
+      <c r="I18" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F18" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="I18" s="5" t="s">
+      <c r="J18" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="4">
-        <v>46150.0</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F20" s="3">
-        <v>120.0</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H20" s="4">
-        <v>46150.0</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1598,10 +1524,8 @@
     <hyperlink r:id="rId15" ref="I16"/>
     <hyperlink r:id="rId16" ref="I17"/>
     <hyperlink r:id="rId17" ref="I18"/>
-    <hyperlink r:id="rId18" ref="I19"/>
-    <hyperlink r:id="rId19" ref="I20"/>
   </hyperlinks>
-  <drawing r:id="rId20"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -1620,38 +1544,38 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="G1" s="7" t="s">
+      <c r="F1" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="I1" s="7" t="s">
+      <c r="H1" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>131</v>
+      <c r="J1" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>9</v>
@@ -1659,19 +1583,19 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F2" s="3">
         <v>70.0</v>
@@ -1683,34 +1607,34 @@
         <v>9.0</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J2" s="8">
+        <v>123</v>
+      </c>
+      <c r="J2" s="12">
         <v>46151.0</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="13">
         <f t="shared" ref="K2:K11" si="1">RANK(J2, $J$2:$J$22)</f>
         <v>3</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" s="3">
         <v>60.0</v>
@@ -1722,31 +1646,31 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="J3" s="1">
         <v>9.0</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="13">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3">
         <v>75.0</v>
@@ -1758,31 +1682,31 @@
         <v>9.0</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="J4" s="8">
+        <v>130</v>
+      </c>
+      <c r="J4" s="12">
         <v>46062.0</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="13">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -1794,31 +1718,31 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="J5" s="8">
+        <v>135</v>
+      </c>
+      <c r="J5" s="12">
         <v>46090.0</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="13">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -1830,31 +1754,31 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="J6" s="8">
+        <v>140</v>
+      </c>
+      <c r="J6" s="12">
         <v>46243.0</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="13">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F7" s="3">
         <v>90.0</v>
@@ -1866,31 +1790,31 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="J7" s="4">
         <v>46211.0</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="13">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
@@ -1902,31 +1826,31 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="J8" s="8">
+        <v>148</v>
+      </c>
+      <c r="J8" s="12">
         <v>46149.0</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="13">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F9" s="3">
         <v>80.0</v>
@@ -1938,31 +1862,31 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="J9" s="8">
+        <v>153</v>
+      </c>
+      <c r="J9" s="12">
         <v>46149.0</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="13">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
@@ -1974,31 +1898,31 @@
         <v>46149.0</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="J10" s="1">
         <v>7.0</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="13">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2010,12 +1934,12 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="J11" s="1">
         <v>6.0</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="13">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="166">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -41,6 +41,9 @@
     <t>Web</t>
   </si>
   <si>
+    <t>Max_personas</t>
+  </si>
+  <si>
     <t>Descripción</t>
   </si>
   <si>
@@ -65,12 +68,15 @@
     <t>Media</t>
   </si>
   <si>
+    <t>Escape Room</t>
+  </si>
+  <si>
+    <t>Una aventura pirata de película donde te sumerges en la búsqueda del tesoro de uno de los piratas más famosos. Destaca por su escenografía espectacular que recuerda a atracciones temáticas de grandes parques.</t>
+  </si>
+  <si>
     <t>https://willyeltuertoescaperoom.com/</t>
   </si>
   <si>
-    <t>Una aventura pirata de película donde te sumerges en la búsqueda del tesoro de uno de los piratas más famosos. Destaca por su escenografía espectacular que recuerda a atracciones temáticas de grandes parques.</t>
-  </si>
-  <si>
     <t>Cybercity 2049</t>
   </si>
   <si>
@@ -146,7 +152,7 @@
     <t>9.0</t>
   </si>
   <si>
-    <t>https://www.escapebarcelona.com/</t>
+    <t>https://escapeup.es/escape-room/unreal/barcelona/distrito-111/</t>
   </si>
   <si>
     <t>Un thriller de supervivencia en un mundo al borde del colapso total. Con una atmósfera de cine y estética post-apocalíptica, los jugadores deben cumplir una misión crítica en un entorno hostil y caótico.</t>
@@ -176,6 +182,9 @@
     <t>Abduction Escape Rooms</t>
   </si>
   <si>
+    <t>Badalona</t>
+  </si>
+  <si>
     <t>Nave espacial / sci-fi</t>
   </si>
   <si>
@@ -191,24 +200,6 @@
     <t>Una aventura tecnológica ambientada en una nave espacial. Destaca por requerir agilidad física y por integrar tecnología avanzada en sus puzzles, alejándose de los candados tradicionales para ofrecer una experiencia de adrenalina.</t>
   </si>
   <si>
-    <t>Nautilus</t>
-  </si>
-  <si>
-    <t>Scaparium</t>
-  </si>
-  <si>
-    <t>Vilanova i la Geltrú</t>
-  </si>
-  <si>
-    <t>Submarino / steampunk</t>
-  </si>
-  <si>
-    <t>https://scaparium.com/</t>
-  </si>
-  <si>
-    <t>Experiencia de estética Steampunk inspirada en las novelas de Julio Verne. Los jugadores deben explorar un submarino fantástico, resolviendo acertijos que combinan la mecánica clásica con una narrativa inmersiva.</t>
-  </si>
-  <si>
     <t>Awaken</t>
   </si>
   <si>
@@ -242,19 +233,16 @@
     <t>Un test de acción y aventura que pone a prueba tanto la mente como la agilidad física (subir escaleras, trepar). Es un juego dinámico y divertido, diseñado para que los adultos vuelvan a sentirse como niños.</t>
   </si>
   <si>
-    <t>Sherlock Holmes</t>
-  </si>
-  <si>
-    <t>Maximum Escape</t>
-  </si>
-  <si>
-    <t>Investigación / detectives</t>
-  </si>
-  <si>
-    <t>Misterio / puzzles</t>
-  </si>
-  <si>
-    <t>En esta misión de investigación, los jugadores son reclutados como agentes para resolver una serie de acertijos en el Londres victoriano y devolver la seguridad a la ciudad antes de que fuerzas oscuras ataquen.</t>
+    <t>Jurassic Land</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploración </t>
+  </si>
+  <si>
+    <t>https://www.escapebarcelona.com/jurassic-land.php</t>
+  </si>
+  <si>
+    <t>Una aventura inmersiva ambientada en una reserva de dinosaurios. Los jugadores deben restaurar los sistemas de seguridad de la isla tras un fallo crítico. Destaca por su ambientación selvática, el uso de animatronics y por ser una sala ideal para grupos grandes y familias.</t>
   </si>
   <si>
     <t>Atlantis</t>
@@ -293,7 +281,7 @@
     <t>Una aventura inmersiva única de 120 minutos (2 horas) donde los jugadores realizan un viaje al interior del cuerpo humano. Es extremadamente tecnológica, de gran formato y requiere calzado cómodo para moverse.</t>
   </si>
   <si>
-    <t>Tomb Hunter</t>
+    <t>Tomb Hunter : La Leyenda de Akasha Escape Room</t>
   </si>
   <si>
     <t>Arqueología</t>
@@ -386,7 +374,7 @@
     <t>https://sagaescaperoom.com/</t>
   </si>
   <si>
-    <t>Esto es un review de pruebas, muy muy chulo guay guay perfecto</t>
+    <t>Inmersión cinematográfica absoluta en el Londres victoriano. Destaca por una escenografía de primer nivel que recrea calles realistas con niebla, olores y texturas impecables. Puzzles de nueva generación totalmente integrados en la trama (sin candados forzados) y un flujo de juego excelente. El acting del Game Master y la transición de espacios elevan la experiencia a un nivel de 'imprescindible' para amantes del misterio. Jugado con 3 adultos + 2 niñas de 10 años</t>
   </si>
   <si>
     <t>La Taberna</t>
@@ -401,6 +389,9 @@
     <t>https://thecityescape.com/</t>
   </si>
   <si>
+    <t>Aventura medieval de alta inmersión situada en una taberna hiperrealista donde la interacción con el entorno y el Game Master es la clave. Destaca por su escenografía detallada, enigmas mecánicos totalmente integrados y un inicio de juego muy original que rompe la cuarta pared. Es una sala con mucho 'flow' que prioriza la diversión y el roleo sobre la dificultad extrema, logrando que el equipo se sienta realmente dentro de una película de fantasía. Interacción con personajes. Fuimos 3 adultos y 2 niñas de 9 años</t>
+  </si>
+  <si>
     <t>K.O.N.G. Protocol</t>
   </si>
   <si>
@@ -420,6 +411,9 @@
   </si>
   <si>
     <t>https://goldenpop.es/</t>
+  </si>
+  <si>
+    <t>Espectáculo visual y sensorial que recrea una selva hiperrealista bajo el centro de Barcelona. Una aventura de 120 minutos cargada de nostalgia, con una escenografía de nivel cinematográfico, efectos de sonido potentes y transiciones asombrosas que te hacen sentir dentro de la película. Es una sala muy física (requiere gatear, trepar y posiblemente ensuciarse un poco) que apuesta por la inmersión total y la adrenalina sin llegar al terror. Los constantes guiños y el acting inicial la consolidan como una de las experiencias de 'nueva generación' más potentes actualmente. Lo hicimos 4 adultos y una niña de 9 años</t>
   </si>
   <si>
     <t>WHITECHAPEL</t>
@@ -445,6 +439,9 @@
     </r>
   </si>
   <si>
+    <t>Un viaje asfixiante al Londres de Jack el Destripador que destaca por una de las ambientaciones más envolventes de Barcelona. El diseño de sus 'calles' oscuras y el uso de la iluminación crean una atmósfera lúgubre y laberíntica donde la narrativa cobra vida gracias a un acting magistral (mención especial al personaje de Sam). Combina puzzles lógicos con momentos de alta adrenalina, logrando que el equipo se sienta acechado constantemente. Es una experiencia puramente cinematográfica donde la tensión nunca decae. Fuimos 6 adultos. Siendo bastantes nuca estabas parado.</t>
+  </si>
+  <si>
     <t>Catacumbas</t>
   </si>
   <si>
@@ -462,10 +459,13 @@
     </r>
   </si>
   <si>
+    <t>Aventura épica de corte clásico inspirada en el universo de Indiana Jones, que destaca por una de las puestas en escena más espectaculares de la ciudad. Con más de 200 m² de decorados hiperrealistas, efectos de sonido envolventes y una iluminación que recrea perfectamente la atmósfera de una expedición arqueológica. Los enigmas están magistralmente integrados en el entorno, priorizando los mecanismos electrónicos y el trabajo cooperativo. Es una experiencia de pura adrenalina y exploración, ideal para quienes buscan sentirse protagonistas de una película de acción sin elementos de terror. Lo hicimos 4 adultos y la peque de 9 años.</t>
+  </si>
+  <si>
     <t>Exorcista</t>
   </si>
   <si>
-    <t>Terror Stories</t>
+    <t xml:space="preserve">Terror Stories </t>
   </si>
   <si>
     <t>Exorcismo / Posesión</t>
@@ -485,6 +485,9 @@
     </r>
   </si>
   <si>
+    <t>Homenaje visceral y cinematográfico al clásico del cine de posesiones. Destaca por un acting agresivo y escenas coreografiadas de una intensidad asombrosa que te hacen sentir dentro de una pesadilla real. La ambientación es lúgubre y opresiva, utilizando tecnología de efectos visuales y sonoros para recrear fenómenos paranormales impactantes. Es una sala dinámica, con pruebas de valor que obligan a dividir al equipo y una fluidez constante. Ideal para quienes buscan un terror físico y psicológico de alto nivel con una puesta en escena inolvidable. Fuimos 5 adultos, igual corto para tanta gente.</t>
+  </si>
+  <si>
     <t>Jaipur</t>
   </si>
   <si>
@@ -508,6 +511,9 @@
     </r>
   </si>
   <si>
+    <t>Fantasía pura y colorista inspirada en el folclore de la India que rompe con la estética lúgubre de los escapes tradicionales. Destaca por una escenografía vibrante, llena de detalles exóticos y una banda sonora envolvente que te transporta a un mercado mágico de Jaipur. Sus puzzles son ingeniosos, muy táctiles y basados en mecanismos 'mágicos' sorprendentes que fluyen con gran naturalidad. Es una experiencia alegre, mágica y cargada de buen rollo, ideal para quienes buscan una aventura inmersiva de alta calidad donde el asombro y el ingenio son los protagonistas. Lo hicimos 3 adultos y 3 peques de 10-11 años. Muy divertido</t>
+  </si>
+  <si>
     <t>encryptroom</t>
   </si>
   <si>
@@ -561,7 +567,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d.m"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -581,7 +587,18 @@
     <font>
       <u/>
       <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -639,7 +656,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -662,18 +679,24 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -901,14 +924,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.75"/>
+    <col customWidth="1" min="1" max="1" width="39.88"/>
     <col customWidth="1" min="2" max="2" width="21.75"/>
     <col customWidth="1" min="3" max="3" width="19.0"/>
     <col customWidth="1" min="4" max="4" width="25.0"/>
-    <col customWidth="1" min="8" max="8" width="16.0"/>
-    <col customWidth="1" min="9" max="9" width="57.13"/>
-    <col customWidth="1" min="10" max="10" width="172.5"/>
-    <col customWidth="1" min="11" max="11" width="40.88"/>
+    <col customWidth="1" min="8" max="8" width="11.5"/>
+    <col customWidth="1" min="9" max="9" width="61.38"/>
+    <col customWidth="1" min="10" max="10" width="13.88"/>
+    <col customWidth="1" min="11" max="11" width="172.5"/>
+    <col customWidth="1" min="12" max="12" width="40.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -942,567 +966,586 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="3">
         <v>80.0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="4">
         <v>46273.0</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>17</v>
+      <c r="J2" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
         <v>90.0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H3" s="4">
         <v>46090.0</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>25</v>
+      <c r="I3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J3" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F4" s="3">
         <v>70.0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" s="4">
         <v>46273.0</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>32</v>
+      <c r="I4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3">
         <v>70.0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="4">
         <v>46089.0</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>39</v>
+      <c r="I5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K6" s="2" t="s">
         <v>46</v>
+      </c>
+      <c r="J6" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F7" s="3">
         <v>60.0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="3">
         <v>7.0</v>
       </c>
-      <c r="I7" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>51</v>
+      <c r="I7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H8" s="3">
         <v>8.0</v>
       </c>
-      <c r="I8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>58</v>
+      <c r="I8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J8" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="3">
-        <v>70.0</v>
+        <v>75.0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H9" s="4">
-        <v>46181.0</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>64</v>
+        <v>46242.0</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J9" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="F10" s="3">
-        <v>75.0</v>
+        <v>90.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="H10" s="4">
-        <v>46242.0</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>69</v>
+        <v>46150.0</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>70</v>
+      <c r="A11" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="F11" s="3">
-        <v>90.0</v>
+        <v>60.0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="H11" s="4">
-        <v>46150.0</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="J11" s="1" t="s">
+        <v>46149.0</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>75</v>
+      </c>
+      <c r="J11" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="F12" s="3">
-        <v>60.0</v>
+        <v>75.0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" s="4">
-        <v>46149.0</v>
-      </c>
-      <c r="I12" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="1" t="s">
+        <v>46061.0</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>80</v>
+      </c>
+      <c r="J12" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="F13" s="3">
-        <v>75.0</v>
+        <v>80.0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="H13" s="4">
-        <v>46061.0</v>
-      </c>
-      <c r="I13" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>85</v>
+        <v>46090.0</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="1">
+        <v>7.0</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>86</v>
+      <c r="A14" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F14" s="3">
-        <v>80.0</v>
+        <v>90.0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="4">
-        <v>46090.0</v>
+        <v>17</v>
+      </c>
+      <c r="H14" s="3">
+        <v>7.0</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="J14" s="1" t="s">
         <v>92</v>
+      </c>
+      <c r="J14" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F15" s="3">
         <v>90.0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="J15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="4">
+        <v>46150.0</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>97</v>
+      </c>
+      <c r="J15" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F16" s="3">
-        <v>90.0</v>
+        <v>120.0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="H16" s="4">
         <v>46150.0</v>
       </c>
-      <c r="I16" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>102</v>
+      <c r="I16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="J16" s="1">
+        <v>8.0</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="A17" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="B17" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="F17" s="3">
+      <c r="C17" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="F17" s="10">
         <v>120.0</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" s="4">
-        <v>46150.0</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="8" t="s">
+      <c r="G17" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="11">
+        <v>46243.0</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="J17" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="8">
-        <v>120.0</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="9">
-        <v>46243.0</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1523,9 +1566,8 @@
     <hyperlink r:id="rId14" ref="I15"/>
     <hyperlink r:id="rId15" ref="I16"/>
     <hyperlink r:id="rId16" ref="I17"/>
-    <hyperlink r:id="rId17" ref="I18"/>
   </hyperlinks>
-  <drawing r:id="rId18"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -1544,260 +1586,272 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="G1" s="11" t="s">
+      <c r="F1" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="I1" s="11" t="s">
+      <c r="H1" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="K1" s="11" t="s">
-        <v>119</v>
+      <c r="J1" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>115</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F2" s="3">
         <v>70.0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H2" s="3">
         <v>9.0</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="J2" s="12">
+      <c r="I2" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="14">
         <v>46151.0</v>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="15">
         <f t="shared" ref="K2:K11" si="1">RANK(J2, $J$2:$J$22)</f>
         <v>3</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3">
         <v>60.0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="4">
         <v>46150.0</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>128</v>
+      <c r="I3" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="J3" s="1">
         <v>9.0</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="15">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
+      <c r="L3" s="2" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F4" s="3">
         <v>75.0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" s="3">
         <v>9.0</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="J4" s="12">
+      <c r="I4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J4" s="14">
         <v>46062.0</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="15">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="3">
         <v>8.0</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="J5" s="12">
+      <c r="I5" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="J5" s="14">
         <v>46090.0</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="15">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
+      <c r="L5" s="2" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" s="3">
         <v>9.0</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="J6" s="12">
+      <c r="I6" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="J6" s="14">
         <v>46243.0</v>
       </c>
-      <c r="K6" s="13">
+      <c r="K6" s="15">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
+      <c r="L6" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3">
         <v>90.0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H7" s="4">
         <v>46149.0</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>143</v>
+      <c r="I7" s="8" t="s">
+        <v>142</v>
       </c>
       <c r="J7" s="4">
         <v>46211.0</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="15">
         <f t="shared" si="1"/>
         <v>2</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="8">
@@ -1808,7 +1862,7 @@
         <v>145</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>146</v>
@@ -1820,126 +1874,132 @@
         <v>90.0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" s="4">
         <v>46150.0</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="14">
         <v>46149.0</v>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
+      <c r="L8" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F9" s="3">
         <v>80.0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" s="4">
         <v>46149.0</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="J9" s="12">
+      <c r="I9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="J9" s="14">
         <v>46149.0</v>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="15">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
+      <c r="L9" s="2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H10" s="4">
         <v>46149.0</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>158</v>
+      <c r="I10" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="J10" s="1">
         <v>7.0</v>
       </c>
-      <c r="K10" s="13">
+      <c r="K10" s="15">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" s="4">
         <v>46148.0</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>163</v>
+      <c r="I11" s="8" t="s">
+        <v>165</v>
       </c>
       <c r="J11" s="1">
         <v>6.0</v>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="15">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -668,7 +668,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -711,10 +711,11 @@
     <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1593,7 +1594,7 @@
     <col customWidth="1" min="1" max="1" width="15.63"/>
     <col customWidth="1" min="9" max="9" width="23.5"/>
     <col customWidth="1" min="10" max="10" width="14.25"/>
-    <col customWidth="1" min="11" max="11" width="21.13"/>
+    <col customWidth="1" min="11" max="11" width="14.13"/>
     <col customWidth="1" min="12" max="15" width="11.75"/>
     <col customWidth="1" min="16" max="16" width="166.0"/>
   </cols>
@@ -1677,20 +1678,21 @@
         <v>123</v>
       </c>
       <c r="J2" s="14">
+        <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
+        <v>11544.75</v>
+      </c>
+      <c r="K2" s="15">
+        <f t="shared" ref="K2:K11" si="2">RANK(J2, $J$2:$J$22)</f>
+        <v>1</v>
+      </c>
+      <c r="L2" s="16">
         <v>46151.0</v>
-      </c>
-      <c r="K2" s="15">
-        <f t="shared" ref="K2:K11" si="1">RANK(J2, $J$2:$J$22)</f>
-        <v>3</v>
-      </c>
-      <c r="L2" s="2">
-        <v>9.0</v>
       </c>
       <c r="M2" s="2">
         <v>10.0</v>
       </c>
       <c r="N2" s="2">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="O2" s="2">
         <v>9.0</v>
@@ -1727,12 +1729,13 @@
       <c r="I3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="J3" s="1">
-        <v>9.0</v>
+      <c r="J3" s="15">
+        <f t="shared" si="1"/>
+        <v>8.5</v>
       </c>
       <c r="K3" s="15">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <f t="shared" si="2"/>
+        <v>4</v>
       </c>
       <c r="L3" s="2">
         <v>9.0</v>
@@ -1778,12 +1781,12 @@
       <c r="I4" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="J4" s="14">
-        <v>46062.0</v>
+      <c r="J4" s="1">
+        <v>0.0</v>
       </c>
       <c r="K4" s="15">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <f t="shared" si="2"/>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -1814,12 +1817,13 @@
       <c r="I5" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="J5" s="14">
-        <v>46090.0</v>
+      <c r="J5" s="15">
+        <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
+        <v>9.25</v>
       </c>
       <c r="K5" s="15">
-        <f t="shared" si="1"/>
-        <v>6</v>
+        <f t="shared" si="2"/>
+        <v>2</v>
       </c>
       <c r="L5" s="2">
         <v>9.0</v>
@@ -1865,12 +1869,13 @@
       <c r="I6" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="J6" s="14">
-        <v>46243.0</v>
+      <c r="J6" s="15">
+        <f t="shared" si="3"/>
+        <v>8.75</v>
       </c>
       <c r="K6" s="15">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="L6" s="2">
         <v>9.0</v>
@@ -1916,12 +1921,13 @@
       <c r="I7" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="J7" s="4">
-        <v>46211.0</v>
+      <c r="J7" s="15">
+        <f t="shared" si="3"/>
+        <v>8.25</v>
       </c>
       <c r="K7" s="15">
-        <f t="shared" si="1"/>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>6</v>
       </c>
       <c r="L7" s="2">
         <v>8.0</v>
@@ -1967,12 +1973,13 @@
       <c r="I8" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="J8" s="14">
-        <v>46149.0</v>
+      <c r="J8" s="15">
+        <f t="shared" si="3"/>
+        <v>8</v>
       </c>
       <c r="K8" s="15">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <f t="shared" si="2"/>
+        <v>7</v>
       </c>
       <c r="L8" s="2">
         <v>8.0</v>
@@ -2018,11 +2025,12 @@
       <c r="I9" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="J9" s="14">
-        <v>46149.0</v>
+      <c r="J9" s="15">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
       </c>
       <c r="K9" s="15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="L9" s="2">
@@ -2069,12 +2077,13 @@
       <c r="I10" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="J10" s="1">
-        <v>7.0</v>
+      <c r="J10" s="15">
+        <f t="shared" si="3"/>
+        <v>7.5</v>
       </c>
       <c r="K10" s="15">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <f t="shared" si="2"/>
+        <v>8</v>
       </c>
       <c r="L10" s="2">
         <v>7.0</v>
@@ -2117,12 +2126,13 @@
       <c r="I11" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="J11" s="1">
-        <v>6.0</v>
+      <c r="J11" s="15">
+        <f t="shared" si="3"/>
+        <v>6.75</v>
       </c>
       <c r="K11" s="15">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>9</v>
       </c>
       <c r="L11" s="2">
         <v>7.0</v>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="171">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -386,7 +386,7 @@
     <t>https://sagaescaperoom.com/</t>
   </si>
   <si>
-    <t>Inmersión cinematográfica absoluta en el Londres victoriano. Destaca por una escenografía de primer nivel que recrea calles realistas con niebla, olores y texturas impecables. Puzzles de nueva generación totalmente integrados en la trama (sin candados forzados) y un flujo de juego excelente. El acting del Game Master y la transición de espacios elevan la experiencia a un nivel de 'imprescindible' para amantes del misterio. Jugado con 3 adultos + 2 niñas de 10 años</t>
+    <t>Inmersión cinematográfica absoluta con una estética Steampunk y victoriana impecable (niebla, olores y texturas de primer nivel). Jugada por 3 adultos y 2 niñas de 10 años en modo Tensión, resultó una experiencia redonda: las niñas fliparon desde la primera sala y el trato del Game Master fue excelente y muy cordial. Los puzzles de nueva generación están totalmente integrados en la trama, logrando un flujo de juego magnífico sin candados forzados. Una joya visual y narrativa que, gracias a su ambientación única, encantó a todo el grupo por igual.</t>
   </si>
   <si>
     <t>La Taberna</t>
@@ -401,7 +401,7 @@
     <t>https://thecityescape.com/</t>
   </si>
   <si>
-    <t>Aventura medieval de alta inmersión situada en una taberna hiperrealista donde la interacción con el entorno y el Game Master es la clave. Destaca por su escenografía detallada, enigmas mecánicos totalmente integrados y un inicio de juego muy original que rompe la cuarta pared. Es una sala con mucho 'flow' que prioriza la diversión y el roleo sobre la dificultad extrema, logrando que el equipo se sienta realmente dentro de una película de fantasía. Interacción con personajes. Fuimos 3 adultos y 2 niñas de 9 años</t>
+    <t>Aventura de alta inmersión que inicia en una taberna hiperrealista donde la interacción con el entorno y el roleo son la clave. Destaca por una escenografía brutal en la mayoría de sus salas, logrando que el equipo (3 adultos y 2 niñas de 9 años) se sienta realmente dentro de una película de fantasía. Aunque el arranque es muy original y los enigmas mecánicos están integrados, nuestra experiencia con el acting de la Game Master Tabernera no nos terminó de impactar y algún puzzle se nos hizo complicado, perdiendo fluidez en ciertos momentos. A pesar de ello, se mantiene sin duda como uno de los mejores escapes a nivel español por su despliegue visual.</t>
   </si>
   <si>
     <t>K.O.N.G. Protocol</t>
@@ -425,7 +425,7 @@
     <t>https://goldenpop.es/</t>
   </si>
   <si>
-    <t>Espectáculo visual y sensorial que recrea una selva hiperrealista bajo el centro de Barcelona. Una aventura de 120 minutos cargada de nostalgia, con una escenografía de nivel cinematográfico, efectos de sonido potentes y transiciones asombrosas que te hacen sentir dentro de la película. Es una sala muy física (requiere gatear, trepar y posiblemente ensuciarse un poco) que apuesta por la inmersión total y la adrenalina sin llegar al terror. Los constantes guiños y el acting inicial la consolidan como una de las experiencias de 'nueva generación' más potentes actualmente. Lo hicimos 4 adultos y una niña de 9 años</t>
+    <t>Espectáculo visual y sensorial que recrea una selva hiperrealista bajo el centro de Barcelona. Una aventura de 120 minutos cargada de nostalgia, con una escenografía cinematográfica y efectos de sonido potentes. Jugado por 4 adultos y una niña de 9 años, destacamos el excelente acting inicial; el impacto del Game Master sobre la peque fue muy bueno y lo recuerda con mucho cariño. Es un escape dinámico con separación del grupo y una gran cantidad de juegos que garantiza que no haya momentos de parón. Ve preparado para gatear y ensuciarte con un poco de barro, ya que la vegetación se tiene que mantener. Una experiencia de 'nueva generación' de las más potentes del panorama actual.</t>
   </si>
   <si>
     <t>WHITECHAPEL</t>
@@ -451,7 +451,7 @@
     </r>
   </si>
   <si>
-    <t>Un viaje asfixiante al Londres de Jack el Destripador que destaca por una de las ambientaciones más envolventes de Barcelona. El diseño de sus 'calles' oscuras y el uso de la iluminación crean una atmósfera lúgubre y laberíntica donde la narrativa cobra vida gracias a un acting magistral (mención especial al personaje de Sam). Combina puzzles lógicos con momentos de alta adrenalina, logrando que el equipo se sienta acechado constantemente. Es una experiencia puramente cinematográfica donde la tensión nunca decae. Fuimos 6 adultos. Siendo bastantes nuca estabas parado.</t>
+    <t>Un viaje asfixiante al Londres de Jack el Destripador con una de las ambientaciones más envolventes y lúgubres de Barcelona. Jugado por 6 adultos en modo Terror (también disponible en modo Aventura), resultó ser una experiencia de una intensidad arrolladora. A pesar de ser un grupo numeroso, nunca estuvimos parados, gracias a un diseño de 'calles' oscuras y laberínticas que mantiene la tensión constante. Destaca por un acting magistral y un contacto físico con los personajes que eleva la adrenalina al máximo. Una experiencia puramente cinematográfica que se sitúa, sin duda, en el top de los escapes de terror realizados.</t>
   </si>
   <si>
     <t>Catacumbas</t>
@@ -471,7 +471,7 @@
     </r>
   </si>
   <si>
-    <t>Aventura épica de corte clásico inspirada en el universo de Indiana Jones, que destaca por una de las puestas en escena más espectaculares de la ciudad. Con más de 200 m² de decorados hiperrealistas, efectos de sonido envolventes y una iluminación que recrea perfectamente la atmósfera de una expedición arqueológica. Los enigmas están magistralmente integrados en el entorno, priorizando los mecanismos electrónicos y el trabajo cooperativo. Es una experiencia de pura adrenalina y exploración, ideal para quienes buscan sentirse protagonistas de una película de acción sin elementos de terror. Lo hicimos 4 adultos y la peque de 9 años.</t>
+    <t>Aventura épica inspirada en el universo de Indiana Jones que ofrece una de las puestas en escena más espectaculares de la ciudad. Jugada por 4 adultos y una niña de 9 años, resultó ser una experiencia increíble con pasadizos, puertas y salas totalmente inesperados. Destaca por sus más de 200 m² de decorados hiperrealistas y pruebas directamente basadas en las películas, logrando una atmósfera de expedición arqueológica total. Los enigmas están magistralmente integrados, priorizando mecanismos electrónicos y un trabajo cooperativo que mantiene la adrenalina alta sin necesidad de terror. Una experiencia de exploración pura donde las transiciones entre zonas dejan al grupo boquiabierto.</t>
   </si>
   <si>
     <t>Exorcista</t>
@@ -497,7 +497,7 @@
     </r>
   </si>
   <si>
-    <t>Homenaje visceral y cinematográfico al clásico del cine de posesiones. Destaca por un acting agresivo y escenas coreografiadas de una intensidad asombrosa que te hacen sentir dentro de una pesadilla real. La ambientación es lúgubre y opresiva, utilizando tecnología de efectos visuales y sonoros para recrear fenómenos paranormales impactantes. Es una sala dinámica, con pruebas de valor que obligan a dividir al equipo y una fluidez constante. Ideal para quienes buscan un terror físico y psicológico de alto nivel con una puesta en escena inolvidable. Fuimos 5 adultos, igual corto para tanta gente.</t>
+    <t>Homenaje visceral y cinematográfico al clásico del cine de posesiones. Jugado por 5 adultos en modo Terror (disponible también modo Aventura), resultó una experiencia de una intensidad asombrosa, aunque el espacio puede sentirse algo justo para un grupo de cinco. Destaca por una ambientación lúgubre y opresiva con efectos visuales y sonoros que recrean fenómenos paranormales impactantes. El punto más fuerte es el acting increíble de los Game Masters, con una mención especial a la interpretación de 'la niña', posiblemente la mejor actuación vista jamás en un escape room. Incluye dinámicas de separación total del grupo, dejando a los jugadores solos en momentos puntuales de máxima vulnerabilidad. Una pesadilla real con una puesta en escena inolvidable.</t>
   </si>
   <si>
     <t>Jaipur</t>
@@ -523,7 +523,7 @@
     </r>
   </si>
   <si>
-    <t>Fantasía pura y colorista inspirada en el folclore de la India que rompe con la estética lúgubre de los escapes tradicionales. Destaca por una escenografía vibrante, llena de detalles exóticos y una banda sonora envolvente que te transporta a un mercado mágico de Jaipur. Sus puzzles son ingeniosos, muy táctiles y basados en mecanismos 'mágicos' sorprendentes que fluyen con gran naturalidad. Es una experiencia alegre, mágica y cargada de buen rollo, ideal para quienes buscan una aventura inmersiva de alta calidad donde el asombro y el ingenio son los protagonistas. Lo hicimos 3 adultos y 3 peques de 10-11 años. Muy divertido</t>
+    <t>Fantasía pura y colorista inspirada en el folclore de la India que rompe con la estética lúgubre tradicional. Jugado por 3 adultos y 3 niñas de 10-11 años, resultó una experiencia sumamente divertida donde las pequeñas no pararon ni un segundo de resolver retos. Destaca por una escenografía vibrante y una decoración preciosa, con olores característicos que te transportan a un mercado exótico. Los puzzles son muy táctiles e ingeniosos, huyendo de los clásicos candados para centrarse en mecanismos 'mágicos' que fluyen con naturalidad. Con una historia sólida y un sorprendente giro de argumento, es un espectáculo visual cargado de buen rollo donde el asombro y el ingenio son los protagonistas.</t>
   </si>
   <si>
     <t>encryptroom</t>
@@ -570,6 +570,9 @@
       </rPr>
       <t>missionleak.com</t>
     </r>
+  </si>
+  <si>
+    <t>Referente de la 'vieja escuela' jugado originalmente en 2015. En su momento fue pionero en la temática de atracos, pero con la perspectiva actual de las salas de nueva generación, se siente una experiencia sencilla, lineal y muy basada en candados. Nota importante: Nuestra valoración se basa en la versión de hace años; desconocemos si ha recibido actualizaciones técnicas o de escenografía desde entonces. Comparado con los estándares inmersivos de 2026, palidece en espectacularidad y fluidez narrativa, quedando como una pieza de coleccionista para entender los inicios del sector. Lo hicimos 4 adultos</t>
   </si>
 </sst>
 </file>
@@ -2146,6 +2149,9 @@
       <c r="O11" s="2">
         <v>6.0</v>
       </c>
+      <c r="P11" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="170">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -68,13 +68,10 @@
     <t>Media</t>
   </si>
   <si>
-    <t>Escape Room</t>
+    <t>https://willyeltuertoescaperoom.com/</t>
   </si>
   <si>
     <t>Una aventura pirata de película donde te sumerges en la búsqueda del tesoro de uno de los piratas más famosos. Destaca por su escenografía espectacular que recuerda a atracciones temáticas de grandes parques.</t>
-  </si>
-  <si>
-    <t>https://willyeltuertoescaperoom.com/</t>
   </si>
   <si>
     <t>Cybercity 2049</t>
@@ -1024,100 +1021,100 @@
         <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F3" s="3">
         <v>90.0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" s="4">
         <v>46090.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J3" s="1">
         <v>6.0</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="F4" s="3">
         <v>70.0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" s="4">
         <v>46273.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J4" s="1">
         <v>6.0</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="F5" s="3">
         <v>70.0</v>
@@ -1129,30 +1126,30 @@
         <v>46089.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J5" s="1">
         <v>7.0</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>16</v>
@@ -1161,39 +1158,39 @@
         <v>90.0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="J6" s="1">
         <v>7.0</v>
       </c>
       <c r="K6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="F7" s="3">
         <v>60.0</v>
@@ -1205,62 +1202,62 @@
         <v>7.0</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J7" s="1">
         <v>8.0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H8" s="3">
         <v>8.0</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J8" s="1">
         <v>10.0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -1269,71 +1266,71 @@
         <v>75.0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="4">
         <v>46242.0</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J9" s="1">
         <v>7.0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="F10" s="3">
         <v>90.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H10" s="4">
         <v>46150.0</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J10" s="1">
         <v>6.0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -1345,30 +1342,30 @@
         <v>46149.0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J11" s="1">
         <v>10.0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>79</v>
-      </c>
       <c r="E12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12" s="3">
         <v>75.0</v>
@@ -1380,65 +1377,65 @@
         <v>46061.0</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J12" s="1">
         <v>12.0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="F13" s="3">
         <v>80.0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H13" s="4">
         <v>46090.0</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J13" s="1">
         <v>7.0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="F14" s="3">
         <v>90.0</v>
@@ -1450,30 +1447,30 @@
         <v>7.0</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J14" s="2">
         <v>6.0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="F15" s="3">
         <v>90.0</v>
@@ -1485,83 +1482,83 @@
         <v>46150.0</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J15" s="1">
         <v>10.0</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="F16" s="3">
         <v>120.0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H16" s="4">
         <v>46150.0</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J16" s="1">
         <v>8.0</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="D17" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>109</v>
       </c>
       <c r="F17" s="10">
         <v>120.0</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H17" s="11">
         <v>46243.0</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J17" s="2">
         <v>6.0</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1619,34 +1616,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="M1" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="N1" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="O1" s="13" t="s">
         <v>118</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>119</v>
       </c>
       <c r="P1" s="13" t="s">
         <v>10</v>
@@ -1654,19 +1651,19 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3">
         <v>70.0</v>
@@ -1678,7 +1675,7 @@
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J2" s="14">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
@@ -1701,24 +1698,24 @@
         <v>9.0</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F3" s="3">
         <v>60.0</v>
@@ -1730,7 +1727,7 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J3" s="15">
         <f t="shared" si="1"/>
@@ -1753,36 +1750,36 @@
         <v>7.0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F4" s="3">
         <v>75.0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" s="3">
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J4" s="1">
         <v>0.0</v>
@@ -1794,19 +1791,19 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>135</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -1818,7 +1815,7 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J5" s="15">
         <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
@@ -1841,24 +1838,24 @@
         <v>10.0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>140</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>141</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -1870,7 +1867,7 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J6" s="15">
         <f t="shared" si="3"/>
@@ -1893,24 +1890,24 @@
         <v>9.0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3">
         <v>90.0</v>
@@ -1922,7 +1919,7 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="3"/>
@@ -1945,24 +1942,24 @@
         <v>8.0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>150</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>151</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
@@ -1974,7 +1971,7 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="3"/>
@@ -1997,24 +1994,24 @@
         <v>9.0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="3">
         <v>80.0</v>
@@ -2026,7 +2023,7 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="3"/>
@@ -2049,36 +2046,36 @@
         <v>8.0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>163</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H10" s="4">
         <v>46149.0</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="3"/>
@@ -2103,19 +2100,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>168</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2127,7 +2124,7 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="3"/>
@@ -2150,7 +2147,7 @@
         <v>6.0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -419,7 +419,7 @@
     <t>Aventura familiar</t>
   </si>
   <si>
-    <t>https://goldenpop.es/</t>
+    <t>https://goldenpop.es/jurasico/</t>
   </si>
   <si>
     <t>Espectáculo visual y sensorial que recrea una selva hiperrealista bajo el centro de Barcelona. Una aventura de 120 minutos cargada de nostalgia, con una escenografía cinematográfica y efectos de sonido potentes. Jugado por 4 adultos y una niña de 9 años, destacamos el excelente acting inicial; el impacto del Game Master sobre la peque fue muy bueno y lo recuerda con mucho cariño. Es un escape dinámico con separación del grupo y una gran cantidad de juegos que garantiza que no haya momentos de parón. Ve preparado para gatear y ensuciarte con un poco de barro, ya que la vegetación se tiene que mantener. Una experiencia de 'nueva generación' de las más potentes del panorama actual.</t>
@@ -437,15 +437,7 @@
     <t>Terror / Inmersivo</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>roomwhitechapel.com</t>
-    </r>
+    <t>https://www.roomwhitechapel.com/</t>
   </si>
   <si>
     <t>Un viaje asfixiante al Londres de Jack el Destripador con una de las ambientaciones más envolventes y lúgubres de Barcelona. Jugado por 6 adultos en modo Terror (también disponible en modo Aventura), resultó ser una experiencia de una intensidad arrolladora. A pesar de ser un grupo numeroso, nunca estuvimos parados, gracias a un diseño de 'calles' oscuras y laberínticas que mantiene la tensión constante. Destaca por un acting magistral y un contacto físico con los personajes que eleva la adrenalina al máximo. Una experiencia puramente cinematográfica que se sitúa, sin duda, en el top de los escapes de terror realizados.</t>
@@ -457,15 +449,7 @@
     <t>Alquimia / Aventuras</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>goldenpop.es/catacumbas/</t>
-    </r>
+    <t>https://goldenpop.es/juegos/catacumbas/</t>
   </si>
   <si>
     <t>Aventura épica inspirada en el universo de Indiana Jones que ofrece una de las puestas en escena más espectaculares de la ciudad. Jugada por 4 adultos y una niña de 9 años, resultó ser una experiencia increíble con pasadizos, puertas y salas totalmente inesperados. Destaca por sus más de 200 m² de decorados hiperrealistas y pruebas directamente basadas en las películas, logrando una atmósfera de expedición arqueológica total. Los enigmas están magistralmente integrados, priorizando mecanismos electrónicos y un trabajo cooperativo que mantiene la adrenalina alta sin necesidad de terror. Una experiencia de exploración pura donde las transiciones entre zonas dejan al grupo boquiabierto.</t>
@@ -483,15 +467,7 @@
     <t>Terror</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>terrorstories.com</t>
-    </r>
+    <t>https://terrorstories.com/barcelona/exorcista-escape-room</t>
   </si>
   <si>
     <t>Homenaje visceral y cinematográfico al clásico del cine de posesiones. Jugado por 5 adultos en modo Terror (disponible también modo Aventura), resultó una experiencia de una intensidad asombrosa, aunque el espacio puede sentirse algo justo para un grupo de cinco. Destaca por una ambientación lúgubre y opresiva con efectos visuales y sonoros que recrean fenómenos paranormales impactantes. El punto más fuerte es el acting increíble de los Game Masters, con una mención especial a la interpretación de 'la niña', posiblemente la mejor actuación vista jamás en un escape room. Incluye dinámicas de separación total del grupo, dejando a los jugadores solos en momentos puntuales de máxima vulnerabilidad. Una pesadilla real con una puesta en escena inolvidable.</t>
@@ -509,15 +485,7 @@
     <t>Bollywood / India</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>kadabraescape.com</t>
-    </r>
+    <t>https://www.kadabraescape.com/el-secreto-de-jaipur/</t>
   </si>
   <si>
     <t>Fantasía pura y colorista inspirada en el folclore de la India que rompe con la estética lúgubre tradicional. Jugado por 3 adultos y 3 niñas de 10-11 años, resultó una experiencia sumamente divertida donde las pequeñas no pararon ni un segundo de resolver retos. Destaca por una escenografía vibrante y una decoración preciosa, con olores característicos que te transportan a un mercado exótico. Los puzzles son muy táctiles e ingeniosos, huyendo de los clásicos candados para centrarse en mecanismos 'mágicos' que fluyen con naturalidad. Con una historia sólida y un sorprendente giro de argumento, es un espectáculo visual cargado de buen rollo donde el asombro y el ingenio son los protagonistas.</t>
@@ -535,15 +503,7 @@
     <t>Tensión / Inmersivo</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>encryptroom.com</t>
-    </r>
+    <t>https://www.encryptroom.com/</t>
   </si>
   <si>
     <t>Bank of Thaqar</t>
@@ -558,15 +518,7 @@
     <t>Acción</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri, sans-serif"/>
-        <color rgb="FF1155CC"/>
-        <sz val="11.0"/>
-        <u/>
-      </rPr>
-      <t>missionleak.com</t>
-    </r>
+    <t>https://www.missionleak.com/bankofthaqar</t>
   </si>
   <si>
     <t>Referente de la 'vieja escuela' jugado originalmente en 2015. En su momento fue pionero en la temática de atracos, pero con la perspectiva actual de las salas de nueva generación, se siente una experiencia sencilla, lineal y muy basada en candados. Nota importante: Nuestra valoración se basa en la versión de hace años; desconocemos si ha recibido actualizaciones técnicas o de escenografía desde entonces. Comparado con los estándares inmersivos de 2026, palidece en espectacularidad y fluidez narrativa, quedando como una pieza de coleccionista para entender los inicios del sector. Lo hicimos 4 adultos</t>
@@ -1592,7 +1544,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="15.63"/>
-    <col customWidth="1" min="9" max="9" width="23.5"/>
+    <col customWidth="1" min="9" max="9" width="36.13"/>
     <col customWidth="1" min="10" max="10" width="14.25"/>
     <col customWidth="1" min="11" max="11" width="14.13"/>
     <col customWidth="1" min="12" max="15" width="11.75"/>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="196">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -167,9 +167,6 @@
     <t>Thriller / misterio</t>
   </si>
   <si>
-    <t>Narrativo</t>
-  </si>
-  <si>
     <t>Un misterio trepidante de 80 minutos donde el trabajo en equipo es vital. Los jugadores deben resolver enigmas y acertijos para completar una misión de la que solo podrán salir "gritando su nombre tres veces".</t>
   </si>
   <si>
@@ -347,6 +344,90 @@
     <t>Una expedición arqueológica de gran formato (120 minutos) en busca del oro maldito de Moctezuma. Destaca por una ambientación selvática impresionante, dimensiones muy amplias y pruebas que requieren agilidad física. Es una experiencia de 'nueva generación' donde la escenografía y los mecanismos electrónicos sustituyen por completo a los candados tradicionales</t>
   </si>
   <si>
+    <t>Outline</t>
+  </si>
+  <si>
+    <t>Outline Escape</t>
+  </si>
+  <si>
+    <t>Cornellà de Llobregat</t>
+  </si>
+  <si>
+    <t>Terror / Fábrica abandonada</t>
+  </si>
+  <si>
+    <t>Terror</t>
+  </si>
+  <si>
+    <t>https://outlineescaperoom.es/</t>
+  </si>
+  <si>
+    <t>Ubicado en una antigua fábrica abandonada. Es una experiencia muy inmersiva y física (120 min) que destaca por su acting y escenarios realistas.</t>
+  </si>
+  <si>
+    <t>Synergo</t>
+  </si>
+  <si>
+    <t>Synergo Escape</t>
+  </si>
+  <si>
+    <t>Tensión / Cazadores de Brujas</t>
+  </si>
+  <si>
+    <t>Tensión</t>
+  </si>
+  <si>
+    <t>https://synergoescaperoom.es/</t>
+  </si>
+  <si>
+    <t>Te conviertes en un cazador de brujas. Destaca por puzzles complejos y una ambientación de bosque y cabaña muy lograda.</t>
+  </si>
+  <si>
+    <t>El cetro de fuego</t>
+  </si>
+  <si>
+    <t>Aventura / Egipto</t>
+  </si>
+  <si>
+    <t>https://www.elementsescaperoom.com/el-cetro-de-fuego/</t>
+  </si>
+  <si>
+    <t>Expedición arqueológica clásica al estilo Indiana Jones. Ideal para familias, con pruebas orgánicas y efectos visuales de calidad.</t>
+  </si>
+  <si>
+    <t>Ouija</t>
+  </si>
+  <si>
+    <t>HorrorBox</t>
+  </si>
+  <si>
+    <t>Terror Paranormal</t>
+  </si>
+  <si>
+    <t>Media / Alta</t>
+  </si>
+  <si>
+    <t>https://www.horrorbox.es/producto/ouija-escape-room/</t>
+  </si>
+  <si>
+    <t>Centrado en el contacto con el más allá. Es un terror psicológico y ambiental muy intenso, con tecnología aplicada a los efectos. Es una sala de "vieja escuela" pero muy bien mantenida, ideal si buscáis una experiencia de terror puro y directo sin tanta parte física como Outline.</t>
+  </si>
+  <si>
+    <t>Escape Room</t>
+  </si>
+  <si>
+    <t>Tipo / Temática</t>
+  </si>
+  <si>
+    <t>Terror / Industrial</t>
+  </si>
+  <si>
+    <t>Tensión / Fantasía</t>
+  </si>
+  <si>
+    <t>El Cetro de Fuego</t>
+  </si>
+  <si>
     <t>Duración (min)</t>
   </si>
   <si>
@@ -462,9 +543,6 @@
   </si>
   <si>
     <t>Exorcismo / Posesión</t>
-  </si>
-  <si>
-    <t>Terror</t>
   </si>
   <si>
     <t>https://terrorstories.com/barcelona/exorcista-escape-room</t>
@@ -531,7 +609,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d.m"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -586,6 +664,19 @@
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
       <b/>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -620,7 +711,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -660,7 +751,19 @@
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -993,7 +1096,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="3">
-        <v>90.0</v>
+        <v>120.0</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
@@ -1031,7 +1134,7 @@
         <v>32</v>
       </c>
       <c r="F4" s="3">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -1069,7 +1172,7 @@
         <v>39</v>
       </c>
       <c r="F5" s="3">
-        <v>70.0</v>
+        <v>90.0</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>17</v>
@@ -1142,10 +1245,10 @@
         <v>50</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F7" s="3">
-        <v>60.0</v>
+        <v>120.0</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>17</v>
@@ -1160,62 +1263,62 @@
         <v>8.0</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H8" s="3">
         <v>8.0</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J8" s="1">
         <v>10.0</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="3">
-        <v>75.0</v>
+        <v>90.0</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
@@ -1224,53 +1327,53 @@
         <v>46242.0</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J9" s="1">
         <v>7.0</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="F10" s="3">
         <v>90.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H10" s="4">
         <v>46150.0</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J10" s="1">
         <v>6.0</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>21</v>
@@ -1279,7 +1382,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>39</v>
@@ -1290,31 +1393,31 @@
       <c r="G11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="4">
-        <v>46149.0</v>
+      <c r="H11" s="3">
+        <v>5.0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J11" s="1">
         <v>10.0</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>39</v>
@@ -1329,33 +1432,33 @@
         <v>46061.0</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J12" s="1">
         <v>12.0</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="F13" s="3">
-        <v>80.0</v>
+        <v>120.0</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
@@ -1364,18 +1467,18 @@
         <v>46090.0</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J13" s="1">
         <v>7.0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>21</v>
@@ -1384,13 +1487,13 @@
         <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="F14" s="3">
-        <v>90.0</v>
+        <v>80.0</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>17</v>
@@ -1399,18 +1502,18 @@
         <v>7.0</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J14" s="2">
         <v>6.0</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>21</v>
@@ -1419,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="F15" s="3">
-        <v>90.0</v>
+        <v>80.0</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>17</v>
@@ -1434,65 +1537,65 @@
         <v>46150.0</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J15" s="1">
         <v>10.0</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="F16" s="3">
         <v>120.0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H16" s="4">
         <v>46150.0</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="J16" s="1">
         <v>8.0</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="D17" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="10" t="s">
         <v>107</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>108</v>
       </c>
       <c r="F17" s="10">
         <v>120.0</v>
@@ -1504,13 +1607,217 @@
         <v>46243.0</v>
       </c>
       <c r="I17" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J17" s="2">
         <v>6.0</v>
       </c>
       <c r="K17" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
         <v>110</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="2">
+        <v>120.0</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="11">
+        <v>46243.0</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="J18" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="2">
+        <v>80.0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="14">
+        <v>46243.0</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="J19" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="2">
+        <v>75.0</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="14">
+        <v>46062.0</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="J20" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="2">
+        <v>75.0</v>
+      </c>
+      <c r="G21" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H21" s="14">
+        <v>46121.0</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="J21" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="14">
+        <v>46243.0</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="B38" s="14">
+        <v>46243.0</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1531,8 +1838,12 @@
     <hyperlink r:id="rId14" ref="I15"/>
     <hyperlink r:id="rId15" ref="I16"/>
     <hyperlink r:id="rId16" ref="I17"/>
+    <hyperlink r:id="rId17" ref="I18"/>
+    <hyperlink r:id="rId18" ref="I19"/>
+    <hyperlink r:id="rId19" ref="I20"/>
+    <hyperlink r:id="rId20" ref="I21"/>
   </hyperlinks>
-  <drawing r:id="rId17"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>
 
@@ -1552,67 +1863,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="13" t="s">
+      <c r="F1" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="I1" s="13" t="s">
+      <c r="H1" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="L1" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="M1" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="N1" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="P1" s="13" t="s">
+      <c r="J1" s="17" t="s">
+        <v>140</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="L1" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>143</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="O1" s="17" t="s">
+        <v>145</v>
+      </c>
+      <c r="P1" s="17" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
@@ -1627,17 +1938,17 @@
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="J2" s="14">
+        <v>149</v>
+      </c>
+      <c r="J2" s="18">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
         <v>11544.75</v>
       </c>
-      <c r="K2" s="15">
+      <c r="K2" s="19">
         <f t="shared" ref="K2:K11" si="2">RANK(J2, $J$2:$J$22)</f>
         <v>1</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="20">
         <v>46151.0</v>
       </c>
       <c r="M2" s="2">
@@ -1650,21 +1961,21 @@
         <v>9.0</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>124</v>
+        <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>125</v>
+        <v>152</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -1679,13 +1990,13 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="J3" s="15">
+        <v>154</v>
+      </c>
+      <c r="J3" s="19">
         <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="19">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -1702,12 +2013,12 @@
         <v>7.0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>
@@ -1719,7 +2030,7 @@
         <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="3">
         <v>75.0</v>
@@ -1731,31 +2042,31 @@
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="J4" s="1">
         <v>0.0</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="19">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -1767,13 +2078,13 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="J5" s="15">
+        <v>162</v>
+      </c>
+      <c r="J5" s="19">
         <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
         <v>9.25</v>
       </c>
-      <c r="K5" s="15">
+      <c r="K5" s="19">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
@@ -1790,24 +2101,24 @@
         <v>10.0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>136</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>140</v>
+        <v>167</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -1819,13 +2130,13 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="J6" s="15">
+        <v>168</v>
+      </c>
+      <c r="J6" s="19">
         <f t="shared" si="3"/>
         <v>8.75</v>
       </c>
-      <c r="K6" s="15">
+      <c r="K6" s="19">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
@@ -1842,21 +2153,21 @@
         <v>9.0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -1871,13 +2182,13 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J7" s="15">
+        <v>172</v>
+      </c>
+      <c r="J7" s="19">
         <f t="shared" si="3"/>
         <v>8.25</v>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="19">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
@@ -1894,24 +2205,24 @@
         <v>8.0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>149</v>
+        <v>176</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>150</v>
+        <v>114</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
@@ -1923,13 +2234,13 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="J8" s="15">
+        <v>177</v>
+      </c>
+      <c r="J8" s="19">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="K8" s="15">
+      <c r="K8" s="19">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -1946,21 +2257,21 @@
         <v>9.0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -1975,13 +2286,13 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="J9" s="15">
+        <v>183</v>
+      </c>
+      <c r="J9" s="19">
         <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
-      <c r="K9" s="15">
+      <c r="K9" s="19">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -1998,24 +2309,24 @@
         <v>8.0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>158</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
@@ -2027,13 +2338,13 @@
         <v>46149.0</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="J10" s="15">
+        <v>189</v>
+      </c>
+      <c r="J10" s="19">
         <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
-      <c r="K10" s="15">
+      <c r="K10" s="19">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -2052,19 +2363,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>164</v>
+        <v>190</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>167</v>
+        <v>193</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2076,13 +2387,13 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="J11" s="15">
+        <v>194</v>
+      </c>
+      <c r="J11" s="19">
         <f t="shared" si="3"/>
         <v>6.75</v>
       </c>
-      <c r="K11" s="15">
+      <c r="K11" s="19">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -2099,7 +2410,7 @@
         <v>6.0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="196">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Descripción</t>
   </si>
   <si>
-    <t>Enlace Web</t>
-  </si>
-  <si>
     <t>Willy el Tuerto</t>
   </si>
   <si>
@@ -71,7 +68,7 @@
     <t>https://willyeltuertoescaperoom.com/</t>
   </si>
   <si>
-    <t>Una aventura pirata de película donde te sumerges en la búsqueda del tesoro de uno de los piratas más famosos. Destaca por su escenografía espectacular que recuerda a atracciones temáticas de grandes parques.</t>
+    <t>Aclamado como una de las mejores aventuras piratas de España, destacando por una escenografía espectacular que parece sacada de un parque temático. Los usuarios elogian su inmersión total en la búsqueda del tesoro y una ambientación "de 10" que te hace sentir dentro de una película de los Goonies. Top Mundial Terpeca (varios años). Ganador de premios nacionales a Mejor Escenografía y Mejor Sala de Aventura.</t>
   </si>
   <si>
     <t>Cybercity 2049</t>
@@ -95,7 +92,7 @@
     <t>https://www.escapebarcelona.com/cybercity-2049.php</t>
   </si>
   <si>
-    <t>Experiencia de estilo Cyberpunk inspirada en clásicos como Blade Runner o Matrix. Te traslada a un mundo decadente y futurista donde la toma de decisiones y la inmersión son los pilares centrales.</t>
+    <t>Espectáculo visual de estilo Cyberpunk que te traslada a una ciudad futurista de 200m² inspirada en Blade Runner. Destaca por sus efectos especiales, puzzles tecnológicos de nueva generación y una toma de decisiones que afecta a la historia. Es una de las experiencias más ambiciosas y premiadas de Barcelona. Top 50 Mundial Terpeca. Ganador de múltiples premios nacionales a Mejor Sala, Mejor Escenografía y Mejor Experiencia.</t>
   </si>
   <si>
     <t>Exodus</t>
@@ -116,7 +113,7 @@
     <t>https://www.elementsescaperoom.com/exodus/</t>
   </si>
   <si>
-    <t>Una odisea de ciencia ficción post-apocalíptica en la que la humanidad debe abandonar la Tierra tras un virus global. Es muy valorada por su narrativa, el papel del Game Master y su ambientación "calma-tensa".</t>
+    <t>Una odisea de ciencia ficción post-apocalíptica muy valorada por su narrativa absorbente y el papel clave del Game Master. Destaca por una ambientación de "calma-tensa" y un diseño de producción que recrea perfectamente una nave de evacuación. Los jugadores elogian la fluidez de sus puzzles y su carga emocional. Nominado a Mejor Inmersión y Mejor Narrativa en ránkings nacionales de expertos.</t>
   </si>
   <si>
     <t>La Mina</t>
@@ -137,7 +134,7 @@
     <t>https://unrealroomescape.es/</t>
   </si>
   <si>
-    <t>Ambientada en la centenaria Mina de St. Louis, donde los jugadores deben investigar una extraña fuente de minerales tras una explosión. Es una sala clásica de aventura con una ambientación minera muy lograda.</t>
+    <t>Aclamada como una de las experiencias más auténticas y físicas de Cataluña, ambientada en una explotación minera hiperrealista. Destaca por su inicio impactante, el uso de materiales reales (roca, hierro) y una atmósfera de tensión constante sin llegar al terror. Es un referente absoluto del género de aventura. Top 100 Mundial Terpeca. Ganador de premios a Mejor Sala de España y Mejor Inmersión.</t>
   </si>
   <si>
     <t>Distrito 111</t>
@@ -152,22 +149,22 @@
     <t>https://escapeup.es/escape-room/unreal/barcelona/distrito-111/</t>
   </si>
   <si>
-    <t>Un thriller de supervivencia en un mundo al borde del colapso total. Con una atmósfera de cine y estética post-apocalíptica, los jugadores deben cumplir una misión crítica en un entorno hostil y caótico.</t>
+    <t>Un thriller de supervivencia con una estética post-apocalíptica brutal que te sumerge en un mundo al borde del colapso. Los usuarios destacan su atmósfera cinematográfica, la tensión constante y una misión crítica que mantiene la adrenalina al máximo. Es una de las joyas de Escape Barcelona por su escala y detalle. Ganador de premios a Mejor Escenografía y nominado a Mejor Experiencia de Juego.</t>
+  </si>
+  <si>
+    <t>Room Angie</t>
+  </si>
+  <si>
+    <t>Ilusium Room Escape</t>
+  </si>
+  <si>
+    <t>Thriller / misterio</t>
   </si>
   <si>
     <t>https://ilusiumroomescape.es/</t>
   </si>
   <si>
-    <t>Room Angie</t>
-  </si>
-  <si>
-    <t>Ilusium Room Escape</t>
-  </si>
-  <si>
-    <t>Thriller / misterio</t>
-  </si>
-  <si>
-    <t>Un misterio trepidante de 80 minutos donde el trabajo en equipo es vital. Los jugadores deben resolver enigmas y acertijos para completar una misión de la que solo podrán salir "gritando su nombre tres veces".</t>
+    <t>Un misterio trepidante de 80 minutos donde la tensión y el trabajo en equipo son los protagonistas. Destaca por una narrativa que te atrapa desde el inicio y un sistema de enigmas muy dinámico. Los jugadores elogian su final intenso y la capacidad de la sala para mantener el suspense hasta el último segundo.</t>
   </si>
   <si>
     <t>Enterprise</t>
@@ -191,7 +188,7 @@
     <t>https://www.abduction.es/badalona/abduction4.html</t>
   </si>
   <si>
-    <t>Una aventura tecnológica ambientada en una nave espacial. Destaca por requerir agilidad física y por integrar tecnología avanzada en sus puzzles, alejándose de los candados tradicionales para ofrecer una experiencia de adrenalina.</t>
+    <t>Aventura tecnológica de alta velocidad que rompe con los clásicos candados para ofrecer puzzles basados en mecanismos avanzados. Destaca por requerir cierta agilidad física y por su ambientación de nave espacial impecable. Es ideal para quienes buscan una experiencia de pura adrenalina y retos modernos.</t>
   </si>
   <si>
     <t>Awaken</t>
@@ -206,7 +203,7 @@
     <t>https://www.reddopamine.com/landing-aventura</t>
   </si>
   <si>
-    <t>Una experiencia inmersiva que mezcla fantasía y magia. Los jugadores se convierten en protagonistas de una "película" donde el ingenio es la clave para superar pruebas diseñadas para fomentar la adrenalina y el trabajo en equipo.</t>
+    <t>Experiencia inmersiva que mezcla magistralmente la fantasía y la magia, convirtiendo a los jugadores en protagonistas de su propia película. Destaca por un acting muy cuidado y pruebas diseñadas para fomentar la cooperación total. Los usuarios resaltan su capacidad de asombro y la belleza de sus escenarios. Ganador de premios a Mejor Acting y nominado a Mejor Sala de Fantasía.</t>
   </si>
   <si>
     <t>The Exam</t>
@@ -224,7 +221,7 @@
     <t>https://www.abduction.es/badalona/abduction3.html</t>
   </si>
   <si>
-    <t>Un test de acción y aventura que pone a prueba tanto la mente como la agilidad física (subir escaleras, trepar). Es un juego dinámico y divertido, diseñado para que los adultos vuelvan a sentirse como niños.</t>
+    <t>Un test de acción y aventura que pone a prueba tanto el ingenio como la condición física (subir, trepar y saltar). Es una sala sumamente divertida y dinámica que destaca por su originalidad y por hacer que los adultos vuelvan a sentirse como niños en un patio de recreo gigante.</t>
   </si>
   <si>
     <t>Jurassic Land</t>
@@ -272,7 +269,7 @@
     <t>https://vortexescape.com/reservar-ahora</t>
   </si>
   <si>
-    <t>Una aventura inmersiva única de 120 minutos (2 horas) donde los jugadores realizan un viaje al interior del cuerpo humano. Es extremadamente tecnológica, de gran formato y requiere calzado cómodo para moverse.</t>
+    <t>Una aventura inmersiva única de 120 minutos (2 horas) donde los jugadores realizan un viaje al interior del cuerpo humano. Es extremadamente tecnológica, de gran formato y requiere calzado cómodo para moverse. Suele aparecer en las listas de "Salas más innovadoras" por el cambio de concepto de juego</t>
   </si>
   <si>
     <t>Tomb Hunter : La Leyenda de Akasha Escape Room</t>
@@ -341,7 +338,7 @@
     <t>https://www.elementsescaperoom.com/katrina/</t>
   </si>
   <si>
-    <t>Una expedición arqueológica de gran formato (120 minutos) en busca del oro maldito de Moctezuma. Destaca por una ambientación selvática impresionante, dimensiones muy amplias y pruebas que requieren agilidad física. Es una experiencia de 'nueva generación' donde la escenografía y los mecanismos electrónicos sustituyen por completo a los candados tradicionales</t>
+    <t>Una expedición arqueológica de gran formato (120 minutos) en busca del oro maldito de Moctezuma. Destaca por una ambientación selvática impresionante, dimensiones muy amplias y pruebas que requieren agilidad física. Es una experiencia de 'nueva generación' donde la escenografía y los mecanismos electrónicos sustituyen por completo a los candados tradicionales. Una de las más premiadas en Cataluña por su escenografía (Premios Taty y otros ránkings de expertos).</t>
   </si>
   <si>
     <t>Outline</t>
@@ -362,64 +359,67 @@
     <t>https://outlineescaperoom.es/</t>
   </si>
   <si>
+    <t>Aclamado como una de las mejores experiencias de terror en España y posicionado en el Top Mundial por los premios Terpeca (Top Escape Rooms Project Enthusiasts' Choice Award). Destaca por su inmersión de 120 minutos, una ambientación industrial "de 10" y un acting intenso que a menudo divide al grupo. Los usuarios elogian sus puzles integrados, sustos constantes y una gran amplitud de salas que le han valido el reconocimiento como una de las salas más completas y premiadas del panorama actual.</t>
+  </si>
+  <si>
+    <t>Synergo</t>
+  </si>
+  <si>
+    <t>Synergo Escape</t>
+  </si>
+  <si>
+    <t>Tensión / Cazadores de Brujas</t>
+  </si>
+  <si>
+    <t>Tensión</t>
+  </si>
+  <si>
+    <t>https://synergoescaperoom.es/</t>
+  </si>
+  <si>
+    <t>Ganador de múltiples galardones en los Horror Awards y reconocido en los ránkings nacionales por su altísima calidad en puzles y una ambientación de fantasía oscura. Te sumerge en una caza de brujas implacable con una dificultad elevada que exige máxima cooperación. Su narrativa fluye a través de escenarios de bosque y cabaña hiperrealistas, consolidándose como un reto imprescindible que ha cosechado excelentes críticas por su diseño de producción y mecanismos originales.</t>
+  </si>
+  <si>
+    <t>El cetro de fuego</t>
+  </si>
+  <si>
+    <t>Aventura / Egipto</t>
+  </si>
+  <si>
+    <t>https://www.elementsescaperoom.com/el-cetro-de-fuego/</t>
+  </si>
+  <si>
+    <t>Una aventura de corte clásico inspirada en Egipto que ha sido premiada por su Escenografía y Ambientación en diversos certámenes nacionales. Con una duración de 75 minutos, ofrece una experiencia de exploración pura, ideal para familias, con pasadizos y cámaras secretas muy logrados. Los jugadores destacan su fluidez y la integración orgánica de los enigmas, lo que la mantiene siempre en los puestos altos de las recomendaciones de aventura de la ciudad.</t>
+  </si>
+  <si>
+    <t>Ouija</t>
+  </si>
+  <si>
+    <t>HorrorBox</t>
+  </si>
+  <si>
+    <t>Terror Paranormal</t>
+  </si>
+  <si>
+    <t>Media / Alta</t>
+  </si>
+  <si>
+    <t>https://www.horrorbox.es/producto/ouija-escape-room/</t>
+  </si>
+  <si>
+    <t>Creada por los maestros de HorrorBox, una de las empresas más galardonadas de España (premios a Mejor Experiencia, Mejor Acting y Trayectoria). Este referente del terror paranormal utiliza el espiritismo para crear una atmósfera opresiva de 60 minutos. Ha sido reconocida históricamente como una de las salas con mejor atmósfera de terror psicológico, destacando por sus efectos especiales y un acting inquietante que la sitúa como un clásico imbatible del género.</t>
+  </si>
+  <si>
+    <t>Escape Room</t>
+  </si>
+  <si>
+    <t>Tipo / Temática</t>
+  </si>
+  <si>
+    <t>Terror / Industrial</t>
+  </si>
+  <si>
     <t>Ubicado en una antigua fábrica abandonada. Es una experiencia muy inmersiva y física (120 min) que destaca por su acting y escenarios realistas.</t>
-  </si>
-  <si>
-    <t>Synergo</t>
-  </si>
-  <si>
-    <t>Synergo Escape</t>
-  </si>
-  <si>
-    <t>Tensión / Cazadores de Brujas</t>
-  </si>
-  <si>
-    <t>Tensión</t>
-  </si>
-  <si>
-    <t>https://synergoescaperoom.es/</t>
-  </si>
-  <si>
-    <t>Te conviertes en un cazador de brujas. Destaca por puzzles complejos y una ambientación de bosque y cabaña muy lograda.</t>
-  </si>
-  <si>
-    <t>El cetro de fuego</t>
-  </si>
-  <si>
-    <t>Aventura / Egipto</t>
-  </si>
-  <si>
-    <t>https://www.elementsescaperoom.com/el-cetro-de-fuego/</t>
-  </si>
-  <si>
-    <t>Expedición arqueológica clásica al estilo Indiana Jones. Ideal para familias, con pruebas orgánicas y efectos visuales de calidad.</t>
-  </si>
-  <si>
-    <t>Ouija</t>
-  </si>
-  <si>
-    <t>HorrorBox</t>
-  </si>
-  <si>
-    <t>Terror Paranormal</t>
-  </si>
-  <si>
-    <t>Media / Alta</t>
-  </si>
-  <si>
-    <t>https://www.horrorbox.es/producto/ouija-escape-room/</t>
-  </si>
-  <si>
-    <t>Centrado en el contacto con el más allá. Es un terror psicológico y ambiental muy intenso, con tecnología aplicada a los efectos. Es una sala de "vieja escuela" pero muy bien mantenida, ideal si buscáis una experiencia de terror puro y directo sin tanta parte física como Outline.</t>
-  </si>
-  <si>
-    <t>Escape Room</t>
-  </si>
-  <si>
-    <t>Tipo / Temática</t>
-  </si>
-  <si>
-    <t>Terror / Industrial</t>
   </si>
   <si>
     <t>Tensión / Fantasía</t>
@@ -609,7 +609,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d.m"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -622,6 +622,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -629,14 +635,14 @@
     <font>
       <u/>
       <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <i/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -711,15 +717,12 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -727,48 +730,54 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -993,14 +1002,17 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="39.88"/>
-    <col customWidth="1" min="2" max="2" width="21.75"/>
-    <col customWidth="1" min="3" max="3" width="19.0"/>
-    <col customWidth="1" min="4" max="4" width="25.0"/>
-    <col customWidth="1" min="8" max="8" width="11.5"/>
-    <col customWidth="1" min="9" max="9" width="61.38"/>
+    <col customWidth="1" min="2" max="2" width="7.63"/>
+    <col customWidth="1" min="3" max="3" width="7.25"/>
+    <col customWidth="1" min="4" max="4" width="8.63"/>
+    <col customWidth="1" min="6" max="6" width="6.13"/>
+    <col customWidth="1" min="7" max="7" width="7.0"/>
+    <col customWidth="1" min="8" max="8" width="8.75"/>
+    <col customWidth="1" min="9" max="9" width="21.0"/>
     <col customWidth="1" min="10" max="10" width="13.88"/>
-    <col customWidth="1" min="11" max="11" width="172.5"/>
-    <col customWidth="1" min="12" max="12" width="40.88"/>
+    <col customWidth="1" min="11" max="11" width="8.13"/>
+    <col customWidth="1" min="12" max="12" width="370.5"/>
+    <col customWidth="1" min="13" max="13" width="145.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1034,790 +1046,793 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="1"/>
+      <c r="L1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="2">
+        <v>80.0</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="3">
-        <v>80.0</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="3">
+        <v>46273.0</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="H2" s="4">
-        <v>46273.0</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="J2" s="1">
         <v>6.0</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="5" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="2">
+        <v>120.0</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="3">
-        <v>120.0</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="3">
+        <v>46090.0</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="H3" s="4">
-        <v>46090.0</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="J3" s="1">
         <v>6.0</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" s="2" t="s">
+      <c r="K3" s="7"/>
+      <c r="L3" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="3">
+        <v>46273.0</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="F4" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="4">
-        <v>46273.0</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="J4" s="1">
         <v>6.0</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="2" t="s">
+      <c r="K4" s="5"/>
+      <c r="L4" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3">
+        <v>46089.0</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="F5" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="4">
-        <v>46089.0</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="J5" s="1">
         <v>7.0</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="2" t="s">
+      <c r="K5" s="5"/>
+      <c r="L5" s="5" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="J6" s="1">
         <v>7.0</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>47</v>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="2">
+        <v>120.0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="3">
-        <v>120.0</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>47</v>
       </c>
       <c r="J7" s="1">
         <v>8.0</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>51</v>
+      <c r="K7" s="5"/>
+      <c r="L7" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F8" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H8" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="J8" s="1">
         <v>10.0</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>59</v>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="3">
+        <v>46242.0</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" s="4">
-        <v>46242.0</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="J9" s="1">
         <v>7.0</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>64</v>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="3">
+        <v>46150.0</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="F10" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="4">
-        <v>46150.0</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="J10" s="1">
         <v>6.0</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K10" s="5"/>
+      <c r="L10" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="3">
-        <v>60.0</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="J11" s="1">
         <v>10.0</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>74</v>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="2">
+        <v>75.0</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="3">
+        <v>46061.0</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="3">
-        <v>75.0</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="4">
-        <v>46061.0</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="J12" s="1">
         <v>12.0</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>79</v>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="2">
+        <v>120.0</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="3">
+        <v>46090.0</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="F13" s="3">
-        <v>120.0</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="4">
-        <v>46090.0</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>85</v>
       </c>
       <c r="J13" s="1">
         <v>7.0</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="K13" s="1"/>
+      <c r="L13" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="F14" s="2">
+        <v>80.0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="3">
-        <v>80.0</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="I14" s="6" t="s">
+      <c r="J14" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="J14" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="F15" s="2">
+        <v>80.0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="3">
+        <v>46150.0</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="F15" s="3">
-        <v>80.0</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="4">
-        <v>46150.0</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="J15" s="1">
         <v>10.0</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>96</v>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="2">
+        <v>120.0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="3">
+        <v>46150.0</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="F16" s="3">
-        <v>120.0</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="4">
-        <v>46150.0</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="J16" s="1">
         <v>8.0</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="s">
+      <c r="B17" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="F17" s="11">
+        <v>120.0</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="12">
+        <v>46243.0</v>
+      </c>
+      <c r="I17" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="10">
+      <c r="J17" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="5">
         <v>120.0</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="11">
+      <c r="G18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="12">
         <v>46243.0</v>
       </c>
-      <c r="I17" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="J17" s="2">
+      <c r="I18" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="5">
         <v>6.0</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="5">
+        <v>80.0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19" s="15">
+        <v>46243.0</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="5">
+        <v>75.0</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="15">
+        <v>46062.0</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="J20" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="5">
+        <v>75.0</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H21" s="15">
+        <v>46121.0</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="J21" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F18" s="2">
-        <v>120.0</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="11">
+      <c r="B37" s="15">
         <v>46243.0</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="J18" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="K18" s="2" t="s">
+      <c r="C37" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F19" s="2">
-        <v>80.0</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H19" s="14">
+      <c r="B38" s="15">
         <v>46243.0</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="J19" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="K19" s="15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
+      <c r="C38" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="2">
-        <v>75.0</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="14">
-        <v>46062.0</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="J20" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="K20" s="15" t="s">
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="D40" s="16" t="s">
         <v>128</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="F21" s="2">
-        <v>75.0</v>
-      </c>
-      <c r="G21" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="H21" s="14">
-        <v>46121.0</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="J21" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B37" s="14">
-        <v>46243.0</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="14">
-        <v>46243.0</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1863,52 +1878,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="P1" s="18" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1920,47 +1935,47 @@
         <v>147</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>148</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="3">
+        <v>38</v>
+      </c>
+      <c r="F2" s="2">
         <v>70.0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="3">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2">
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="J2" s="18">
+      <c r="J2" s="19">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
         <v>11544.75</v>
       </c>
-      <c r="K2" s="19">
+      <c r="K2" s="20">
         <f t="shared" ref="K2:K11" si="2">RANK(J2, $J$2:$J$22)</f>
         <v>1</v>
       </c>
-      <c r="L2" s="20">
+      <c r="L2" s="21">
         <v>46151.0</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="5">
         <v>10.0</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="5">
         <v>9.0</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="5">
         <v>9.0</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="5" t="s">
         <v>150</v>
       </c>
     </row>
@@ -1972,47 +1987,47 @@
         <v>152</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>153</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="3">
+        <v>38</v>
+      </c>
+      <c r="F3" s="2">
         <v>60.0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="4">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3">
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="20">
         <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="20">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="5">
         <v>9.0</v>
       </c>
-      <c r="M3" s="2">
+      <c r="M3" s="5">
         <v>9.0</v>
       </c>
-      <c r="N3" s="2">
+      <c r="N3" s="5">
         <v>9.0</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="5">
         <v>7.0</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="5" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2021,24 +2036,24 @@
         <v>156</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F4" s="3">
+        <v>55</v>
+      </c>
+      <c r="F4" s="2">
         <v>75.0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4" s="3">
+        <v>24</v>
+      </c>
+      <c r="H4" s="2">
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -2047,7 +2062,7 @@
       <c r="J4" s="1">
         <v>0.0</v>
       </c>
-      <c r="K4" s="19">
+      <c r="K4" s="20">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
@@ -2060,7 +2075,7 @@
         <v>159</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>160</v>
@@ -2068,39 +2083,39 @@
       <c r="E5" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>60.0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="3">
+        <v>16</v>
+      </c>
+      <c r="H5" s="2">
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="J5" s="19">
+      <c r="J5" s="20">
         <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
         <v>9.25</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="20">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="5">
         <v>9.0</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="5">
         <v>10.0</v>
       </c>
-      <c r="N5" s="2">
+      <c r="N5" s="5">
         <v>8.0</v>
       </c>
-      <c r="O5" s="2">
+      <c r="O5" s="5">
         <v>10.0</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="P5" s="5" t="s">
         <v>163</v>
       </c>
     </row>
@@ -2112,7 +2127,7 @@
         <v>165</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>166</v>
@@ -2120,39 +2135,39 @@
       <c r="E6" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>90.0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="3">
+        <v>16</v>
+      </c>
+      <c r="H6" s="2">
         <v>9.0</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="20">
         <f t="shared" si="3"/>
         <v>8.75</v>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="20">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="5">
         <v>9.0</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="5">
         <v>8.0</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="5">
         <v>9.0</v>
       </c>
-      <c r="O6" s="2">
+      <c r="O6" s="5">
         <v>9.0</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="P6" s="5" t="s">
         <v>169</v>
       </c>
     </row>
@@ -2164,47 +2179,47 @@
         <v>159</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>171</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="3">
+        <v>38</v>
+      </c>
+      <c r="F7" s="2">
         <v>90.0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="4">
+        <v>16</v>
+      </c>
+      <c r="H7" s="3">
         <v>46149.0</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="20">
         <f t="shared" si="3"/>
         <v>8.25</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="20">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="5">
         <v>8.0</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="5">
         <v>9.0</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="5">
         <v>8.0</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="5">
         <v>8.0</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P7" s="5" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2216,47 +2231,47 @@
         <v>175</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>176</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F8" s="3">
+        <v>113</v>
+      </c>
+      <c r="F8" s="2">
         <v>90.0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="4">
+        <v>16</v>
+      </c>
+      <c r="H8" s="3">
         <v>46150.0</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="J8" s="19">
+      <c r="J8" s="20">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="K8" s="19">
+      <c r="K8" s="20">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="5">
         <v>8.0</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="5">
         <v>8.0</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="5">
         <v>7.0</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" s="5">
         <v>9.0</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="P8" s="5" t="s">
         <v>178</v>
       </c>
     </row>
@@ -2274,41 +2289,41 @@
         <v>182</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3">
+        <v>38</v>
+      </c>
+      <c r="F9" s="2">
         <v>80.0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="4">
+        <v>16</v>
+      </c>
+      <c r="H9" s="3">
         <v>46149.0</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="20">
         <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="20">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="5">
         <v>8.0</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="5">
         <v>9.0</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="5">
         <v>9.0</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O9" s="5">
         <v>8.0</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="P9" s="5" t="s">
         <v>184</v>
       </c>
     </row>
@@ -2320,7 +2335,7 @@
         <v>186</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>187</v>
@@ -2328,36 +2343,36 @@
       <c r="E10" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>70.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="4">
+        <v>24</v>
+      </c>
+      <c r="H10" s="3">
         <v>46149.0</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="20">
         <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="20">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="L10" s="2">
+      <c r="L10" s="5">
         <v>7.0</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="5">
         <v>8.0</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="5">
         <v>7.0</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="5">
         <v>8.0</v>
       </c>
     </row>
@@ -2369,7 +2384,7 @@
         <v>191</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>192</v>
@@ -2377,39 +2392,39 @@
       <c r="E11" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>60.0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="4">
+        <v>16</v>
+      </c>
+      <c r="H11" s="3">
         <v>46148.0</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="20">
         <f t="shared" si="3"/>
         <v>6.75</v>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L11" s="5">
         <v>7.0</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11" s="5">
         <v>7.0</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="5">
         <v>7.0</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="5">
         <v>6.0</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="P11" s="5" t="s">
         <v>195</v>
       </c>
     </row>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="197">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>Max_personas</t>
+  </si>
+  <si>
+    <t>Posición TERPECA</t>
   </si>
   <si>
     <t>Descripción</t>
@@ -622,15 +625,15 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11.0"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -724,17 +727,17 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -775,9 +778,9 @@
     <xf borderId="1" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -1010,7 +1013,7 @@
     <col customWidth="1" min="8" max="8" width="8.75"/>
     <col customWidth="1" min="9" max="9" width="21.0"/>
     <col customWidth="1" min="10" max="10" width="13.88"/>
-    <col customWidth="1" min="11" max="11" width="8.13"/>
+    <col customWidth="1" min="11" max="11" width="9.0"/>
     <col customWidth="1" min="12" max="12" width="370.5"/>
     <col customWidth="1" min="13" max="13" width="145.25"/>
   </cols>
@@ -1046,734 +1049,748 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1"/>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="2">
+        <v>16</v>
+      </c>
+      <c r="F2" s="3">
         <v>80.0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="3">
+        <v>17</v>
+      </c>
+      <c r="H2" s="4">
         <v>46273.0</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>17</v>
+      <c r="I2" s="5" t="s">
+        <v>18</v>
       </c>
       <c r="J2" s="1">
         <v>6.0</v>
       </c>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
-        <v>18</v>
+      <c r="K2" s="2">
+        <v>71.0</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3">
         <v>120.0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="3">
+        <v>25</v>
+      </c>
+      <c r="H3" s="4">
         <v>46090.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="1">
         <v>6.0</v>
       </c>
-      <c r="K3" s="7"/>
+      <c r="K3" s="7">
+        <v>55.0</v>
+      </c>
       <c r="L3" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F4" s="2">
+        <v>32</v>
+      </c>
+      <c r="F4" s="3">
         <v>90.0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3">
+        <v>25</v>
+      </c>
+      <c r="H4" s="4">
         <v>46273.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J4" s="1">
         <v>6.0</v>
       </c>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5" t="s">
-        <v>33</v>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="2">
+        <v>39</v>
+      </c>
+      <c r="F5" s="3">
         <v>90.0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="3">
+        <v>17</v>
+      </c>
+      <c r="H5" s="4">
         <v>46089.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J5" s="1">
         <v>7.0</v>
       </c>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5" t="s">
-        <v>40</v>
+      <c r="K5" s="2">
+        <v>78.0</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="2">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3">
         <v>90.0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>44</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="J6" s="1">
         <v>7.0</v>
       </c>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5" t="s">
-        <v>45</v>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="2">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3">
         <v>120.0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="2">
+        <v>17</v>
+      </c>
+      <c r="H7" s="3">
         <v>7.0</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J7" s="1">
         <v>8.0</v>
       </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5" t="s">
-        <v>50</v>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="2">
+        <v>56</v>
+      </c>
+      <c r="F8" s="3">
         <v>90.0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="2">
+        <v>57</v>
+      </c>
+      <c r="H8" s="3">
         <v>8.0</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J8" s="1">
         <v>10.0</v>
       </c>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5" t="s">
-        <v>58</v>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="2">
+        <v>16</v>
+      </c>
+      <c r="F9" s="3">
         <v>90.0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="3">
+        <v>25</v>
+      </c>
+      <c r="H9" s="4">
         <v>46242.0</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J9" s="1">
         <v>7.0</v>
       </c>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5" t="s">
-        <v>63</v>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="2">
+        <v>68</v>
+      </c>
+      <c r="F10" s="3">
         <v>90.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="3">
+        <v>57</v>
+      </c>
+      <c r="H10" s="4">
         <v>46150.0</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J10" s="1">
         <v>6.0</v>
       </c>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5" t="s">
-        <v>69</v>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="2">
+        <v>39</v>
+      </c>
+      <c r="F11" s="3">
         <v>60.0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="2">
+        <v>17</v>
+      </c>
+      <c r="H11" s="3">
         <v>5.0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J11" s="1">
         <v>10.0</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="2">
+        <v>39</v>
+      </c>
+      <c r="F12" s="3">
         <v>75.0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="3">
+        <v>17</v>
+      </c>
+      <c r="H12" s="4">
         <v>46061.0</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J12" s="1">
         <v>12.0</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="2">
+        <v>84</v>
+      </c>
+      <c r="F13" s="3">
         <v>120.0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="3">
+        <v>25</v>
+      </c>
+      <c r="H13" s="4">
         <v>46090.0</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" s="1">
         <v>7.0</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>86</v>
+      <c r="A14" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F14" s="2">
+        <v>89</v>
+      </c>
+      <c r="F14" s="3">
         <v>80.0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H14" s="2">
+        <v>17</v>
+      </c>
+      <c r="H14" s="3">
         <v>7.0</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J14" s="5">
+        <v>90</v>
+      </c>
+      <c r="J14" s="2">
         <v>6.0</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="2">
+        <v>94</v>
+      </c>
+      <c r="F15" s="3">
         <v>80.0</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="3">
+        <v>17</v>
+      </c>
+      <c r="H15" s="4">
         <v>46150.0</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J15" s="1">
         <v>10.0</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="2">
+        <v>100</v>
+      </c>
+      <c r="F16" s="3">
         <v>120.0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" s="3">
+        <v>57</v>
+      </c>
+      <c r="H16" s="4">
         <v>46150.0</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J16" s="1">
         <v>8.0</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F17" s="11">
         <v>120.0</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" s="12">
         <v>46243.0</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="J17" s="5">
+        <v>108</v>
+      </c>
+      <c r="J17" s="2">
         <v>6.0</v>
       </c>
-      <c r="K17" s="1"/>
+      <c r="K17" s="1">
+        <v>19.0</v>
+      </c>
       <c r="L17" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="D18" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F18" s="5">
+      <c r="E18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="2">
         <v>120.0</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H18" s="12">
         <v>46243.0</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="5">
+        <v>115</v>
+      </c>
+      <c r="J18" s="2">
         <v>6.0</v>
       </c>
-      <c r="K18" s="1"/>
+      <c r="K18" s="2">
+        <v>10.0</v>
+      </c>
       <c r="L18" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="5" t="s">
+      <c r="A19" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="B19" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="C19" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F19" s="5">
+      <c r="E19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19" s="2">
         <v>80.0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H19" s="15">
         <v>46243.0</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="J19" s="5">
+        <v>121</v>
+      </c>
+      <c r="J19" s="2">
         <v>7.0</v>
       </c>
-      <c r="K19" s="1"/>
+      <c r="K19" s="1">
+        <v>113.0</v>
+      </c>
       <c r="L19" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>29</v>
+      <c r="A20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="5">
+        <v>39</v>
+      </c>
+      <c r="F20" s="2">
         <v>75.0</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
         <v>46062.0</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="J20" s="5">
+        <v>125</v>
+      </c>
+      <c r="J20" s="2">
         <v>6.0</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="A21" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>29</v>
+      <c r="B21" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="5">
+        <v>129</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="2">
         <v>75.0</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H21" s="15">
         <v>46121.0</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="J21" s="5">
+        <v>131</v>
+      </c>
+      <c r="J21" s="2">
         <v>6.0</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" s="16" t="s">
         <v>7</v>
@@ -1782,57 +1799,57 @@
         <v>6</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="15">
         <v>46243.0</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B38" s="15">
         <v>46243.0</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -1894,66 +1911,66 @@
         <v>4</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L1" s="18" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M1" s="18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N1" s="18" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O1" s="18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P1" s="18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F2" s="2">
+        <v>39</v>
+      </c>
+      <c r="F2" s="3">
         <v>70.0</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="2">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3">
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J2" s="19">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
@@ -1966,46 +1983,46 @@
       <c r="L2" s="21">
         <v>46151.0</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="2">
         <v>10.0</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="2">
         <v>9.0</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="2">
         <v>9.0</v>
       </c>
-      <c r="P2" s="5" t="s">
-        <v>150</v>
+      <c r="P2" s="2" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="2">
+        <v>39</v>
+      </c>
+      <c r="F3" s="3">
         <v>60.0</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="3">
+        <v>17</v>
+      </c>
+      <c r="H3" s="4">
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J3" s="20">
         <f t="shared" si="1"/>
@@ -2015,49 +2032,49 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="2">
         <v>9.0</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="2">
         <v>9.0</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="2">
         <v>9.0</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="2">
         <v>7.0</v>
       </c>
-      <c r="P3" s="5" t="s">
-        <v>155</v>
+      <c r="P3" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F4" s="2">
+        <v>56</v>
+      </c>
+      <c r="F4" s="3">
         <v>75.0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="2">
+        <v>25</v>
+      </c>
+      <c r="H4" s="3">
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J4" s="1">
         <v>0.0</v>
@@ -2069,31 +2086,31 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="F5" s="2">
+        <v>162</v>
+      </c>
+      <c r="F5" s="3">
         <v>60.0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="2">
+        <v>17</v>
+      </c>
+      <c r="H5" s="3">
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J5" s="20">
         <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
@@ -2103,49 +2120,49 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="2">
         <v>9.0</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="2">
         <v>10.0</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" s="2">
         <v>8.0</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="2">
         <v>10.0</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>163</v>
+      <c r="P5" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="F6" s="2">
+        <v>168</v>
+      </c>
+      <c r="F6" s="3">
         <v>90.0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="2">
+        <v>17</v>
+      </c>
+      <c r="H6" s="3">
         <v>9.0</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J6" s="20">
         <f t="shared" si="3"/>
@@ -2155,49 +2172,49 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="2">
         <v>9.0</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="2">
         <v>8.0</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="2">
         <v>9.0</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="2">
         <v>9.0</v>
       </c>
-      <c r="P6" s="5" t="s">
-        <v>169</v>
+      <c r="P6" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="2">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3">
         <v>90.0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="3">
+        <v>17</v>
+      </c>
+      <c r="H7" s="4">
         <v>46149.0</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J7" s="20">
         <f t="shared" si="3"/>
@@ -2207,49 +2224,49 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="2">
         <v>8.0</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="2">
         <v>9.0</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="2">
         <v>8.0</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="2">
         <v>8.0</v>
       </c>
-      <c r="P7" s="5" t="s">
-        <v>173</v>
+      <c r="P7" s="2" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F8" s="2">
+        <v>114</v>
+      </c>
+      <c r="F8" s="3">
         <v>90.0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="3">
+        <v>17</v>
+      </c>
+      <c r="H8" s="4">
         <v>46150.0</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J8" s="20">
         <f t="shared" si="3"/>
@@ -2259,49 +2276,49 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="2">
         <v>8.0</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="2">
         <v>8.0</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="2">
         <v>7.0</v>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="2">
         <v>9.0</v>
       </c>
-      <c r="P8" s="5" t="s">
-        <v>178</v>
+      <c r="P8" s="2" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="2">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3">
         <v>80.0</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="3">
+        <v>17</v>
+      </c>
+      <c r="H9" s="4">
         <v>46149.0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J9" s="20">
         <f t="shared" si="3"/>
@@ -2311,49 +2328,49 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="2">
         <v>8.0</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="2">
         <v>9.0</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="2">
         <v>9.0</v>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="2">
         <v>8.0</v>
       </c>
-      <c r="P9" s="5" t="s">
-        <v>184</v>
+      <c r="P9" s="2" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F10" s="2">
+        <v>189</v>
+      </c>
+      <c r="F10" s="3">
         <v>70.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="3">
+        <v>25</v>
+      </c>
+      <c r="H10" s="4">
         <v>46149.0</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J10" s="20">
         <f t="shared" si="3"/>
@@ -2363,46 +2380,46 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="2">
         <v>7.0</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="2">
         <v>8.0</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="2">
         <v>7.0</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="2">
         <v>8.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="F11" s="2">
+        <v>194</v>
+      </c>
+      <c r="F11" s="3">
         <v>60.0</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" s="3">
+        <v>17</v>
+      </c>
+      <c r="H11" s="4">
         <v>46148.0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J11" s="20">
         <f t="shared" si="3"/>
@@ -2412,20 +2429,20 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="2">
         <v>7.0</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="2">
         <v>7.0</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="2">
         <v>7.0</v>
       </c>
-      <c r="O11" s="5">
+      <c r="O11" s="2">
         <v>6.0</v>
       </c>
-      <c r="P11" s="5" t="s">
-        <v>195</v>
+      <c r="P11" s="2" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="191">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -411,24 +411,6 @@
   </si>
   <si>
     <t>Creada por los maestros de HorrorBox, una de las empresas más galardonadas de España (premios a Mejor Experiencia, Mejor Acting y Trayectoria). Este referente del terror paranormal utiliza el espiritismo para crear una atmósfera opresiva de 60 minutos. Ha sido reconocida históricamente como una de las salas con mejor atmósfera de terror psicológico, destacando por sus efectos especiales y un acting inquietante que la sitúa como un clásico imbatible del género.</t>
-  </si>
-  <si>
-    <t>Escape Room</t>
-  </si>
-  <si>
-    <t>Tipo / Temática</t>
-  </si>
-  <si>
-    <t>Terror / Industrial</t>
-  </si>
-  <si>
-    <t>Ubicado en una antigua fábrica abandonada. Es una experiencia muy inmersiva y física (120 min) que destaca por su acting y escenarios realistas.</t>
-  </si>
-  <si>
-    <t>Tensión / Fantasía</t>
-  </si>
-  <si>
-    <t>El Cetro de Fuego</t>
   </si>
   <si>
     <t>Duración (min)</t>
@@ -1789,68 +1771,32 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="s">
-        <v>133</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>11</v>
-      </c>
+      <c r="A36" s="16"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="B37" s="15">
-        <v>46243.0</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>136</v>
-      </c>
+      <c r="A37" s="17"/>
+      <c r="B37" s="15"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="15">
-        <v>46243.0</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>137</v>
-      </c>
+      <c r="A38" s="17"/>
+      <c r="B38" s="15"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>124</v>
-      </c>
+      <c r="A39" s="17"/>
+      <c r="D39" s="16"/>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>129</v>
-      </c>
+      <c r="A40" s="17"/>
+      <c r="D40" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1911,34 +1857,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="18" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="18" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="18" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K1" s="18" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="L1" s="18" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="M1" s="18" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="N1" s="18" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="O1" s="18" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="P1" s="18" t="s">
         <v>11</v>
@@ -1946,16 +1892,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
@@ -1970,7 +1916,7 @@
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="J2" s="19">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
@@ -1993,21 +1939,21 @@
         <v>9.0</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -2022,7 +1968,7 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J3" s="20">
         <f t="shared" si="1"/>
@@ -2045,12 +1991,12 @@
         <v>7.0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>
@@ -2074,7 +2020,7 @@
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J4" s="1">
         <v>0.0</v>
@@ -2086,19 +2032,19 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -2110,7 +2056,7 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J5" s="20">
         <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
@@ -2133,24 +2079,24 @@
         <v>10.0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -2162,7 +2108,7 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="J6" s="20">
         <f t="shared" si="3"/>
@@ -2185,21 +2131,21 @@
         <v>9.0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -2214,7 +2160,7 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="J7" s="20">
         <f t="shared" si="3"/>
@@ -2237,21 +2183,21 @@
         <v>8.0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>114</v>
@@ -2266,7 +2212,7 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="J8" s="20">
         <f t="shared" si="3"/>
@@ -2289,21 +2235,21 @@
         <v>9.0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -2318,7 +2264,7 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="J9" s="20">
         <f t="shared" si="3"/>
@@ -2341,24 +2287,24 @@
         <v>8.0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
@@ -2370,7 +2316,7 @@
         <v>46149.0</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="J10" s="20">
         <f t="shared" si="3"/>
@@ -2395,19 +2341,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2419,7 +2365,7 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J11" s="20">
         <f t="shared" si="3"/>
@@ -2442,7 +2388,7 @@
         <v>6.0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="194">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -146,9 +146,6 @@
     <t>Espionaje / conspiración</t>
   </si>
   <si>
-    <t>9.0</t>
-  </si>
-  <si>
     <t>https://escapeup.es/escape-room/unreal/barcelona/distrito-111/</t>
   </si>
   <si>
@@ -413,6 +410,24 @@
     <t>Creada por los maestros de HorrorBox, una de las empresas más galardonadas de España (premios a Mejor Experiencia, Mejor Acting y Trayectoria). Este referente del terror paranormal utiliza el espiritismo para crear una atmósfera opresiva de 60 minutos. Ha sido reconocida históricamente como una de las salas con mejor atmósfera de terror psicológico, destacando por sus efectos especiales y un acting inquietante que la sitúa como un clásico imbatible del género.</t>
   </si>
   <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t>Kadabra</t>
+  </si>
+  <si>
+    <t>Mataró</t>
+  </si>
+  <si>
+    <t>Misterio</t>
+  </si>
+  <si>
+    <t>https://www.kadabraescape.com/reserva-2/</t>
+  </si>
+  <si>
+    <t>Un maníaco un tanto peculiar se ha fugado y tiene un descerebrado plan para acabar con todo Gotham, ¿seréis capaces de encontrar su guarida a tiempo y ponerle fin a esta locura? Se requiere un mínimo de habilidad física, no saltaréis por ningún lado pero sí os deberéis en algún momento agachar durante el recorrido del juego. No es un juego de terror, el sonido o la ambientación podrán confundir pero remarcamos para todos aquellos que tengáis alguna duda: No es de terror, podrá jugar todo el público.</t>
+  </si>
+  <si>
     <t>Duración (min)</t>
   </si>
   <si>
@@ -537,12 +552,6 @@
   </si>
   <si>
     <t>Jaipur</t>
-  </si>
-  <si>
-    <t>Kadabra</t>
-  </si>
-  <si>
-    <t>Mataró</t>
   </si>
   <si>
     <t>Bollywood / India</t>
@@ -594,7 +603,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d.m"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -668,6 +677,10 @@
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
       <b/>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -702,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -754,17 +767,20 @@
     <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -987,7 +1003,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="39.88"/>
-    <col customWidth="1" min="2" max="2" width="7.63"/>
+    <col customWidth="1" min="2" max="2" width="14.0"/>
     <col customWidth="1" min="3" max="3" width="7.25"/>
     <col customWidth="1" min="4" max="4" width="8.63"/>
     <col customWidth="1" min="6" max="6" width="6.13"/>
@@ -1061,7 +1077,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="4">
-        <v>46273.0</v>
+        <v>46062.0</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>18</v>
@@ -1173,7 +1189,7 @@
         <v>17</v>
       </c>
       <c r="H5" s="4">
-        <v>46089.0</v>
+        <v>46211.0</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>40</v>
@@ -1210,32 +1226,32 @@
       <c r="G6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="4">
+        <v>46150.0</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="J6" s="1">
         <v>7.0</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -1246,68 +1262,68 @@
       <c r="G7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="3">
-        <v>7.0</v>
+      <c r="H7" s="4">
+        <v>46241.0</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J7" s="1">
         <v>8.0</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="4">
+        <v>46149.0</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H8" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="J8" s="1">
         <v>10.0</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -1319,58 +1335,58 @@
         <v>25</v>
       </c>
       <c r="H9" s="4">
-        <v>46242.0</v>
+        <v>46061.0</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J9" s="1">
         <v>7.0</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="F10" s="3">
         <v>90.0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" s="4">
-        <v>46150.0</v>
+        <v>46030.0</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J10" s="1">
         <v>6.0</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>21</v>
@@ -1379,7 +1395,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>39</v>
@@ -1391,31 +1407,31 @@
         <v>17</v>
       </c>
       <c r="H11" s="3">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J11" s="1">
         <v>10.0</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>39</v>
@@ -1430,31 +1446,31 @@
         <v>46061.0</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J12" s="1">
         <v>12.0</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="F13" s="3">
         <v>120.0</v>
@@ -1466,19 +1482,19 @@
         <v>46090.0</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J13" s="1">
         <v>7.0</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>21</v>
@@ -1487,10 +1503,10 @@
         <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="F14" s="3">
         <v>80.0</v>
@@ -1502,19 +1518,19 @@
         <v>7.0</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J14" s="2">
         <v>6.0</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>21</v>
@@ -1523,10 +1539,10 @@
         <v>22</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="F15" s="3">
         <v>80.0</v>
@@ -1538,67 +1554,67 @@
         <v>46150.0</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J15" s="1">
         <v>10.0</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="F16" s="3">
         <v>120.0</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H16" s="4">
         <v>46150.0</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J16" s="1">
         <v>8.0</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="C17" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>107</v>
       </c>
       <c r="F17" s="11">
         <v>120.0</v>
@@ -1607,10 +1623,10 @@
         <v>25</v>
       </c>
       <c r="H17" s="12">
-        <v>46243.0</v>
+        <v>46212.0</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J17" s="2">
         <v>6.0</v>
@@ -1619,24 +1635,24 @@
         <v>19.0</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="F18" s="2">
         <v>120.0</v>
@@ -1648,7 +1664,7 @@
         <v>46243.0</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J18" s="2">
         <v>6.0</v>
@@ -1657,36 +1673,36 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="F19" s="2">
         <v>80.0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H19" s="15">
-        <v>46243.0</v>
+        <v>46182.0</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J19" s="2">
         <v>7.0</v>
@@ -1695,21 +1711,21 @@
         <v>113.0</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>39</v>
@@ -1724,50 +1740,88 @@
         <v>46062.0</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J20" s="2">
         <v>6.0</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F21" s="2">
         <v>75.0</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H21" s="15">
         <v>46121.0</v>
       </c>
       <c r="I21" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J21" s="2">
         <v>6.0</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="s">
         <v>132</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="2">
+        <v>80.0</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="17">
+        <v>46212.0</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="J22" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>95.0</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="36">
@@ -1778,24 +1832,24 @@
       <c r="E36" s="16"/>
     </row>
     <row r="37">
-      <c r="A37" s="17"/>
+      <c r="A37" s="19"/>
       <c r="B37" s="15"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
     </row>
     <row r="38">
-      <c r="A38" s="17"/>
+      <c r="A38" s="19"/>
       <c r="B38" s="15"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
     </row>
     <row r="39">
-      <c r="A39" s="17"/>
+      <c r="A39" s="19"/>
       <c r="D39" s="16"/>
     </row>
     <row r="40">
-      <c r="A40" s="17"/>
+      <c r="A40" s="19"/>
       <c r="D40" s="16"/>
     </row>
   </sheetData>
@@ -1820,8 +1874,9 @@
     <hyperlink r:id="rId18" ref="I19"/>
     <hyperlink r:id="rId19" ref="I20"/>
     <hyperlink r:id="rId20" ref="I21"/>
+    <hyperlink r:id="rId21" ref="I22"/>
   </hyperlinks>
-  <drawing r:id="rId21"/>
+  <drawing r:id="rId22"/>
 </worksheet>
 </file>
 
@@ -1841,67 +1896,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
-        <v>133</v>
-      </c>
-      <c r="G1" s="18" t="s">
+      <c r="F1" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="I1" s="18" t="s">
+      <c r="H1" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="K1" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="L1" s="18" t="s">
-        <v>137</v>
-      </c>
-      <c r="M1" s="18" t="s">
-        <v>138</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="O1" s="18" t="s">
+      <c r="J1" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="P1" s="18" t="s">
+      <c r="K1" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="P1" s="20" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
@@ -1916,17 +1971,17 @@
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="J2" s="19">
+        <v>149</v>
+      </c>
+      <c r="J2" s="21">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
         <v>11544.75</v>
       </c>
-      <c r="K2" s="20">
+      <c r="K2" s="22">
         <f t="shared" ref="K2:K11" si="2">RANK(J2, $J$2:$J$22)</f>
         <v>1</v>
       </c>
-      <c r="L2" s="21">
+      <c r="L2" s="17">
         <v>46151.0</v>
       </c>
       <c r="M2" s="2">
@@ -1939,21 +1994,21 @@
         <v>9.0</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -1968,13 +2023,13 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="J3" s="20">
+        <v>154</v>
+      </c>
+      <c r="J3" s="22">
         <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="22">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -1991,12 +2046,12 @@
         <v>7.0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>
@@ -2008,7 +2063,7 @@
         <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="3">
         <v>75.0</v>
@@ -2020,31 +2075,31 @@
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J4" s="1">
         <v>0.0</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="22">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -2056,13 +2111,13 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="J5" s="20">
+        <v>162</v>
+      </c>
+      <c r="J5" s="22">
         <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
         <v>9.25</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="22">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
@@ -2079,24 +2134,24 @@
         <v>10.0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -2108,13 +2163,13 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="J6" s="20">
+        <v>168</v>
+      </c>
+      <c r="J6" s="22">
         <f t="shared" si="3"/>
         <v>8.75</v>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="22">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
@@ -2131,21 +2186,21 @@
         <v>9.0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -2160,13 +2215,13 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="J7" s="20">
+        <v>172</v>
+      </c>
+      <c r="J7" s="22">
         <f t="shared" si="3"/>
         <v>8.25</v>
       </c>
-      <c r="K7" s="20">
+      <c r="K7" s="22">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
@@ -2183,24 +2238,24 @@
         <v>8.0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F8" s="3">
         <v>90.0</v>
@@ -2212,13 +2267,13 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="J8" s="20">
+        <v>177</v>
+      </c>
+      <c r="J8" s="22">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="K8" s="20">
+      <c r="K8" s="22">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
@@ -2235,21 +2290,21 @@
         <v>9.0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>176</v>
+        <v>134</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -2264,13 +2319,13 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="J9" s="20">
+        <v>181</v>
+      </c>
+      <c r="J9" s="22">
         <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="22">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -2287,24 +2342,24 @@
         <v>8.0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
@@ -2316,13 +2371,13 @@
         <v>46149.0</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="J10" s="20">
+        <v>187</v>
+      </c>
+      <c r="J10" s="22">
         <f t="shared" si="3"/>
         <v>7.5</v>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="22">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
@@ -2341,19 +2396,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2365,13 +2420,13 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="J11" s="20">
+        <v>192</v>
+      </c>
+      <c r="J11" s="22">
         <f t="shared" si="3"/>
         <v>6.75</v>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="22">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
@@ -2388,7 +2443,7 @@
         <v>6.0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="205">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -426,6 +426,39 @@
   </si>
   <si>
     <t>Un maníaco un tanto peculiar se ha fugado y tiene un descerebrado plan para acabar con todo Gotham, ¿seréis capaces de encontrar su guarida a tiempo y ponerle fin a esta locura? Se requiere un mínimo de habilidad física, no saltaréis por ningún lado pero sí os deberéis en algún momento agachar durante el recorrido del juego. No es un juego de terror, el sonido o la ambientación podrán confundir pero remarcamos para todos aquellos que tengáis alguna duda: No es de terror, podrá jugar todo el público.</t>
+  </si>
+  <si>
+    <t>Roomions</t>
+  </si>
+  <si>
+    <t>Virus Games</t>
+  </si>
+  <si>
+    <t>Calella</t>
+  </si>
+  <si>
+    <t>Fiesta</t>
+  </si>
+  <si>
+    <t>Avenura</t>
+  </si>
+  <si>
+    <t>Media/Facil</t>
+  </si>
+  <si>
+    <t>https://virusroomescape.com/es/escape-room-calella-roomions/#reserva-roomions</t>
+  </si>
+  <si>
+    <t>¡El día del lanzamiento ha llegado! Aunque el laboratorio del doctor Nefário ha sido saboteado por alguien… preparadlo todo para el despegue del año a tiempo! En este escape room visual, familiar y lleno de color, vuestro equipo tendrá que reparar un cohete antes de que sea demasiado tarde. Con pruebas colaborativas, lógica sencilla y ambientación futurista, Roomions es ideal para quienes buscan una aventura accesible pero emocionante, sin sustos ni oscuridad. Perfecto para grupos con peques, adultos primerizos o amantes de lo geek.</t>
+  </si>
+  <si>
+    <t>Tao Room Escape</t>
+  </si>
+  <si>
+    <t>https://virusroomescape.com/es/escape-room-calella-tao/</t>
+  </si>
+  <si>
+    <t>Habéis reservado un tratamiento exclusivo en el misterioso Tao Japanese Massage Center, pero al llegar… nada es lo que parece. Tras una extraña bienvenida, os adentráis en una experiencia sensorial con giros inesperados, enigmas envolventes y un ambiente que mezcla calma oriental con diversión creciente. Una sala original,  perfecta para quienes buscan algo diferente, elegante y sorprendente en Calella.</t>
   </si>
   <si>
     <t>Duración (min)</t>
@@ -1009,7 +1042,7 @@
     <col customWidth="1" min="6" max="6" width="6.13"/>
     <col customWidth="1" min="7" max="7" width="7.0"/>
     <col customWidth="1" min="8" max="8" width="8.75"/>
-    <col customWidth="1" min="9" max="9" width="21.0"/>
+    <col customWidth="1" min="9" max="9" width="61.75"/>
     <col customWidth="1" min="10" max="10" width="13.88"/>
     <col customWidth="1" min="11" max="11" width="9.0"/>
     <col customWidth="1" min="12" max="12" width="370.5"/>
@@ -1670,7 +1703,7 @@
         <v>6.0</v>
       </c>
       <c r="K18" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>115</v>
@@ -1822,6 +1855,76 @@
       </c>
       <c r="L22" s="2" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F23" s="2">
+        <v>75.0</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H23" s="17">
+        <v>46150.0</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="J23" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H24" s="17">
+        <v>46150.0</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="J24" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="36">
@@ -1875,8 +1978,10 @@
     <hyperlink r:id="rId19" ref="I20"/>
     <hyperlink r:id="rId20" ref="I21"/>
     <hyperlink r:id="rId21" ref="I22"/>
+    <hyperlink r:id="rId22" location="reserva-roomions" ref="I23"/>
+    <hyperlink r:id="rId23" ref="I24"/>
   </hyperlinks>
-  <drawing r:id="rId22"/>
+  <drawing r:id="rId24"/>
 </worksheet>
 </file>
 
@@ -1912,34 +2017,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="P1" s="20" t="s">
         <v>11</v>
@@ -1947,16 +2052,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
@@ -1971,7 +2076,7 @@
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J2" s="21">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
@@ -1994,21 +2099,21 @@
         <v>9.0</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -2023,7 +2128,7 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J3" s="22">
         <f t="shared" si="1"/>
@@ -2046,12 +2151,12 @@
         <v>7.0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>
@@ -2075,7 +2180,7 @@
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="J4" s="1">
         <v>0.0</v>
@@ -2087,19 +2192,19 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -2111,7 +2216,7 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J5" s="22">
         <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
@@ -2134,24 +2239,24 @@
         <v>10.0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -2163,7 +2268,7 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="J6" s="22">
         <f t="shared" si="3"/>
@@ -2186,21 +2291,21 @@
         <v>9.0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -2215,7 +2320,7 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J7" s="22">
         <f t="shared" si="3"/>
@@ -2238,21 +2343,21 @@
         <v>8.0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>113</v>
@@ -2267,7 +2372,7 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="J8" s="22">
         <f t="shared" si="3"/>
@@ -2290,12 +2395,12 @@
         <v>9.0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>133</v>
@@ -2304,7 +2409,7 @@
         <v>134</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -2319,7 +2424,7 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J9" s="22">
         <f t="shared" si="3"/>
@@ -2342,24 +2447,24 @@
         <v>8.0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
@@ -2371,7 +2476,7 @@
         <v>46149.0</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="J10" s="22">
         <f t="shared" si="3"/>
@@ -2396,19 +2501,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2420,7 +2525,7 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="J11" s="22">
         <f t="shared" si="3"/>
@@ -2443,7 +2548,7 @@
         <v>6.0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="209">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -459,6 +459,18 @@
   </si>
   <si>
     <t>Habéis reservado un tratamiento exclusivo en el misterioso Tao Japanese Massage Center, pero al llegar… nada es lo que parece. Tras una extraña bienvenida, os adentráis en una experiencia sensorial con giros inesperados, enigmas envolventes y un ambiente que mezcla calma oriental con diversión creciente. Una sala original,  perfecta para quienes buscan algo diferente, elegante y sorprendente en Calella.</t>
+  </si>
+  <si>
+    <t>Achijira</t>
+  </si>
+  <si>
+    <t>Red Dopamine</t>
+  </si>
+  <si>
+    <t>https://www.reddopamine.com/landing-misterio-achijira</t>
+  </si>
+  <si>
+    <t>Tu Misión Será recatar a los que hicieron la última expedición. Su vida está en tus manos. No es tan sencillo como parece. Las pruebas y los distintos tipos de escenarios que te encontrarán pondrán a prueba tu conocimiento. Jugar es fácil, conseguir que todo salga bien no tanto...</t>
   </si>
   <si>
     <t>Duración (min)</t>
@@ -1927,6 +1939,38 @@
         <v>148</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" s="2">
+        <v>105.0</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="J25" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
     <row r="36">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
@@ -1980,8 +2024,9 @@
     <hyperlink r:id="rId21" ref="I22"/>
     <hyperlink r:id="rId22" location="reserva-roomions" ref="I23"/>
     <hyperlink r:id="rId23" ref="I24"/>
+    <hyperlink r:id="rId24" ref="I25"/>
   </hyperlinks>
-  <drawing r:id="rId24"/>
+  <drawing r:id="rId25"/>
 </worksheet>
 </file>
 
@@ -2017,34 +2062,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="P1" s="20" t="s">
         <v>11</v>
@@ -2052,16 +2097,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
@@ -2076,7 +2121,7 @@
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="J2" s="21">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
@@ -2099,21 +2144,21 @@
         <v>9.0</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -2128,7 +2173,7 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="J3" s="22">
         <f t="shared" si="1"/>
@@ -2151,12 +2196,12 @@
         <v>7.0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>
@@ -2180,7 +2225,7 @@
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="J4" s="1">
         <v>0.0</v>
@@ -2192,19 +2237,19 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -2216,7 +2261,7 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J5" s="22">
         <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
@@ -2239,24 +2284,24 @@
         <v>10.0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -2268,7 +2313,7 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J6" s="22">
         <f t="shared" si="3"/>
@@ -2291,21 +2336,21 @@
         <v>9.0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -2320,7 +2365,7 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="J7" s="22">
         <f t="shared" si="3"/>
@@ -2343,21 +2388,21 @@
         <v>8.0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>113</v>
@@ -2372,7 +2417,7 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="J8" s="22">
         <f t="shared" si="3"/>
@@ -2395,12 +2440,12 @@
         <v>9.0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>133</v>
@@ -2409,7 +2454,7 @@
         <v>134</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -2424,7 +2469,7 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J9" s="22">
         <f t="shared" si="3"/>
@@ -2447,24 +2492,24 @@
         <v>8.0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
@@ -2476,7 +2521,7 @@
         <v>46149.0</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="J10" s="22">
         <f t="shared" si="3"/>
@@ -2501,19 +2546,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2525,7 +2570,7 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J11" s="22">
         <f t="shared" si="3"/>
@@ -2548,7 +2593,7 @@
         <v>6.0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -428,217 +428,217 @@
     <t>Un maníaco un tanto peculiar se ha fugado y tiene un descerebrado plan para acabar con todo Gotham, ¿seréis capaces de encontrar su guarida a tiempo y ponerle fin a esta locura? Se requiere un mínimo de habilidad física, no saltaréis por ningún lado pero sí os deberéis en algún momento agachar durante el recorrido del juego. No es un juego de terror, el sonido o la ambientación podrán confundir pero remarcamos para todos aquellos que tengáis alguna duda: No es de terror, podrá jugar todo el público.</t>
   </si>
   <si>
+    <t>Tao Room Escape</t>
+  </si>
+  <si>
+    <t>Virus Games</t>
+  </si>
+  <si>
+    <t>Calella</t>
+  </si>
+  <si>
+    <t>Fiesta</t>
+  </si>
+  <si>
+    <t>Avenura</t>
+  </si>
+  <si>
+    <t>Media/Facil</t>
+  </si>
+  <si>
+    <t>https://virusroomescape.com/es/escape-room-calella-tao/</t>
+  </si>
+  <si>
+    <t>Habéis reservado un tratamiento exclusivo en el misterioso Tao Japanese Massage Center, pero al llegar… nada es lo que parece. Tras una extraña bienvenida, os adentráis en una experiencia sensorial con giros inesperados, enigmas envolventes y un ambiente que mezcla calma oriental con diversión creciente. Una sala original,  perfecta para quienes buscan algo diferente, elegante y sorprendente en Calella.</t>
+  </si>
+  <si>
+    <t>Achijira</t>
+  </si>
+  <si>
+    <t>Red Dopamine</t>
+  </si>
+  <si>
+    <t>https://www.reddopamine.com/landing-misterio-achijira</t>
+  </si>
+  <si>
+    <t>Tu Misión Será recatar a los que hicieron la última expedición. Su vida está en tus manos. No es tan sencillo como parece. Las pruebas y los distintos tipos de escenarios que te encontrarán pondrán a prueba tu conocimiento. Jugar es fácil, conseguir que todo salga bien no tanto...</t>
+  </si>
+  <si>
+    <t>Duración (min)</t>
+  </si>
+  <si>
+    <t>Rating Escapistas</t>
+  </si>
+  <si>
+    <t>Valoración Grupo</t>
+  </si>
+  <si>
+    <t>Ranking</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>Ambientación</t>
+  </si>
+  <si>
+    <t>Jugabilidad</t>
+  </si>
+  <si>
+    <t>GameMaster</t>
+  </si>
+  <si>
+    <t>Londium</t>
+  </si>
+  <si>
+    <t>Saga Escape Room</t>
+  </si>
+  <si>
+    <t>Steampunk</t>
+  </si>
+  <si>
+    <t>https://sagaescaperoom.com/</t>
+  </si>
+  <si>
+    <t>Inmersión cinematográfica absoluta con una estética Steampunk y victoriana impecable (niebla, olores y texturas de primer nivel). Jugada por 3 adultos y 2 niñas de 10 años en modo Tensión, resultó una experiencia redonda: las niñas fliparon desde la primera sala y el trato del Game Master fue excelente y muy cordial. Los puzzles de nueva generación están totalmente integrados en la trama, logrando un flujo de juego magnífico sin candados forzados. Una joya visual y narrativa que, gracias a su ambientación única, encantó a todo el grupo por igual.</t>
+  </si>
+  <si>
+    <t>La Taberna</t>
+  </si>
+  <si>
+    <t>The City Escape</t>
+  </si>
+  <si>
+    <t>Piratas</t>
+  </si>
+  <si>
+    <t>https://thecityescape.com/</t>
+  </si>
+  <si>
+    <t>Aventura de alta inmersión que inicia en una taberna hiperrealista donde la interacción con el entorno y el roleo son la clave. Destaca por una escenografía brutal en la mayoría de sus salas, logrando que el equipo (3 adultos y 2 niñas de 9 años) se sienta realmente dentro de una película de fantasía. Aunque el arranque es muy original y los enigmas mecánicos están integrados, nuestra experiencia con el acting de la Game Master Tabernera no nos terminó de impactar y algún puzzle se nos hizo complicado, perdiendo fluidez en ciertos momentos. A pesar de ello, se mantiene sin duda como uno de los mejores escapes a nivel español por su despliegue visual.</t>
+  </si>
+  <si>
+    <t>K.O.N.G. Protocol</t>
+  </si>
+  <si>
+    <t>https://escapebarcelona.com/</t>
+  </si>
+  <si>
+    <t>Jurásico</t>
+  </si>
+  <si>
+    <t>Golden Pop</t>
+  </si>
+  <si>
+    <t>Dinosaurios</t>
+  </si>
+  <si>
+    <t>Aventura familiar</t>
+  </si>
+  <si>
+    <t>https://goldenpop.es/jurasico/</t>
+  </si>
+  <si>
+    <t>Espectáculo visual y sensorial que recrea una selva hiperrealista bajo el centro de Barcelona. Una aventura de 120 minutos cargada de nostalgia, con una escenografía cinematográfica y efectos de sonido potentes. Jugado por 4 adultos y una niña de 9 años, destacamos el excelente acting inicial; el impacto del Game Master sobre la peque fue muy bueno y lo recuerda con mucho cariño. Es un escape dinámico con separación del grupo y una gran cantidad de juegos que garantiza que no haya momentos de parón. Ve preparado para gatear y ensuciarte con un poco de barro, ya que la vegetación se tiene que mantener. Una experiencia de 'nueva generación' de las más potentes del panorama actual.</t>
+  </si>
+  <si>
+    <t>WHITECHAPEL</t>
+  </si>
+  <si>
+    <t>Room Whitechapel</t>
+  </si>
+  <si>
+    <t>Jack el Destripador</t>
+  </si>
+  <si>
+    <t>Terror / Inmersivo</t>
+  </si>
+  <si>
+    <t>https://www.roomwhitechapel.com/</t>
+  </si>
+  <si>
+    <t>Un viaje asfixiante al Londres de Jack el Destripador con una de las ambientaciones más envolventes y lúgubres de Barcelona. Jugado por 6 adultos en modo Terror (también disponible en modo Aventura), resultó ser una experiencia de una intensidad arrolladora. A pesar de ser un grupo numeroso, nunca estuvimos parados, gracias a un diseño de 'calles' oscuras y laberínticas que mantiene la tensión constante. Destaca por un acting magistral y un contacto físico con los personajes que eleva la adrenalina al máximo. Una experiencia puramente cinematográfica que se sitúa, sin duda, en el top de los escapes de terror realizados.</t>
+  </si>
+  <si>
+    <t>Catacumbas</t>
+  </si>
+  <si>
+    <t>Alquimia / Aventuras</t>
+  </si>
+  <si>
+    <t>https://goldenpop.es/juegos/catacumbas/</t>
+  </si>
+  <si>
+    <t>Aventura épica inspirada en el universo de Indiana Jones que ofrece una de las puestas en escena más espectaculares de la ciudad. Jugada por 4 adultos y una niña de 9 años, resultó ser una experiencia increíble con pasadizos, puertas y salas totalmente inesperados. Destaca por sus más de 200 m² de decorados hiperrealistas y pruebas directamente basadas en las películas, logrando una atmósfera de expedición arqueológica total. Los enigmas están magistralmente integrados, priorizando mecanismos electrónicos y un trabajo cooperativo que mantiene la adrenalina alta sin necesidad de terror. Una experiencia de exploración pura donde las transiciones entre zonas dejan al grupo boquiabierto.</t>
+  </si>
+  <si>
+    <t>Exorcista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terror Stories </t>
+  </si>
+  <si>
+    <t>Exorcismo / Posesión</t>
+  </si>
+  <si>
+    <t>https://terrorstories.com/barcelona/exorcista-escape-room</t>
+  </si>
+  <si>
+    <t>Homenaje visceral y cinematográfico al clásico del cine de posesiones. Jugado por 5 adultos en modo Terror (disponible también modo Aventura), resultó una experiencia de una intensidad asombrosa, aunque el espacio puede sentirse algo justo para un grupo de cinco. Destaca por una ambientación lúgubre y opresiva con efectos visuales y sonoros que recrean fenómenos paranormales impactantes. El punto más fuerte es el acting increíble de los Game Masters, con una mención especial a la interpretación de 'la niña', posiblemente la mejor actuación vista jamás en un escape room. Incluye dinámicas de separación total del grupo, dejando a los jugadores solos en momentos puntuales de máxima vulnerabilidad. Una pesadilla real con una puesta en escena inolvidable.</t>
+  </si>
+  <si>
+    <t>Jaipur</t>
+  </si>
+  <si>
+    <t>Bollywood / India</t>
+  </si>
+  <si>
+    <t>https://www.kadabraescape.com/el-secreto-de-jaipur/</t>
+  </si>
+  <si>
+    <t>Fantasía pura y colorista inspirada en el folclore de la India que rompe con la estética lúgubre tradicional. Jugado por 3 adultos y 3 niñas de 10-11 años, resultó una experiencia sumamente divertida donde las pequeñas no pararon ni un segundo de resolver retos. Destaca por una escenografía vibrante y una decoración preciosa, con olores característicos que te transportan a un mercado exótico. Los puzzles son muy táctiles e ingeniosos, huyendo de los clásicos candados para centrarse en mecanismos 'mágicos' que fluyen con naturalidad. Con una historia sólida y un sorprendente giro de argumento, es un espectáculo visual cargado de buen rollo donde el asombro y el ingenio son los protagonistas.</t>
+  </si>
+  <si>
+    <t>encryptroom</t>
+  </si>
+  <si>
+    <t>Encrypt</t>
+  </si>
+  <si>
+    <t>Asesino en serie</t>
+  </si>
+  <si>
+    <t>Tensión / Inmersivo</t>
+  </si>
+  <si>
+    <t>https://www.encryptroom.com/</t>
+  </si>
+  <si>
+    <t>Bank of Thaqar</t>
+  </si>
+  <si>
+    <t>MissionLeak</t>
+  </si>
+  <si>
+    <t>Atraco / Acción</t>
+  </si>
+  <si>
+    <t>Acción</t>
+  </si>
+  <si>
+    <t>https://www.missionleak.com/bankofthaqar</t>
+  </si>
+  <si>
+    <t>Referente de la 'vieja escuela' jugado originalmente en 2015. En su momento fue pionero en la temática de atracos, pero con la perspectiva actual de las salas de nueva generación, se siente una experiencia sencilla, lineal y muy basada en candados. Nota importante: Nuestra valoración se basa en la versión de hace años; desconocemos si ha recibido actualizaciones técnicas o de escenografía desde entonces. Comparado con los estándares inmersivos de 2026, palidece en espectacularidad y fluidez narrativa, quedando como una pieza de coleccionista para entender los inicios del sector. Lo hicimos 4 adultos</t>
+  </si>
+  <si>
     <t>Roomions</t>
   </si>
   <si>
-    <t>Virus Games</t>
-  </si>
-  <si>
-    <t>Calella</t>
-  </si>
-  <si>
-    <t>Fiesta</t>
-  </si>
-  <si>
-    <t>Avenura</t>
-  </si>
-  <si>
-    <t>Media/Facil</t>
-  </si>
-  <si>
     <t>https://virusroomescape.com/es/escape-room-calella-roomions/#reserva-roomions</t>
   </si>
   <si>
-    <t>¡El día del lanzamiento ha llegado! Aunque el laboratorio del doctor Nefário ha sido saboteado por alguien… preparadlo todo para el despegue del año a tiempo! En este escape room visual, familiar y lleno de color, vuestro equipo tendrá que reparar un cohete antes de que sea demasiado tarde. Con pruebas colaborativas, lógica sencilla y ambientación futurista, Roomions es ideal para quienes buscan una aventura accesible pero emocionante, sin sustos ni oscuridad. Perfecto para grupos con peques, adultos primerizos o amantes de lo geek.</t>
-  </si>
-  <si>
-    <t>Tao Room Escape</t>
-  </si>
-  <si>
-    <t>https://virusroomescape.com/es/escape-room-calella-tao/</t>
-  </si>
-  <si>
-    <t>Habéis reservado un tratamiento exclusivo en el misterioso Tao Japanese Massage Center, pero al llegar… nada es lo que parece. Tras una extraña bienvenida, os adentráis en una experiencia sensorial con giros inesperados, enigmas envolventes y un ambiente que mezcla calma oriental con diversión creciente. Una sala original,  perfecta para quienes buscan algo diferente, elegante y sorprendente en Calella.</t>
-  </si>
-  <si>
-    <t>Achijira</t>
-  </si>
-  <si>
-    <t>Red Dopamine</t>
-  </si>
-  <si>
-    <t>https://www.reddopamine.com/landing-misterio-achijira</t>
-  </si>
-  <si>
-    <t>Tu Misión Será recatar a los que hicieron la última expedición. Su vida está en tus manos. No es tan sencillo como parece. Las pruebas y los distintos tipos de escenarios que te encontrarán pondrán a prueba tu conocimiento. Jugar es fácil, conseguir que todo salga bien no tanto...</t>
-  </si>
-  <si>
-    <t>Duración (min)</t>
-  </si>
-  <si>
-    <t>Rating Escapistas</t>
-  </si>
-  <si>
-    <t>Valoración Grupo</t>
-  </si>
-  <si>
-    <t>Ranking</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>Ambientación</t>
-  </si>
-  <si>
-    <t>Jugabilidad</t>
-  </si>
-  <si>
-    <t>GameMaster</t>
-  </si>
-  <si>
-    <t>Londium</t>
-  </si>
-  <si>
-    <t>Saga Escape Room</t>
-  </si>
-  <si>
-    <t>Steampunk</t>
-  </si>
-  <si>
-    <t>https://sagaescaperoom.com/</t>
-  </si>
-  <si>
-    <t>Inmersión cinematográfica absoluta con una estética Steampunk y victoriana impecable (niebla, olores y texturas de primer nivel). Jugada por 3 adultos y 2 niñas de 10 años en modo Tensión, resultó una experiencia redonda: las niñas fliparon desde la primera sala y el trato del Game Master fue excelente y muy cordial. Los puzzles de nueva generación están totalmente integrados en la trama, logrando un flujo de juego magnífico sin candados forzados. Una joya visual y narrativa que, gracias a su ambientación única, encantó a todo el grupo por igual.</t>
-  </si>
-  <si>
-    <t>La Taberna</t>
-  </si>
-  <si>
-    <t>The City Escape</t>
-  </si>
-  <si>
-    <t>Piratas</t>
-  </si>
-  <si>
-    <t>https://thecityescape.com/</t>
-  </si>
-  <si>
-    <t>Aventura de alta inmersión que inicia en una taberna hiperrealista donde la interacción con el entorno y el roleo son la clave. Destaca por una escenografía brutal en la mayoría de sus salas, logrando que el equipo (3 adultos y 2 niñas de 9 años) se sienta realmente dentro de una película de fantasía. Aunque el arranque es muy original y los enigmas mecánicos están integrados, nuestra experiencia con el acting de la Game Master Tabernera no nos terminó de impactar y algún puzzle se nos hizo complicado, perdiendo fluidez en ciertos momentos. A pesar de ello, se mantiene sin duda como uno de los mejores escapes a nivel español por su despliegue visual.</t>
-  </si>
-  <si>
-    <t>K.O.N.G. Protocol</t>
-  </si>
-  <si>
-    <t>https://escapebarcelona.com/</t>
-  </si>
-  <si>
-    <t>Jurásico</t>
-  </si>
-  <si>
-    <t>Golden Pop</t>
-  </si>
-  <si>
-    <t>Dinosaurios</t>
-  </si>
-  <si>
-    <t>Aventura familiar</t>
-  </si>
-  <si>
-    <t>https://goldenpop.es/jurasico/</t>
-  </si>
-  <si>
-    <t>Espectáculo visual y sensorial que recrea una selva hiperrealista bajo el centro de Barcelona. Una aventura de 120 minutos cargada de nostalgia, con una escenografía cinematográfica y efectos de sonido potentes. Jugado por 4 adultos y una niña de 9 años, destacamos el excelente acting inicial; el impacto del Game Master sobre la peque fue muy bueno y lo recuerda con mucho cariño. Es un escape dinámico con separación del grupo y una gran cantidad de juegos que garantiza que no haya momentos de parón. Ve preparado para gatear y ensuciarte con un poco de barro, ya que la vegetación se tiene que mantener. Una experiencia de 'nueva generación' de las más potentes del panorama actual.</t>
-  </si>
-  <si>
-    <t>WHITECHAPEL</t>
-  </si>
-  <si>
-    <t>Room Whitechapel</t>
-  </si>
-  <si>
-    <t>Jack el Destripador</t>
-  </si>
-  <si>
-    <t>Terror / Inmersivo</t>
-  </si>
-  <si>
-    <t>https://www.roomwhitechapel.com/</t>
-  </si>
-  <si>
-    <t>Un viaje asfixiante al Londres de Jack el Destripador con una de las ambientaciones más envolventes y lúgubres de Barcelona. Jugado por 6 adultos en modo Terror (también disponible en modo Aventura), resultó ser una experiencia de una intensidad arrolladora. A pesar de ser un grupo numeroso, nunca estuvimos parados, gracias a un diseño de 'calles' oscuras y laberínticas que mantiene la tensión constante. Destaca por un acting magistral y un contacto físico con los personajes que eleva la adrenalina al máximo. Una experiencia puramente cinematográfica que se sitúa, sin duda, en el top de los escapes de terror realizados.</t>
-  </si>
-  <si>
-    <t>Catacumbas</t>
-  </si>
-  <si>
-    <t>Alquimia / Aventuras</t>
-  </si>
-  <si>
-    <t>https://goldenpop.es/juegos/catacumbas/</t>
-  </si>
-  <si>
-    <t>Aventura épica inspirada en el universo de Indiana Jones que ofrece una de las puestas en escena más espectaculares de la ciudad. Jugada por 4 adultos y una niña de 9 años, resultó ser una experiencia increíble con pasadizos, puertas y salas totalmente inesperados. Destaca por sus más de 200 m² de decorados hiperrealistas y pruebas directamente basadas en las películas, logrando una atmósfera de expedición arqueológica total. Los enigmas están magistralmente integrados, priorizando mecanismos electrónicos y un trabajo cooperativo que mantiene la adrenalina alta sin necesidad de terror. Una experiencia de exploración pura donde las transiciones entre zonas dejan al grupo boquiabierto.</t>
-  </si>
-  <si>
-    <t>Exorcista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terror Stories </t>
-  </si>
-  <si>
-    <t>Exorcismo / Posesión</t>
-  </si>
-  <si>
-    <t>https://terrorstories.com/barcelona/exorcista-escape-room</t>
-  </si>
-  <si>
-    <t>Homenaje visceral y cinematográfico al clásico del cine de posesiones. Jugado por 5 adultos en modo Terror (disponible también modo Aventura), resultó una experiencia de una intensidad asombrosa, aunque el espacio puede sentirse algo justo para un grupo de cinco. Destaca por una ambientación lúgubre y opresiva con efectos visuales y sonoros que recrean fenómenos paranormales impactantes. El punto más fuerte es el acting increíble de los Game Masters, con una mención especial a la interpretación de 'la niña', posiblemente la mejor actuación vista jamás en un escape room. Incluye dinámicas de separación total del grupo, dejando a los jugadores solos en momentos puntuales de máxima vulnerabilidad. Una pesadilla real con una puesta en escena inolvidable.</t>
-  </si>
-  <si>
-    <t>Jaipur</t>
-  </si>
-  <si>
-    <t>Bollywood / India</t>
-  </si>
-  <si>
-    <t>https://www.kadabraescape.com/el-secreto-de-jaipur/</t>
-  </si>
-  <si>
-    <t>Fantasía pura y colorista inspirada en el folclore de la India que rompe con la estética lúgubre tradicional. Jugado por 3 adultos y 3 niñas de 10-11 años, resultó una experiencia sumamente divertida donde las pequeñas no pararon ni un segundo de resolver retos. Destaca por una escenografía vibrante y una decoración preciosa, con olores característicos que te transportan a un mercado exótico. Los puzzles son muy táctiles e ingeniosos, huyendo de los clásicos candados para centrarse en mecanismos 'mágicos' que fluyen con naturalidad. Con una historia sólida y un sorprendente giro de argumento, es un espectáculo visual cargado de buen rollo donde el asombro y el ingenio son los protagonistas.</t>
-  </si>
-  <si>
-    <t>encryptroom</t>
-  </si>
-  <si>
-    <t>Encrypt</t>
-  </si>
-  <si>
-    <t>Asesino en serie</t>
-  </si>
-  <si>
-    <t>Tensión / Inmersivo</t>
-  </si>
-  <si>
-    <t>https://www.encryptroom.com/</t>
-  </si>
-  <si>
-    <t>Bank of Thaqar</t>
-  </si>
-  <si>
-    <t>MissionLeak</t>
-  </si>
-  <si>
-    <t>Atraco / Acción</t>
-  </si>
-  <si>
-    <t>Acción</t>
-  </si>
-  <si>
-    <t>https://www.missionleak.com/bankofthaqar</t>
-  </si>
-  <si>
-    <t>Referente de la 'vieja escuela' jugado originalmente en 2015. En su momento fue pionero en la temática de atracos, pero con la perspectiva actual de las salas de nueva generación, se siente una experiencia sencilla, lineal y muy basada en candados. Nota importante: Nuestra valoración se basa en la versión de hace años; desconocemos si ha recibido actualizaciones técnicas o de escenografía desde entonces. Comparado con los estándares inmersivos de 2026, palidece en espectacularidad y fluidez narrativa, quedando como una pieza de coleccionista para entender los inicios del sector. Lo hicimos 4 adultos</t>
+    <t>Hoy hemos probado el escape room de Roomions y la experiencia ha sido muy positiva. Fuimos dos adultos y dos niños (6 y 10 años) y el juego funcionó perfecto para todos. El pequeño, en su primer escape room, participó mucho y salió encantado. La mayor, con experiencia, también lo disfrutó mucho. Es un room de tamaño contenido (una sala y media), pero muy bien aprovechado: no paras en ningún momento y todo fluye. Mención especial al Game Master, Edu (Nefario Jr.), que lo hizo genial. Muy recomendable: familiar y muy divertido.</t>
   </si>
 </sst>
 </file>
@@ -1869,44 +1869,9 @@
         <v>137</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F23" s="2">
-        <v>75.0</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H23" s="17">
-        <v>46150.0</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="J23" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>139</v>
@@ -1930,21 +1895,21 @@
         <v>46150.0</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J24" s="2">
         <v>8.0</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>135</v>
@@ -1962,13 +1927,13 @@
         <v>9.0</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J25" s="2">
         <v>7.0</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36">
@@ -2022,11 +1987,10 @@
     <hyperlink r:id="rId19" ref="I20"/>
     <hyperlink r:id="rId20" ref="I21"/>
     <hyperlink r:id="rId21" ref="I22"/>
-    <hyperlink r:id="rId22" location="reserva-roomions" ref="I23"/>
-    <hyperlink r:id="rId23" ref="I24"/>
-    <hyperlink r:id="rId24" ref="I25"/>
+    <hyperlink r:id="rId22" ref="I24"/>
+    <hyperlink r:id="rId23" ref="I25"/>
   </hyperlinks>
-  <drawing r:id="rId25"/>
+  <drawing r:id="rId24"/>
 </worksheet>
 </file>
 
@@ -2062,34 +2026,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="L1" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="M1" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>157</v>
-      </c>
-      <c r="M1" s="20" t="s">
-        <v>158</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>160</v>
       </c>
       <c r="P1" s="20" t="s">
         <v>11</v>
@@ -2097,16 +2061,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
@@ -2121,14 +2085,14 @@
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J2" s="21">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
         <v>11544.75</v>
       </c>
       <c r="K2" s="22">
-        <f t="shared" ref="K2:K11" si="2">RANK(J2, $J$2:$J$22)</f>
+        <f t="shared" ref="K2:K12" si="2">RANK(J2, $J$2:$J$22)</f>
         <v>1</v>
       </c>
       <c r="L2" s="17">
@@ -2144,21 +2108,21 @@
         <v>9.0</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -2173,7 +2137,7 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J3" s="22">
         <f t="shared" si="1"/>
@@ -2196,12 +2160,12 @@
         <v>7.0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>
@@ -2225,31 +2189,31 @@
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J4" s="1">
         <v>0.0</v>
       </c>
       <c r="K4" s="22">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -2261,7 +2225,7 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J5" s="22">
         <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
@@ -2284,24 +2248,24 @@
         <v>10.0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -2313,7 +2277,7 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="J6" s="22">
         <f t="shared" si="3"/>
@@ -2336,21 +2300,21 @@
         <v>9.0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -2365,7 +2329,7 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J7" s="22">
         <f t="shared" si="3"/>
@@ -2388,21 +2352,21 @@
         <v>8.0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>113</v>
@@ -2417,7 +2381,7 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J8" s="22">
         <f t="shared" si="3"/>
@@ -2440,12 +2404,12 @@
         <v>9.0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>133</v>
@@ -2454,7 +2418,7 @@
         <v>134</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -2469,7 +2433,7 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="J9" s="22">
         <f t="shared" si="3"/>
@@ -2492,24 +2456,24 @@
         <v>8.0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
@@ -2521,7 +2485,7 @@
         <v>46149.0</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="J10" s="22">
         <f t="shared" si="3"/>
@@ -2529,7 +2493,7 @@
       </c>
       <c r="K10" s="22">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L10" s="2">
         <v>7.0</v>
@@ -2546,19 +2510,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2570,7 +2534,7 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="J11" s="22">
         <f t="shared" si="3"/>
@@ -2578,7 +2542,7 @@
       </c>
       <c r="K11" s="22">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L11" s="2">
         <v>7.0</v>
@@ -2593,6 +2557,57 @@
         <v>6.0</v>
       </c>
       <c r="P11" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" s="2">
+        <v>75.0</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="17">
+        <v>46150.0</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="J12" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="K12" s="22">
+        <f t="shared" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="L12" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="M12" s="17">
+        <v>46150.0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="O12" s="17">
+        <v>46150.0</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>208</v>
       </c>
     </row>
@@ -2608,7 +2623,8 @@
     <hyperlink r:id="rId8" ref="I9"/>
     <hyperlink r:id="rId9" ref="I10"/>
     <hyperlink r:id="rId10" ref="I11"/>
+    <hyperlink r:id="rId11" location="reserva-roomions" ref="I12"/>
   </hyperlinks>
-  <drawing r:id="rId11"/>
+  <drawing r:id="rId12"/>
 </worksheet>
 </file>
--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -428,217 +428,217 @@
     <t>Un maníaco un tanto peculiar se ha fugado y tiene un descerebrado plan para acabar con todo Gotham, ¿seréis capaces de encontrar su guarida a tiempo y ponerle fin a esta locura? Se requiere un mínimo de habilidad física, no saltaréis por ningún lado pero sí os deberéis en algún momento agachar durante el recorrido del juego. No es un juego de terror, el sonido o la ambientación podrán confundir pero remarcamos para todos aquellos que tengáis alguna duda: No es de terror, podrá jugar todo el público.</t>
   </si>
   <si>
+    <t>Achijira</t>
+  </si>
+  <si>
+    <t>Red Dopamine</t>
+  </si>
+  <si>
+    <t>Avenura</t>
+  </si>
+  <si>
+    <t>https://www.reddopamine.com/landing-misterio-achijira</t>
+  </si>
+  <si>
+    <t>Tu Misión Será recatar a los que hicieron la última expedición. Su vida está en tus manos. No es tan sencillo como parece. Las pruebas y los distintos tipos de escenarios que te encontrarán pondrán a prueba tu conocimiento. Jugar es fácil, conseguir que todo salga bien no tanto...</t>
+  </si>
+  <si>
+    <t>Duración (min)</t>
+  </si>
+  <si>
+    <t>Rating Escapistas</t>
+  </si>
+  <si>
+    <t>Valoración Grupo</t>
+  </si>
+  <si>
+    <t>Ranking</t>
+  </si>
+  <si>
+    <t>Historia</t>
+  </si>
+  <si>
+    <t>Ambientación</t>
+  </si>
+  <si>
+    <t>Jugabilidad</t>
+  </si>
+  <si>
+    <t>GameMaster</t>
+  </si>
+  <si>
+    <t>Londium</t>
+  </si>
+  <si>
+    <t>Saga Escape Room</t>
+  </si>
+  <si>
+    <t>Steampunk</t>
+  </si>
+  <si>
+    <t>https://sagaescaperoom.com/</t>
+  </si>
+  <si>
+    <t>Inmersión cinematográfica absoluta con una estética Steampunk y victoriana impecable (niebla, olores y texturas de primer nivel). Jugada por 3 adultos y 2 niñas de 10 años en modo Tensión, resultó una experiencia redonda: las niñas fliparon desde la primera sala y el trato del Game Master fue excelente y muy cordial. Los puzzles de nueva generación están totalmente integrados en la trama, logrando un flujo de juego magnífico sin candados forzados. Una joya visual y narrativa que, gracias a su ambientación única, encantó a todo el grupo por igual.</t>
+  </si>
+  <si>
+    <t>La Taberna</t>
+  </si>
+  <si>
+    <t>The City Escape</t>
+  </si>
+  <si>
+    <t>Piratas</t>
+  </si>
+  <si>
+    <t>https://thecityescape.com/</t>
+  </si>
+  <si>
+    <t>Aventura de alta inmersión que inicia en una taberna hiperrealista donde la interacción con el entorno y el roleo son la clave. Destaca por una escenografía brutal en la mayoría de sus salas, logrando que el equipo (3 adultos y 2 niñas de 9 años) se sienta realmente dentro de una película de fantasía. Aunque el arranque es muy original y los enigmas mecánicos están integrados, nuestra experiencia con el acting de la Game Master Tabernera no nos terminó de impactar y algún puzzle se nos hizo complicado, perdiendo fluidez en ciertos momentos. A pesar de ello, se mantiene sin duda como uno de los mejores escapes a nivel español por su despliegue visual.</t>
+  </si>
+  <si>
+    <t>K.O.N.G. Protocol</t>
+  </si>
+  <si>
+    <t>https://escapebarcelona.com/</t>
+  </si>
+  <si>
+    <t>Jurásico</t>
+  </si>
+  <si>
+    <t>Golden Pop</t>
+  </si>
+  <si>
+    <t>Dinosaurios</t>
+  </si>
+  <si>
+    <t>Aventura familiar</t>
+  </si>
+  <si>
+    <t>https://goldenpop.es/jurasico/</t>
+  </si>
+  <si>
+    <t>Espectáculo visual y sensorial que recrea una selva hiperrealista bajo el centro de Barcelona. Una aventura de 120 minutos cargada de nostalgia, con una escenografía cinematográfica y efectos de sonido potentes. Jugado por 4 adultos y una niña de 9 años, destacamos el excelente acting inicial; el impacto del Game Master sobre la peque fue muy bueno y lo recuerda con mucho cariño. Es un escape dinámico con separación del grupo y una gran cantidad de juegos que garantiza que no haya momentos de parón. Ve preparado para gatear y ensuciarte con un poco de barro, ya que la vegetación se tiene que mantener. Una experiencia de 'nueva generación' de las más potentes del panorama actual.</t>
+  </si>
+  <si>
+    <t>WHITECHAPEL</t>
+  </si>
+  <si>
+    <t>Room Whitechapel</t>
+  </si>
+  <si>
+    <t>Jack el Destripador</t>
+  </si>
+  <si>
+    <t>Terror / Inmersivo</t>
+  </si>
+  <si>
+    <t>https://www.roomwhitechapel.com/</t>
+  </si>
+  <si>
+    <t>Un viaje asfixiante al Londres de Jack el Destripador con una de las ambientaciones más envolventes y lúgubres de Barcelona. Jugado por 6 adultos en modo Terror (también disponible en modo Aventura), resultó ser una experiencia de una intensidad arrolladora. A pesar de ser un grupo numeroso, nunca estuvimos parados, gracias a un diseño de 'calles' oscuras y laberínticas que mantiene la tensión constante. Destaca por un acting magistral y un contacto físico con los personajes que eleva la adrenalina al máximo. Una experiencia puramente cinematográfica que se sitúa, sin duda, en el top de los escapes de terror realizados.</t>
+  </si>
+  <si>
+    <t>Catacumbas</t>
+  </si>
+  <si>
+    <t>Alquimia / Aventuras</t>
+  </si>
+  <si>
+    <t>https://goldenpop.es/juegos/catacumbas/</t>
+  </si>
+  <si>
+    <t>Aventura épica inspirada en el universo de Indiana Jones que ofrece una de las puestas en escena más espectaculares de la ciudad. Jugada por 4 adultos y una niña de 9 años, resultó ser una experiencia increíble con pasadizos, puertas y salas totalmente inesperados. Destaca por sus más de 200 m² de decorados hiperrealistas y pruebas directamente basadas en las películas, logrando una atmósfera de expedición arqueológica total. Los enigmas están magistralmente integrados, priorizando mecanismos electrónicos y un trabajo cooperativo que mantiene la adrenalina alta sin necesidad de terror. Una experiencia de exploración pura donde las transiciones entre zonas dejan al grupo boquiabierto.</t>
+  </si>
+  <si>
+    <t>Exorcista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terror Stories </t>
+  </si>
+  <si>
+    <t>Exorcismo / Posesión</t>
+  </si>
+  <si>
+    <t>https://terrorstories.com/barcelona/exorcista-escape-room</t>
+  </si>
+  <si>
+    <t>Homenaje visceral y cinematográfico al clásico del cine de posesiones. Jugado por 5 adultos en modo Terror (disponible también modo Aventura), resultó una experiencia de una intensidad asombrosa, aunque el espacio puede sentirse algo justo para un grupo de cinco. Destaca por una ambientación lúgubre y opresiva con efectos visuales y sonoros que recrean fenómenos paranormales impactantes. El punto más fuerte es el acting increíble de los Game Masters, con una mención especial a la interpretación de 'la niña', posiblemente la mejor actuación vista jamás en un escape room. Incluye dinámicas de separación total del grupo, dejando a los jugadores solos en momentos puntuales de máxima vulnerabilidad. Una pesadilla real con una puesta en escena inolvidable.</t>
+  </si>
+  <si>
+    <t>Jaipur</t>
+  </si>
+  <si>
+    <t>Bollywood / India</t>
+  </si>
+  <si>
+    <t>https://www.kadabraescape.com/el-secreto-de-jaipur/</t>
+  </si>
+  <si>
+    <t>Fantasía pura y colorista inspirada en el folclore de la India que rompe con la estética lúgubre tradicional. Jugado por 3 adultos y 3 niñas de 10-11 años, resultó una experiencia sumamente divertida donde las pequeñas no pararon ni un segundo de resolver retos. Destaca por una escenografía vibrante y una decoración preciosa, con olores característicos que te transportan a un mercado exótico. Los puzzles son muy táctiles e ingeniosos, huyendo de los clásicos candados para centrarse en mecanismos 'mágicos' que fluyen con naturalidad. Con una historia sólida y un sorprendente giro de argumento, es un espectáculo visual cargado de buen rollo donde el asombro y el ingenio son los protagonistas.</t>
+  </si>
+  <si>
+    <t>encryptroom</t>
+  </si>
+  <si>
+    <t>Encrypt</t>
+  </si>
+  <si>
+    <t>Asesino en serie</t>
+  </si>
+  <si>
+    <t>Tensión / Inmersivo</t>
+  </si>
+  <si>
+    <t>https://www.encryptroom.com/</t>
+  </si>
+  <si>
+    <t>Bank of Thaqar</t>
+  </si>
+  <si>
+    <t>MissionLeak</t>
+  </si>
+  <si>
+    <t>Atraco / Acción</t>
+  </si>
+  <si>
+    <t>Acción</t>
+  </si>
+  <si>
+    <t>https://www.missionleak.com/bankofthaqar</t>
+  </si>
+  <si>
+    <t>Referente de la 'vieja escuela' jugado originalmente en 2015. En su momento fue pionero en la temática de atracos, pero con la perspectiva actual de las salas de nueva generación, se siente una experiencia sencilla, lineal y muy basada en candados. Nota importante: Nuestra valoración se basa en la versión de hace años; desconocemos si ha recibido actualizaciones técnicas o de escenografía desde entonces. Comparado con los estándares inmersivos de 2026, palidece en espectacularidad y fluidez narrativa, quedando como una pieza de coleccionista para entender los inicios del sector. Lo hicimos 4 adultos</t>
+  </si>
+  <si>
+    <t>Roomions</t>
+  </si>
+  <si>
+    <t>Virus Games</t>
+  </si>
+  <si>
+    <t>Calella</t>
+  </si>
+  <si>
+    <t>Fiesta</t>
+  </si>
+  <si>
+    <t>Media/Facil</t>
+  </si>
+  <si>
+    <t>https://virusroomescape.com/es/escape-room-calella-roomions/#reserva-roomions</t>
+  </si>
+  <si>
+    <t>Hoy hemos probado el escape room de Roomions y la experiencia ha sido muy positiva. Fuimos dos adultos y dos niños (6 y 10 años) y el juego funcionó perfecto para todos. El pequeño, en su primer escape room, participó mucho y salió encantado. La mayor, con experiencia, también lo disfrutó mucho. Es un room de tamaño contenido (una sala y media), pero muy bien aprovechado: no paras en ningún momento y todo fluye. Mención especial al Game Master, Edu (Nefario Jr.), que lo hizo genial. Muy recomendable: familiar y muy divertido.</t>
+  </si>
+  <si>
     <t>Tao Room Escape</t>
   </si>
   <si>
-    <t>Virus Games</t>
-  </si>
-  <si>
-    <t>Calella</t>
-  </si>
-  <si>
-    <t>Fiesta</t>
-  </si>
-  <si>
-    <t>Avenura</t>
-  </si>
-  <si>
-    <t>Media/Facil</t>
-  </si>
-  <si>
     <t>https://virusroomescape.com/es/escape-room-calella-tao/</t>
   </si>
   <si>
-    <t>Habéis reservado un tratamiento exclusivo en el misterioso Tao Japanese Massage Center, pero al llegar… nada es lo que parece. Tras una extraña bienvenida, os adentráis en una experiencia sensorial con giros inesperados, enigmas envolventes y un ambiente que mezcla calma oriental con diversión creciente. Una sala original,  perfecta para quienes buscan algo diferente, elegante y sorprendente en Calella.</t>
-  </si>
-  <si>
-    <t>Achijira</t>
-  </si>
-  <si>
-    <t>Red Dopamine</t>
-  </si>
-  <si>
-    <t>https://www.reddopamine.com/landing-misterio-achijira</t>
-  </si>
-  <si>
-    <t>Tu Misión Será recatar a los que hicieron la última expedición. Su vida está en tus manos. No es tan sencillo como parece. Las pruebas y los distintos tipos de escenarios que te encontrarán pondrán a prueba tu conocimiento. Jugar es fácil, conseguir que todo salga bien no tanto...</t>
-  </si>
-  <si>
-    <t>Duración (min)</t>
-  </si>
-  <si>
-    <t>Rating Escapistas</t>
-  </si>
-  <si>
-    <t>Valoración Grupo</t>
-  </si>
-  <si>
-    <t>Ranking</t>
-  </si>
-  <si>
-    <t>Historia</t>
-  </si>
-  <si>
-    <t>Ambientación</t>
-  </si>
-  <si>
-    <t>Jugabilidad</t>
-  </si>
-  <si>
-    <t>GameMaster</t>
-  </si>
-  <si>
-    <t>Londium</t>
-  </si>
-  <si>
-    <t>Saga Escape Room</t>
-  </si>
-  <si>
-    <t>Steampunk</t>
-  </si>
-  <si>
-    <t>https://sagaescaperoom.com/</t>
-  </si>
-  <si>
-    <t>Inmersión cinematográfica absoluta con una estética Steampunk y victoriana impecable (niebla, olores y texturas de primer nivel). Jugada por 3 adultos y 2 niñas de 10 años en modo Tensión, resultó una experiencia redonda: las niñas fliparon desde la primera sala y el trato del Game Master fue excelente y muy cordial. Los puzzles de nueva generación están totalmente integrados en la trama, logrando un flujo de juego magnífico sin candados forzados. Una joya visual y narrativa que, gracias a su ambientación única, encantó a todo el grupo por igual.</t>
-  </si>
-  <si>
-    <t>La Taberna</t>
-  </si>
-  <si>
-    <t>The City Escape</t>
-  </si>
-  <si>
-    <t>Piratas</t>
-  </si>
-  <si>
-    <t>https://thecityescape.com/</t>
-  </si>
-  <si>
-    <t>Aventura de alta inmersión que inicia en una taberna hiperrealista donde la interacción con el entorno y el roleo son la clave. Destaca por una escenografía brutal en la mayoría de sus salas, logrando que el equipo (3 adultos y 2 niñas de 9 años) se sienta realmente dentro de una película de fantasía. Aunque el arranque es muy original y los enigmas mecánicos están integrados, nuestra experiencia con el acting de la Game Master Tabernera no nos terminó de impactar y algún puzzle se nos hizo complicado, perdiendo fluidez en ciertos momentos. A pesar de ello, se mantiene sin duda como uno de los mejores escapes a nivel español por su despliegue visual.</t>
-  </si>
-  <si>
-    <t>K.O.N.G. Protocol</t>
-  </si>
-  <si>
-    <t>https://escapebarcelona.com/</t>
-  </si>
-  <si>
-    <t>Jurásico</t>
-  </si>
-  <si>
-    <t>Golden Pop</t>
-  </si>
-  <si>
-    <t>Dinosaurios</t>
-  </si>
-  <si>
-    <t>Aventura familiar</t>
-  </si>
-  <si>
-    <t>https://goldenpop.es/jurasico/</t>
-  </si>
-  <si>
-    <t>Espectáculo visual y sensorial que recrea una selva hiperrealista bajo el centro de Barcelona. Una aventura de 120 minutos cargada de nostalgia, con una escenografía cinematográfica y efectos de sonido potentes. Jugado por 4 adultos y una niña de 9 años, destacamos el excelente acting inicial; el impacto del Game Master sobre la peque fue muy bueno y lo recuerda con mucho cariño. Es un escape dinámico con separación del grupo y una gran cantidad de juegos que garantiza que no haya momentos de parón. Ve preparado para gatear y ensuciarte con un poco de barro, ya que la vegetación se tiene que mantener. Una experiencia de 'nueva generación' de las más potentes del panorama actual.</t>
-  </si>
-  <si>
-    <t>WHITECHAPEL</t>
-  </si>
-  <si>
-    <t>Room Whitechapel</t>
-  </si>
-  <si>
-    <t>Jack el Destripador</t>
-  </si>
-  <si>
-    <t>Terror / Inmersivo</t>
-  </si>
-  <si>
-    <t>https://www.roomwhitechapel.com/</t>
-  </si>
-  <si>
-    <t>Un viaje asfixiante al Londres de Jack el Destripador con una de las ambientaciones más envolventes y lúgubres de Barcelona. Jugado por 6 adultos en modo Terror (también disponible en modo Aventura), resultó ser una experiencia de una intensidad arrolladora. A pesar de ser un grupo numeroso, nunca estuvimos parados, gracias a un diseño de 'calles' oscuras y laberínticas que mantiene la tensión constante. Destaca por un acting magistral y un contacto físico con los personajes que eleva la adrenalina al máximo. Una experiencia puramente cinematográfica que se sitúa, sin duda, en el top de los escapes de terror realizados.</t>
-  </si>
-  <si>
-    <t>Catacumbas</t>
-  </si>
-  <si>
-    <t>Alquimia / Aventuras</t>
-  </si>
-  <si>
-    <t>https://goldenpop.es/juegos/catacumbas/</t>
-  </si>
-  <si>
-    <t>Aventura épica inspirada en el universo de Indiana Jones que ofrece una de las puestas en escena más espectaculares de la ciudad. Jugada por 4 adultos y una niña de 9 años, resultó ser una experiencia increíble con pasadizos, puertas y salas totalmente inesperados. Destaca por sus más de 200 m² de decorados hiperrealistas y pruebas directamente basadas en las películas, logrando una atmósfera de expedición arqueológica total. Los enigmas están magistralmente integrados, priorizando mecanismos electrónicos y un trabajo cooperativo que mantiene la adrenalina alta sin necesidad de terror. Una experiencia de exploración pura donde las transiciones entre zonas dejan al grupo boquiabierto.</t>
-  </si>
-  <si>
-    <t>Exorcista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terror Stories </t>
-  </si>
-  <si>
-    <t>Exorcismo / Posesión</t>
-  </si>
-  <si>
-    <t>https://terrorstories.com/barcelona/exorcista-escape-room</t>
-  </si>
-  <si>
-    <t>Homenaje visceral y cinematográfico al clásico del cine de posesiones. Jugado por 5 adultos en modo Terror (disponible también modo Aventura), resultó una experiencia de una intensidad asombrosa, aunque el espacio puede sentirse algo justo para un grupo de cinco. Destaca por una ambientación lúgubre y opresiva con efectos visuales y sonoros que recrean fenómenos paranormales impactantes. El punto más fuerte es el acting increíble de los Game Masters, con una mención especial a la interpretación de 'la niña', posiblemente la mejor actuación vista jamás en un escape room. Incluye dinámicas de separación total del grupo, dejando a los jugadores solos en momentos puntuales de máxima vulnerabilidad. Una pesadilla real con una puesta en escena inolvidable.</t>
-  </si>
-  <si>
-    <t>Jaipur</t>
-  </si>
-  <si>
-    <t>Bollywood / India</t>
-  </si>
-  <si>
-    <t>https://www.kadabraescape.com/el-secreto-de-jaipur/</t>
-  </si>
-  <si>
-    <t>Fantasía pura y colorista inspirada en el folclore de la India que rompe con la estética lúgubre tradicional. Jugado por 3 adultos y 3 niñas de 10-11 años, resultó una experiencia sumamente divertida donde las pequeñas no pararon ni un segundo de resolver retos. Destaca por una escenografía vibrante y una decoración preciosa, con olores característicos que te transportan a un mercado exótico. Los puzzles son muy táctiles e ingeniosos, huyendo de los clásicos candados para centrarse en mecanismos 'mágicos' que fluyen con naturalidad. Con una historia sólida y un sorprendente giro de argumento, es un espectáculo visual cargado de buen rollo donde el asombro y el ingenio son los protagonistas.</t>
-  </si>
-  <si>
-    <t>encryptroom</t>
-  </si>
-  <si>
-    <t>Encrypt</t>
-  </si>
-  <si>
-    <t>Asesino en serie</t>
-  </si>
-  <si>
-    <t>Tensión / Inmersivo</t>
-  </si>
-  <si>
-    <t>https://www.encryptroom.com/</t>
-  </si>
-  <si>
-    <t>Bank of Thaqar</t>
-  </si>
-  <si>
-    <t>MissionLeak</t>
-  </si>
-  <si>
-    <t>Atraco / Acción</t>
-  </si>
-  <si>
-    <t>Acción</t>
-  </si>
-  <si>
-    <t>https://www.missionleak.com/bankofthaqar</t>
-  </si>
-  <si>
-    <t>Referente de la 'vieja escuela' jugado originalmente en 2015. En su momento fue pionero en la temática de atracos, pero con la perspectiva actual de las salas de nueva generación, se siente una experiencia sencilla, lineal y muy basada en candados. Nota importante: Nuestra valoración se basa en la versión de hace años; desconocemos si ha recibido actualizaciones técnicas o de escenografía desde entonces. Comparado con los estándares inmersivos de 2026, palidece en espectacularidad y fluidez narrativa, quedando como una pieza de coleccionista para entender los inicios del sector. Lo hicimos 4 adultos</t>
-  </si>
-  <si>
-    <t>Roomions</t>
-  </si>
-  <si>
-    <t>https://virusroomescape.com/es/escape-room-calella-roomions/#reserva-roomions</t>
-  </si>
-  <si>
-    <t>Hoy hemos probado el escape room de Roomions y la experiencia ha sido muy positiva. Fuimos dos adultos y dos niños (6 y 10 años) y el juego funcionó perfecto para todos. El pequeño, en su primer escape room, participó mucho y salió encantado. La mayor, con experiencia, también lo disfrutó mucho. Es un room de tamaño contenido (una sala y media), pero muy bien aprovechado: no paras en ningún momento y todo fluye. Mención especial al Game Master, Edu (Nefario Jr.), que lo hizo genial. Muy recomendable: familiar y muy divertido.</t>
+    <t>Visitamos Tao Room Escape Virus Games en grupo de 8 (4 adultos y 4 niños de entre 6 y 10 años, algunos ya con experiencia en escape rooms). La experiencia seguramente cambia mucho según el tamaño del grupo: en nuestro caso, las salas se nos quedaron pequeñas y con pocos enigmas para tanta gente, lo que hizo que varios participantes se quedaran sin apenas intervenir. Es una pena, porque es un escape del que nos habían hablado muy bien y le teníamos muchas ganas. Aun así, nos dejó un poco fríos. Probablemente sea más disfrutable en grupos más reducidos (3-4 personas). No descartamos darle otra oportunidad en el futuro en ese formato.</t>
   </si>
 </sst>
 </file>
@@ -760,7 +760,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -824,7 +824,6 @@
     <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1056,7 +1055,7 @@
     <col customWidth="1" min="8" max="8" width="8.75"/>
     <col customWidth="1" min="9" max="9" width="61.75"/>
     <col customWidth="1" min="10" max="10" width="13.88"/>
-    <col customWidth="1" min="11" max="11" width="9.0"/>
+    <col customWidth="1" min="11" max="11" width="11.38"/>
     <col customWidth="1" min="12" max="12" width="370.5"/>
     <col customWidth="1" min="13" max="13" width="145.25"/>
   </cols>
@@ -1869,71 +1868,36 @@
         <v>137</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
+    <row r="23">
+      <c r="A23" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="F23" s="2">
+        <v>105.0</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="I23" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="J23" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="F24" s="2">
-        <v>90.0</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H24" s="17">
-        <v>46150.0</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="J24" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F25" s="2">
-        <v>105.0</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="J25" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="36">
@@ -1987,10 +1951,9 @@
     <hyperlink r:id="rId19" ref="I20"/>
     <hyperlink r:id="rId20" ref="I21"/>
     <hyperlink r:id="rId21" ref="I22"/>
-    <hyperlink r:id="rId22" ref="I24"/>
-    <hyperlink r:id="rId23" ref="I25"/>
+    <hyperlink r:id="rId22" ref="I23"/>
   </hyperlinks>
-  <drawing r:id="rId24"/>
+  <drawing r:id="rId23"/>
 </worksheet>
 </file>
 
@@ -2026,34 +1989,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="L1" s="20" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="M1" s="20" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="N1" s="20" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="O1" s="20" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="P1" s="20" t="s">
         <v>11</v>
@@ -2061,16 +2024,16 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>39</v>
@@ -2085,18 +2048,18 @@
         <v>9.0</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="J2" s="21">
         <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
-        <v>11544.75</v>
-      </c>
-      <c r="K2" s="22">
-        <f t="shared" ref="K2:K12" si="2">RANK(J2, $J$2:$J$22)</f>
+        <v>9.375</v>
+      </c>
+      <c r="K2" s="21">
+        <f t="shared" ref="K2:K13" si="2">RANK(J2, $J$2:$J$22)</f>
         <v>1</v>
       </c>
-      <c r="L2" s="17">
-        <v>46151.0</v>
+      <c r="L2" s="2">
+        <v>9.5</v>
       </c>
       <c r="M2" s="2">
         <v>10.0</v>
@@ -2108,21 +2071,21 @@
         <v>9.0</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>39</v>
@@ -2137,13 +2100,13 @@
         <v>46150.0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="J3" s="22">
+        <v>159</v>
+      </c>
+      <c r="J3" s="21">
         <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="21">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
@@ -2160,12 +2123,12 @@
         <v>7.0</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>21</v>
@@ -2189,425 +2152,478 @@
         <v>9.0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="J4" s="1">
         <v>0.0</v>
       </c>
-      <c r="K4" s="22">
+      <c r="K4" s="21">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F5" s="3">
+        <v>60.0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="J5" s="21">
+        <f t="shared" ref="J5:J13" si="3">AVERAGE(L5:O5)</f>
+        <v>9.25</v>
+      </c>
+      <c r="K5" s="21">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="L5" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="N5" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="O5" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="3">
+        <v>90.0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="J6" s="21">
+        <f t="shared" si="3"/>
+        <v>8.75</v>
+      </c>
+      <c r="K6" s="21">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="L6" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N6" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="O6" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="3">
+        <v>90.0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="4">
+        <v>46149.0</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="J7" s="21">
+        <f t="shared" si="3"/>
+        <v>8.25</v>
+      </c>
+      <c r="K7" s="21">
+        <f t="shared" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="L7" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N7" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="3">
+        <v>90.0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="4">
+        <v>46150.0</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="J8" s="21">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="K8" s="21">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="L8" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="M8" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N8" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="O8" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="3">
+        <v>80.0</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="4">
+        <v>46149.0</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="J9" s="21">
+        <f t="shared" si="3"/>
+        <v>8.5</v>
+      </c>
+      <c r="K9" s="21">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="L9" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="M9" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N9" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="O9" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="3">
+        <v>70.0</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="4">
+        <v>46149.0</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="J10" s="21">
+        <f t="shared" si="3"/>
+        <v>7.5</v>
+      </c>
+      <c r="K10" s="21">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="L10" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="M10" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="N10" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="O10" s="2">
+        <v>8.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F11" s="3">
+        <v>60.0</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="4">
+        <v>46148.0</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="J11" s="21">
+        <f t="shared" si="3"/>
+        <v>6.75</v>
+      </c>
+      <c r="K11" s="21">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F5" s="3">
-        <v>60.0</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="J5" s="22">
-        <f t="shared" ref="J5:J11" si="3">AVERAGE(L5:O5)</f>
-        <v>9.25</v>
-      </c>
-      <c r="K5" s="22">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="L5" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="J6" s="22">
-        <f t="shared" si="3"/>
-        <v>8.75</v>
-      </c>
-      <c r="K6" s="22">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="L6" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="O6" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="3">
-        <v>90.0</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="4">
-        <v>46149.0</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="J7" s="22">
+      <c r="L11" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="M11" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="N11" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="O11" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="2">
+        <v>75.0</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H12" s="17">
+        <v>46150.0</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="J12" s="21">
         <f t="shared" si="3"/>
         <v>8.25</v>
       </c>
-      <c r="K7" s="22">
+      <c r="K12" s="21">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L12" s="2">
         <v>8.0</v>
       </c>
-      <c r="M7" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="M12" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="N12" s="2">
         <v>8.0</v>
       </c>
-      <c r="O7" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="O12" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F13" s="2">
         <v>90.0</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="G13" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H13" s="17">
         <v>46150.0</v>
       </c>
-      <c r="I8" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="J8" s="22">
+      <c r="I13" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="J13" s="21">
         <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
-      <c r="K8" s="22">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="L8" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="O8" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="3">
-        <v>80.0</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="4">
-        <v>46149.0</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="J9" s="22">
-        <f t="shared" si="3"/>
-        <v>8.5</v>
-      </c>
-      <c r="K9" s="22">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="L9" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="M9" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="N9" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="O9" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="F10" s="3">
-        <v>70.0</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="4">
-        <v>46149.0</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="J10" s="22">
-        <f t="shared" si="3"/>
-        <v>7.5</v>
-      </c>
-      <c r="K10" s="22">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="L10" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="M10" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="N10" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="O10" s="2">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F11" s="3">
-        <v>60.0</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="4">
-        <v>46148.0</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="J11" s="22">
-        <f t="shared" si="3"/>
-        <v>6.75</v>
-      </c>
-      <c r="K11" s="22">
+        <v>7.375</v>
+      </c>
+      <c r="K13" s="21">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="L11" s="2">
+      <c r="L13" s="2">
         <v>7.0</v>
       </c>
-      <c r="M11" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="N11" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="O11" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F12" s="2">
-        <v>75.0</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H12" s="17">
-        <v>46150.0</v>
-      </c>
-      <c r="I12" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="J12" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="K12" s="22">
-        <f t="shared" si="2"/>
-        <v>7</v>
-      </c>
-      <c r="L12" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>46150.0</v>
-      </c>
-      <c r="N12" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="O12" s="17">
-        <v>46150.0</v>
-      </c>
-      <c r="P12" s="2" t="s">
+      <c r="M13" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="N13" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="O13" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>208</v>
       </c>
     </row>
@@ -2624,7 +2640,8 @@
     <hyperlink r:id="rId9" ref="I10"/>
     <hyperlink r:id="rId10" ref="I11"/>
     <hyperlink r:id="rId11" location="reserva-roomions" ref="I12"/>
+    <hyperlink r:id="rId12" ref="I13"/>
   </hyperlinks>
-  <drawing r:id="rId12"/>
+  <drawing r:id="rId13"/>
 </worksheet>
 </file>
--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="210">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -501,6 +501,9 @@
   </si>
   <si>
     <t>https://escapebarcelona.com/</t>
+  </si>
+  <si>
+    <t>Ambientación muy cuidada y sorprendente, lo mejor del escape. Requiere algo de agilidad física. Inicio algo duro: los primeros enigmas cuestan incluso con experiencia, pero luego fluye mejor.  Gran trabajo del GM como NPC, con buena tensión durante la partida. Ojo: zona complicada para aparcar.</t>
   </si>
   <si>
     <t>Jurásico</t>
@@ -2051,7 +2054,7 @@
         <v>154</v>
       </c>
       <c r="J2" s="21">
-        <f t="shared" ref="J2:J3" si="1">AVERAGE(L2:O2)</f>
+        <f t="shared" ref="J2:J13" si="1">AVERAGE(L2:O2)</f>
         <v>9.375</v>
       </c>
       <c r="K2" s="21">
@@ -2143,7 +2146,7 @@
         <v>55</v>
       </c>
       <c r="F4" s="3">
-        <v>75.0</v>
+        <v>120.0</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
@@ -2154,29 +2157,45 @@
       <c r="I4" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="J4" s="1">
-        <v>0.0</v>
+      <c r="J4" s="21">
+        <f t="shared" si="1"/>
+        <v>8.375</v>
       </c>
       <c r="K4" s="21">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="L4" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="M4" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="N4" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="O4" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F5" s="3">
         <v>60.0</v>
@@ -2188,10 +2207,10 @@
         <v>8.0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J5" s="21">
-        <f t="shared" ref="J5:J13" si="3">AVERAGE(L5:O5)</f>
+        <f t="shared" si="1"/>
         <v>9.25</v>
       </c>
       <c r="K5" s="21">
@@ -2211,24 +2230,24 @@
         <v>10.0</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F6" s="3">
         <v>90.0</v>
@@ -2240,10 +2259,10 @@
         <v>9.0</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J6" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8.75</v>
       </c>
       <c r="K6" s="21">
@@ -2263,21 +2282,21 @@
         <v>9.0</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>39</v>
@@ -2292,15 +2311,15 @@
         <v>46149.0</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J7" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8.25</v>
       </c>
       <c r="K7" s="21">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L7" s="2">
         <v>8.0</v>
@@ -2315,21 +2334,21 @@
         <v>8.0</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>113</v>
@@ -2344,15 +2363,15 @@
         <v>46150.0</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J8" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="K8" s="21">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L8" s="2">
         <v>8.0</v>
@@ -2367,12 +2386,12 @@
         <v>9.0</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>133</v>
@@ -2381,7 +2400,7 @@
         <v>134</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>39</v>
@@ -2396,10 +2415,10 @@
         <v>46149.0</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J9" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
       <c r="K9" s="21">
@@ -2419,24 +2438,24 @@
         <v>8.0</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F10" s="3">
         <v>70.0</v>
@@ -2448,15 +2467,15 @@
         <v>46149.0</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J10" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>7.5</v>
       </c>
       <c r="K10" s="21">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L10" s="2">
         <v>7.0</v>
@@ -2473,19 +2492,19 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F11" s="3">
         <v>60.0</v>
@@ -2497,15 +2516,15 @@
         <v>46148.0</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J11" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>6.75</v>
       </c>
       <c r="K11" s="21">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L11" s="2">
         <v>7.0</v>
@@ -2520,21 +2539,21 @@
         <v>6.0</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>140</v>
@@ -2543,27 +2562,27 @@
         <v>75.0</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H12" s="17">
         <v>46150.0</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J12" s="21">
-        <f t="shared" si="3"/>
-        <v>8.25</v>
+        <f t="shared" si="1"/>
+        <v>8.125</v>
       </c>
       <c r="K12" s="21">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L12" s="2">
         <v>8.0</v>
       </c>
       <c r="M12" s="2">
-        <v>8.5</v>
+        <v>8.0</v>
       </c>
       <c r="N12" s="2">
         <v>8.0</v>
@@ -2572,21 +2591,21 @@
         <v>8.5</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>140</v>
@@ -2595,21 +2614,21 @@
         <v>90.0</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H13" s="17">
         <v>46150.0</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J13" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>7.375</v>
       </c>
       <c r="K13" s="21">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L13" s="2">
         <v>7.0</v>
@@ -2624,7 +2643,7 @@
         <v>7.5</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -1,18 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Isaac\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9E5B55-A972-49BC-862F-427864AB6789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Pendientes" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Hechos" sheetId="2" r:id="rId6"/>
+    <sheet name="Pendientes" sheetId="1" r:id="rId1"/>
+    <sheet name="Hechos" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="215">
   <si>
     <t>Nombre del Escape</t>
   </si>
@@ -642,97 +665,135 @@
   </si>
   <si>
     <t>Visitamos Tao Room Escape Virus Games en grupo de 8 (4 adultos y 4 niños de entre 6 y 10 años, algunos ya con experiencia en escape rooms). La experiencia seguramente cambia mucho según el tamaño del grupo: en nuestro caso, las salas se nos quedaron pequeñas y con pocos enigmas para tanta gente, lo que hizo que varios participantes se quedaran sin apenas intervenir. Es una pena, porque es un escape del que nos habían hablado muy bien y le teníamos muchas ganas. Aun así, nos dejó un poco fríos. Probablemente sea más disfrutable en grupos más reducidos (3-4 personas). No descartamos darle otra oportunidad en el futuro en ese formato.</t>
+  </si>
+  <si>
+    <t>El secreto de los Krugger</t>
+  </si>
+  <si>
+    <t>Insomnia Corp.</t>
+  </si>
+  <si>
+    <t>Berga</t>
+  </si>
+  <si>
+    <t>https://www.insomniacorp.com/escapes/secreto-krugger</t>
+  </si>
+  <si>
+    <t>Fuimos a vivir la experiencia de El Secreto de los Krugger y salimos convencidos de que una sola vez no es suficiente.
+Éramos dos parejas y cogimos una habitación por pareja, así que pudimos jugar dos experiencias distintas: Xperiment y Aradia.
+Xperiment nos pareció una auténtica barbaridad: enorme, súper inmersiva y muy disfrutable. Conseguimos salir en unos 70-75 minutos. Después hicimos los cuatro juntos Aradia y llegamos por los pelos… incluso teniendo que mirar alguna prueba en el papel de ayuda (sí, losers). Aun así, las dos horas volaron. Cuesta entender cómo se le puede sacar tantísimo partido a unas habitaciones. Ambientaciones brutales.
+Luego llegó la cena tematizada con espectáculo, que ya fue otro nivel… y para rematar, el auténtico “escape de los escapes”: todo el hotel abierto, corriendo por pasillos, persecuciones, sustos y una tensión constante espectacular.
+De los 22 juegos no conseguimos verlo todo: resolvimos unos 10 y llegaríamos a ver unos 16-18 aproximadamente.
+Sinceramente, dudo que podamos vivir una experiencia de terror mejor que la que ofrece Krugger. Una auténtica pasada.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d.m"/>
+    <numFmt numFmtId="164" formatCode="d\.m"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -740,11 +801,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -758,90 +825,62 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="24">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -849,7 +888,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1039,31 +1078,34 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="39.88"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="3" width="7.25"/>
-    <col customWidth="1" min="4" max="4" width="8.63"/>
-    <col customWidth="1" min="6" max="6" width="6.13"/>
-    <col customWidth="1" min="7" max="7" width="7.0"/>
-    <col customWidth="1" min="8" max="8" width="8.75"/>
-    <col customWidth="1" min="9" max="9" width="61.75"/>
-    <col customWidth="1" min="10" max="10" width="13.88"/>
-    <col customWidth="1" min="11" max="11" width="11.38"/>
-    <col customWidth="1" min="12" max="12" width="370.5"/>
-    <col customWidth="1" min="13" max="13" width="145.25"/>
+    <col min="1" max="1" width="39.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="7.21875" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="8.77734375" customWidth="1"/>
+    <col min="9" max="9" width="61.77734375" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" customWidth="1"/>
+    <col min="11" max="11" width="11.33203125" customWidth="1"/>
+    <col min="12" max="12" width="370.44140625" customWidth="1"/>
+    <col min="13" max="13" width="145.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1101,7 +1143,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -1118,28 +1160,28 @@
         <v>16</v>
       </c>
       <c r="F2" s="3">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="4">
-        <v>46062.0</v>
+        <v>46062</v>
       </c>
       <c r="I2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K2" s="2">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1156,28 +1198,28 @@
         <v>24</v>
       </c>
       <c r="F3" s="3">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H3" s="4">
-        <v>46090.0</v>
+        <v>46090</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K3" s="7">
-        <v>55.0</v>
+        <v>55</v>
       </c>
       <c r="L3" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -1194,26 +1236,26 @@
         <v>32</v>
       </c>
       <c r="F4" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="4">
-        <v>46273.0</v>
+        <v>46273</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J4" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
@@ -1230,28 +1272,28 @@
         <v>39</v>
       </c>
       <c r="F5" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="4">
-        <v>46211.0</v>
+        <v>46211</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>40</v>
       </c>
       <c r="J5" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K5" s="2">
-        <v>78.0</v>
+        <v>78</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
@@ -1268,26 +1310,26 @@
         <v>16</v>
       </c>
       <c r="F6" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H6" s="4">
-        <v>46150.0</v>
+        <v>46150</v>
       </c>
       <c r="I6" s="5" t="s">
         <v>44</v>
       </c>
       <c r="J6" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -1304,26 +1346,26 @@
         <v>39</v>
       </c>
       <c r="F7" s="3">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="4">
-        <v>46241.0</v>
+        <v>46241</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>49</v>
       </c>
       <c r="J7" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>51</v>
       </c>
@@ -1340,26 +1382,26 @@
         <v>55</v>
       </c>
       <c r="F8" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H8" s="4">
-        <v>46149.0</v>
+        <v>46149</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>57</v>
       </c>
       <c r="J8" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>59</v>
       </c>
@@ -1376,26 +1418,26 @@
         <v>16</v>
       </c>
       <c r="F9" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H9" s="4">
-        <v>46061.0</v>
+        <v>46061</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>62</v>
       </c>
       <c r="J9" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>64</v>
       </c>
@@ -1412,26 +1454,26 @@
         <v>67</v>
       </c>
       <c r="F10" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H10" s="4">
-        <v>46030.0</v>
+        <v>46030</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>68</v>
       </c>
       <c r="J10" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>70</v>
       </c>
@@ -1448,26 +1490,26 @@
         <v>39</v>
       </c>
       <c r="F11" s="3">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="3">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>72</v>
       </c>
       <c r="J11" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>74</v>
       </c>
@@ -1484,26 +1526,26 @@
         <v>39</v>
       </c>
       <c r="F12" s="3">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H12" s="4">
-        <v>46061.0</v>
+        <v>46061</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>77</v>
       </c>
       <c r="J12" s="1">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>79</v>
       </c>
@@ -1520,26 +1562,26 @@
         <v>83</v>
       </c>
       <c r="F13" s="3">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H13" s="4">
-        <v>46090.0</v>
+        <v>46090</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>84</v>
       </c>
       <c r="J13" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>86</v>
       </c>
@@ -1556,26 +1598,26 @@
         <v>88</v>
       </c>
       <c r="F14" s="3">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H14" s="3">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>89</v>
       </c>
       <c r="J14" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>91</v>
       </c>
@@ -1592,26 +1634,26 @@
         <v>93</v>
       </c>
       <c r="F15" s="3">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H15" s="4">
-        <v>46150.0</v>
+        <v>46150</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>94</v>
       </c>
       <c r="J15" s="1">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>96</v>
       </c>
@@ -1628,26 +1670,26 @@
         <v>99</v>
       </c>
       <c r="F16" s="3">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="4">
-        <v>46150.0</v>
+        <v>46150</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>100</v>
       </c>
       <c r="J16" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:12" ht="15.75" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>102</v>
       </c>
@@ -1664,28 +1706,28 @@
         <v>106</v>
       </c>
       <c r="F17" s="11">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G17" s="11" t="s">
         <v>25</v>
       </c>
       <c r="H17" s="12">
-        <v>46212.0</v>
+        <v>46212</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>107</v>
       </c>
       <c r="J17" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K17" s="1">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="L17" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:12" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>109</v>
       </c>
@@ -1702,28 +1744,28 @@
         <v>113</v>
       </c>
       <c r="F18" s="2">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="12">
-        <v>46243.0</v>
+        <v>46243</v>
       </c>
       <c r="I18" s="14" t="s">
         <v>114</v>
       </c>
       <c r="J18" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K18" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:12" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>116</v>
       </c>
@@ -1740,28 +1782,28 @@
         <v>119</v>
       </c>
       <c r="F19" s="2">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H19" s="15">
-        <v>46182.0</v>
+        <v>46182</v>
       </c>
       <c r="I19" s="14" t="s">
         <v>120</v>
       </c>
       <c r="J19" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K19" s="1">
-        <v>113.0</v>
+        <v>113</v>
       </c>
       <c r="L19" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:12" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>122</v>
       </c>
@@ -1778,26 +1820,26 @@
         <v>39</v>
       </c>
       <c r="F20" s="2">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>46062.0</v>
+        <v>46062</v>
       </c>
       <c r="I20" s="14" t="s">
         <v>124</v>
       </c>
       <c r="J20" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:12" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>126</v>
       </c>
@@ -1814,26 +1856,26 @@
         <v>113</v>
       </c>
       <c r="F21" s="2">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>129</v>
       </c>
       <c r="H21" s="15">
-        <v>46121.0</v>
+        <v>46121</v>
       </c>
       <c r="I21" s="14" t="s">
         <v>130</v>
       </c>
       <c r="J21" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:12" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>132</v>
       </c>
@@ -1850,28 +1892,28 @@
         <v>135</v>
       </c>
       <c r="F22" s="2">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="17">
-        <v>46212.0</v>
+        <v>46212</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>136</v>
       </c>
       <c r="J22" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="K22" s="2">
-        <v>95.0</v>
+        <v>95</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:12">
       <c r="A23" s="2" t="s">
         <v>138</v>
       </c>
@@ -1885,97 +1927,99 @@
         <v>140</v>
       </c>
       <c r="F23" s="2">
-        <v>105.0</v>
+        <v>105</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H23" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I23" s="14" t="s">
         <v>141</v>
       </c>
       <c r="J23" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:5" ht="13.2">
       <c r="A36" s="16"/>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" ht="13.2">
       <c r="A37" s="19"/>
       <c r="B37" s="15"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
       <c r="E37" s="16"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:5" ht="13.2">
       <c r="A38" s="19"/>
       <c r="B38" s="15"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:5" ht="13.2">
       <c r="A39" s="19"/>
       <c r="D39" s="16"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:5" ht="13.2">
       <c r="A40" s="19"/>
       <c r="D40" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="I2"/>
-    <hyperlink r:id="rId2" ref="I3"/>
-    <hyperlink r:id="rId3" ref="I4"/>
-    <hyperlink r:id="rId4" ref="I5"/>
-    <hyperlink r:id="rId5" ref="I6"/>
-    <hyperlink r:id="rId6" ref="I7"/>
-    <hyperlink r:id="rId7" ref="I8"/>
-    <hyperlink r:id="rId8" ref="I9"/>
-    <hyperlink r:id="rId9" ref="I10"/>
-    <hyperlink r:id="rId10" ref="I11"/>
-    <hyperlink r:id="rId11" ref="I12"/>
-    <hyperlink r:id="rId12" ref="I13"/>
-    <hyperlink r:id="rId13" ref="I14"/>
-    <hyperlink r:id="rId14" ref="I15"/>
-    <hyperlink r:id="rId15" ref="I16"/>
-    <hyperlink r:id="rId16" ref="I17"/>
-    <hyperlink r:id="rId17" ref="I18"/>
-    <hyperlink r:id="rId18" ref="I19"/>
-    <hyperlink r:id="rId19" ref="I20"/>
-    <hyperlink r:id="rId20" ref="I21"/>
-    <hyperlink r:id="rId21" ref="I22"/>
-    <hyperlink r:id="rId22" ref="I23"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="I11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="I12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="I17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="I19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="I20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="I21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="I22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="I23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
   </hyperlinks>
-  <drawing r:id="rId23"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.63"/>
-    <col customWidth="1" min="9" max="9" width="36.13"/>
-    <col customWidth="1" min="10" max="10" width="14.25"/>
-    <col customWidth="1" min="11" max="11" width="14.13"/>
-    <col customWidth="1" min="12" max="15" width="11.75"/>
-    <col customWidth="1" min="16" max="16" width="166.0"/>
+    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="9" max="9" width="36.109375" customWidth="1"/>
+    <col min="10" max="10" width="14.21875" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" customWidth="1"/>
+    <col min="12" max="15" width="11.77734375" customWidth="1"/>
+    <col min="16" max="16" width="166" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:16">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -2025,7 +2069,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:16" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>151</v>
       </c>
@@ -2042,42 +2086,42 @@
         <v>39</v>
       </c>
       <c r="F2" s="3">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>154</v>
       </c>
       <c r="J2" s="21">
-        <f t="shared" ref="J2:J13" si="1">AVERAGE(L2:O2)</f>
+        <f t="shared" ref="J2:J13" si="0">AVERAGE(L2:O2)</f>
         <v>9.375</v>
       </c>
       <c r="K2" s="21">
-        <f t="shared" ref="K2:K13" si="2">RANK(J2, $J$2:$J$22)</f>
-        <v>1</v>
+        <f t="shared" ref="K2:K14" si="1">RANK(J2, $J$2:$J$22)</f>
+        <v>2</v>
       </c>
       <c r="L2" s="2">
         <v>9.5</v>
       </c>
       <c r="M2" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N2" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="O2" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:16" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>156</v>
       </c>
@@ -2094,42 +2138,42 @@
         <v>39</v>
       </c>
       <c r="F3" s="3">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H3" s="4">
-        <v>46150.0</v>
+        <v>46150</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>159</v>
       </c>
       <c r="J3" s="21">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="K3" s="21">
         <f t="shared" si="1"/>
-        <v>8.5</v>
-      </c>
-      <c r="K3" s="21">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="M3" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="N3" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="O3" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:16" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>161</v>
       </c>
@@ -2146,42 +2190,42 @@
         <v>55</v>
       </c>
       <c r="F4" s="3">
-        <v>120.0</v>
+        <v>120</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>162</v>
       </c>
       <c r="J4" s="21">
+        <f t="shared" si="0"/>
+        <v>8.375</v>
+      </c>
+      <c r="K4" s="21">
         <f t="shared" si="1"/>
-        <v>8.375</v>
-      </c>
-      <c r="K4" s="21">
-        <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" s="2">
         <v>8.5</v>
       </c>
       <c r="M4" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="N4" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="O4" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="P4" s="2" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>164</v>
       </c>
@@ -2198,42 +2242,42 @@
         <v>167</v>
       </c>
       <c r="F5" s="3">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H5" s="3">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>168</v>
       </c>
       <c r="J5" s="21">
+        <f t="shared" si="0"/>
+        <v>9.25</v>
+      </c>
+      <c r="K5" s="21">
         <f t="shared" si="1"/>
-        <v>9.25</v>
-      </c>
-      <c r="K5" s="21">
-        <f t="shared" si="2"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="N5" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="O5" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:16" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>170</v>
       </c>
@@ -2250,42 +2294,42 @@
         <v>173</v>
       </c>
       <c r="F6" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="3">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>174</v>
       </c>
       <c r="J6" s="21">
+        <f t="shared" si="0"/>
+        <v>8.75</v>
+      </c>
+      <c r="K6" s="21">
         <f t="shared" si="1"/>
-        <v>8.75</v>
-      </c>
-      <c r="K6" s="21">
-        <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="M6" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="N6" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="O6" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:16" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>176</v>
       </c>
@@ -2302,42 +2346,42 @@
         <v>39</v>
       </c>
       <c r="F7" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H7" s="4">
-        <v>46149.0</v>
+        <v>46149</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>178</v>
       </c>
       <c r="J7" s="21">
+        <f t="shared" si="0"/>
+        <v>8.25</v>
+      </c>
+      <c r="K7" s="21">
         <f t="shared" si="1"/>
-        <v>8.25</v>
-      </c>
-      <c r="K7" s="21">
-        <f t="shared" si="2"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L7" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="M7" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="N7" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="O7" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:16" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>180</v>
       </c>
@@ -2354,42 +2398,42 @@
         <v>113</v>
       </c>
       <c r="F8" s="3">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="4">
-        <v>46150.0</v>
+        <v>46150</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>183</v>
       </c>
       <c r="J8" s="21">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="K8" s="21">
         <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="L8" s="2">
         <v>8</v>
       </c>
-      <c r="K8" s="21">
-        <f t="shared" si="2"/>
+      <c r="M8" s="2">
+        <v>8</v>
+      </c>
+      <c r="N8" s="2">
+        <v>7</v>
+      </c>
+      <c r="O8" s="2">
         <v>9</v>
-      </c>
-      <c r="L8" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="M8" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="N8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="O8" s="2">
-        <v>9.0</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:16" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>185</v>
       </c>
@@ -2406,42 +2450,42 @@
         <v>39</v>
       </c>
       <c r="F9" s="3">
-        <v>80.0</v>
+        <v>80</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H9" s="4">
-        <v>46149.0</v>
+        <v>46149</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>187</v>
       </c>
       <c r="J9" s="21">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="K9" s="21">
         <f t="shared" si="1"/>
-        <v>8.5</v>
-      </c>
-      <c r="K9" s="21">
-        <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="M9" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="N9" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="O9" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:16" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>189</v>
       </c>
@@ -2458,39 +2502,39 @@
         <v>192</v>
       </c>
       <c r="F10" s="3">
-        <v>70.0</v>
+        <v>70</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="4">
-        <v>46149.0</v>
+        <v>46149</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>193</v>
       </c>
       <c r="J10" s="21">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="K10" s="21">
         <f t="shared" si="1"/>
-        <v>7.5</v>
-      </c>
-      <c r="K10" s="21">
-        <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L10" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="M10" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="N10" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="O10" s="2">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>194</v>
       </c>
@@ -2507,42 +2551,42 @@
         <v>197</v>
       </c>
       <c r="F11" s="3">
-        <v>60.0</v>
+        <v>60</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="4">
-        <v>46148.0</v>
+        <v>46148</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>198</v>
       </c>
       <c r="J11" s="21">
+        <f t="shared" si="0"/>
+        <v>6.75</v>
+      </c>
+      <c r="K11" s="21">
         <f t="shared" si="1"/>
-        <v>6.75</v>
-      </c>
-      <c r="K11" s="21">
-        <f t="shared" si="2"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L11" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="M11" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="N11" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="O11" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:16">
       <c r="A12" s="2" t="s">
         <v>200</v>
       </c>
@@ -2559,33 +2603,33 @@
         <v>140</v>
       </c>
       <c r="F12" s="2">
-        <v>75.0</v>
+        <v>75</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>204</v>
       </c>
       <c r="H12" s="17">
-        <v>46150.0</v>
+        <v>46150</v>
       </c>
       <c r="I12" s="14" t="s">
         <v>205</v>
       </c>
       <c r="J12" s="21">
+        <f t="shared" si="0"/>
+        <v>8.125</v>
+      </c>
+      <c r="K12" s="21">
         <f t="shared" si="1"/>
-        <v>8.125</v>
-      </c>
-      <c r="K12" s="21">
-        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="L12" s="2">
         <v>8</v>
       </c>
-      <c r="L12" s="2">
-        <v>8.0</v>
-      </c>
       <c r="M12" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="N12" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="O12" s="2">
         <v>8.5</v>
@@ -2594,7 +2638,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:16">
       <c r="A13" s="2" t="s">
         <v>207</v>
       </c>
@@ -2611,27 +2655,27 @@
         <v>140</v>
       </c>
       <c r="F13" s="2">
-        <v>90.0</v>
+        <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>204</v>
       </c>
       <c r="H13" s="17">
-        <v>46150.0</v>
+        <v>46150</v>
       </c>
       <c r="I13" s="14" t="s">
         <v>208</v>
       </c>
       <c r="J13" s="21">
+        <f t="shared" si="0"/>
+        <v>7.375</v>
+      </c>
+      <c r="K13" s="21">
         <f t="shared" si="1"/>
-        <v>7.375</v>
-      </c>
-      <c r="K13" s="21">
-        <f t="shared" si="2"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L13" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="M13" s="2">
         <v>7.5</v>
@@ -2646,21 +2690,73 @@
         <v>209</v>
       </c>
     </row>
+    <row r="14" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" s="3">
+        <v>360</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="4">
+        <v>10</v>
+      </c>
+      <c r="I14" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="J14">
+        <v>10</v>
+      </c>
+      <c r="K14" s="21">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L14" s="2">
+        <v>10</v>
+      </c>
+      <c r="M14" s="2">
+        <v>10</v>
+      </c>
+      <c r="N14" s="2">
+        <v>10</v>
+      </c>
+      <c r="O14" s="2">
+        <v>10</v>
+      </c>
+      <c r="P14" s="23" t="s">
+        <v>214</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="I2"/>
-    <hyperlink r:id="rId2" ref="I3"/>
-    <hyperlink r:id="rId3" ref="I4"/>
-    <hyperlink r:id="rId4" ref="I5"/>
-    <hyperlink r:id="rId5" ref="I6"/>
-    <hyperlink r:id="rId6" ref="I7"/>
-    <hyperlink r:id="rId7" ref="I8"/>
-    <hyperlink r:id="rId8" ref="I9"/>
-    <hyperlink r:id="rId9" ref="I10"/>
-    <hyperlink r:id="rId10" ref="I11"/>
-    <hyperlink r:id="rId11" location="reserva-roomions" ref="I12"/>
-    <hyperlink r:id="rId12" ref="I13"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
+    <hyperlink ref="I10" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
+    <hyperlink ref="I11" r:id="rId10" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
+    <hyperlink ref="I12" r:id="rId11" location="reserva-roomions" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
+    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{E4DAB110-E83E-4DEC-A2CC-8650550F459C}"/>
   </hyperlinks>
-  <drawing r:id="rId13"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Isaac\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA9E5B55-A972-49BC-862F-427864AB6789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11BD1A3-449A-41B9-83CA-F1AC10BA101D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1913,7 +1913,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" ht="13.2">
       <c r="A23" s="2" t="s">
         <v>138</v>
       </c>
@@ -2019,7 +2019,7 @@
     <col min="16" max="16" width="166" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" ht="14.4">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" ht="13.2">
       <c r="A12" s="2" t="s">
         <v>200</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" ht="13.2">
       <c r="A13" s="2" t="s">
         <v>207</v>
       </c>
@@ -2712,7 +2712,7 @@
       <c r="G14" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="3">
         <v>10</v>
       </c>
       <c r="I14" s="22" t="s">

--- a/escape_rooms_tracker_mejorado.xlsx
+++ b/escape_rooms_tracker_mejorado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Isaac\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11BD1A3-449A-41B9-83CA-F1AC10BA101D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417E6A7B-F4EF-443A-B82A-EEA14937354F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pendientes" sheetId="1" r:id="rId1"/>
@@ -82,9 +82,6 @@
     <t>Sabadell</t>
   </si>
   <si>
-    <t>Piratas / tesoro</t>
-  </si>
-  <si>
     <t>Aventura inmersiva</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
   </si>
   <si>
     <t>https://willyeltuertoescaperoom.com/</t>
-  </si>
-  <si>
-    <t>Aclamado como una de las mejores aventuras piratas de España, destacando por una escenografía espectacular que parece sacada de un parque temático. Los usuarios elogian su inmersión total en la búsqueda del tesoro y una ambientación "de 10" que te hace sentir dentro de una película de los Goonies. Top Mundial Terpeca (varios años). Ganador de premios nacionales a Mejor Escenografía y Mejor Sala de Aventura.</t>
   </si>
   <si>
     <t>Cybercity 2049</t>
@@ -685,6 +679,17 @@
 Luego llegó la cena tematizada con espectáculo, que ya fue otro nivel… y para rematar, el auténtico “escape de los escapes”: todo el hotel abierto, corriendo por pasillos, persecuciones, sustos y una tensión constante espectacular.
 De los 22 juegos no conseguimos verlo todo: resolvimos unos 10 y llegaríamos a ver unos 16-18 aproximadamente.
 Sinceramente, dudo que podamos vivir una experiencia de terror mejor que la que ofrece Krugger. Una auténtica pasada.</t>
+  </si>
+  <si>
+    <t>Piratas / tesoro / Goonies</t>
+  </si>
+  <si>
+    <t>Este fin de semana visitamos **Willy el Tuerto** en familia (2 adultos y dos peques de 10 y 6 años) y lo pasamos en grande.
+Un consejo: si podéis, ved **Los Goonies** unos días antes. Nosotros lo hicimos y ayuda muchísimo a entrar en el ambiente y disfrutar de todos los guiños que esconde el juego.
+La ambientación está muy conseguida, especialmente teniendo en cuenta que es una sala con unos años a sus espaldas. Está llena de referencias a la película y transmite perfectamente ese espíritu de aventura y búsqueda del tesoro.
+En cuanto a jugadores, para nosotros 4 personas fue el número ideal. Todos participamos activamente en las pruebas y nadie se quedó mirando. Con grupos más grandes quizá podría quedarse algo corto.
+Entre la introducción, la partida y la charla final con el GM estuvimos cerca de una hora y media disfrutando de la experiencia.
+Un escape room muy recomendable para familias y para cualquier fan de **Los Goonies**. ¡Los Goonies nunca dicen muerto!</t>
   </si>
 </sst>
 </file>
@@ -1088,7 +1093,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="39.88671875" customWidth="1"/>
@@ -1145,809 +1150,778 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H2" s="4">
-        <v>46062</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>18</v>
+        <v>46090</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="J2" s="1">
         <v>6</v>
       </c>
-      <c r="K2" s="2">
-        <v>71</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>19</v>
+      <c r="K2" s="7">
+        <v>55</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="3">
+        <v>90</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="3">
-        <v>120</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="H3" s="4">
-        <v>46090</v>
+        <v>46273</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J3" s="1">
         <v>6</v>
       </c>
-      <c r="K3" s="7">
-        <v>55</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>27</v>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F4" s="3">
         <v>90</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H4" s="4">
-        <v>46273</v>
+        <v>46211</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J4" s="1">
-        <v>6</v>
-      </c>
-      <c r="K4" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="K4" s="2">
+        <v>78</v>
+      </c>
       <c r="L4" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3">
         <v>90</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H5" s="4">
-        <v>46211</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>40</v>
+        <v>46150</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="J5" s="1">
         <v>7</v>
       </c>
-      <c r="K5" s="2">
-        <v>78</v>
-      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="3">
+        <v>120</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="3">
-        <v>90</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="H6" s="4">
-        <v>46150</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>44</v>
+        <v>46241</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="J6" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F7" s="3">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="H7" s="4">
-        <v>46241</v>
+        <v>46149</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J7" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3">
         <v>90</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="H8" s="4">
-        <v>46149</v>
+        <v>46061</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="J8" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="F9" s="3">
         <v>90</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="H9" s="4">
-        <v>46061</v>
+        <v>46030</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="J9" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>64</v>
+      <c r="A10" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="F10" s="3">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="4">
-        <v>46030</v>
+        <v>16</v>
+      </c>
+      <c r="H10" s="3">
+        <v>6</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="J10" s="1">
-        <v>6</v>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="s">
-        <v>69</v>
+        <v>10</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A11" s="8" t="s">
-        <v>70</v>
+      <c r="A11" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" s="3">
-        <v>6</v>
+        <v>16</v>
+      </c>
+      <c r="H11" s="4">
+        <v>46061</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J11" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="F12" s="3">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H12" s="4">
-        <v>46061</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>77</v>
+        <v>46090</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>82</v>
       </c>
       <c r="J12" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>79</v>
+      <c r="A13" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="3">
         <v>80</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" s="3">
-        <v>120</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="4">
-        <v>46090</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="1">
+        <v>16</v>
+      </c>
+      <c r="H13" s="3">
         <v>7</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="2">
+        <v>6</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>86</v>
+      <c r="A14" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F14" s="3">
         <v>80</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="3">
-        <v>7</v>
+        <v>16</v>
+      </c>
+      <c r="H14" s="4">
+        <v>46150</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="J14" s="2">
-        <v>6</v>
+        <v>92</v>
+      </c>
+      <c r="J14" s="1">
+        <v>10</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F15" s="3">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="H15" s="4">
         <v>46150</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J15" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F16" s="3">
+      <c r="A16" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F16" s="11">
         <v>120</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="H16" s="4">
-        <v>46150</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J16" s="1">
-        <v>8</v>
-      </c>
-      <c r="K16" s="1"/>
+      <c r="G16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="12">
+        <v>46212</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="J16" s="2">
+        <v>6</v>
+      </c>
+      <c r="K16" s="1">
+        <v>19</v>
+      </c>
       <c r="L16" s="1" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A17" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="F17" s="11">
+      <c r="A17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F17" s="2">
         <v>120</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H17" s="12">
-        <v>46212</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>107</v>
+        <v>46243</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="J17" s="2">
         <v>6</v>
       </c>
-      <c r="K17" s="1">
-        <v>19</v>
+      <c r="K17" s="2">
+        <v>12</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="D18" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F18" s="2">
+        <v>80</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H18" s="15">
+        <v>46182</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="J18" s="2">
+        <v>7</v>
+      </c>
+      <c r="K18" s="1">
         <v>113</v>
       </c>
-      <c r="F18" s="2">
-        <v>120</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="12">
-        <v>46243</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="2">
-        <v>6</v>
-      </c>
-      <c r="K18" s="2">
-        <v>12</v>
-      </c>
       <c r="L18" s="1" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>119</v>
+        <v>28</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F19" s="2">
-        <v>80</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>56</v>
+        <v>75</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>16</v>
       </c>
       <c r="H19" s="15">
-        <v>46182</v>
+        <v>46062</v>
       </c>
       <c r="I19" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J19" s="2">
-        <v>7</v>
-      </c>
-      <c r="K19" s="1">
-        <v>113</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="K19" s="1"/>
       <c r="L19" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>39</v>
+        <v>126</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="F20" s="2">
         <v>75</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>17</v>
+        <v>127</v>
       </c>
       <c r="H20" s="15">
-        <v>46062</v>
+        <v>46121</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="J20" s="2">
         <v>6</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>128</v>
+        <v>130</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="F21" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="H21" s="15">
-        <v>46121</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>130</v>
+        <v>16</v>
+      </c>
+      <c r="H21" s="17">
+        <v>46212</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>134</v>
       </c>
       <c r="J21" s="2">
-        <v>6</v>
-      </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="15.75" customHeight="1">
+        <v>7</v>
+      </c>
+      <c r="K21" s="2">
+        <v>95</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="13.2">
       <c r="A22" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="B22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F22" s="2">
-        <v>80</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="17">
-        <v>46212</v>
-      </c>
-      <c r="I22" s="18" t="s">
-        <v>136</v>
+        <v>105</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="2">
+        <v>9</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>139</v>
       </c>
       <c r="J22" s="2">
         <v>7</v>
       </c>
-      <c r="K22" s="2">
-        <v>95</v>
-      </c>
       <c r="L22" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="13.2">
-      <c r="A23" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="F23" s="2">
-        <v>105</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="2">
-        <v>9</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="J23" s="2">
-        <v>7</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>142</v>
-      </c>
+    </row>
+    <row r="35" spans="1:5" ht="13.2">
+      <c r="A35" s="16"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
     </row>
     <row r="36" spans="1:5" ht="13.2">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
+      <c r="A36" s="19"/>
+      <c r="B36" s="15"/>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="16"/>
@@ -1957,46 +1931,38 @@
       <c r="B37" s="15"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
     </row>
     <row r="38" spans="1:5" ht="13.2">
       <c r="A38" s="19"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="16"/>
       <c r="D38" s="16"/>
     </row>
     <row r="39" spans="1:5" ht="13.2">
       <c r="A39" s="19"/>
       <c r="D39" s="16"/>
     </row>
-    <row r="40" spans="1:5" ht="13.2">
-      <c r="A40" s="19"/>
-      <c r="D40" s="16"/>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="I6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="I7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="I8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="I9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="I10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="I11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="I12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="I14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="I16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="I17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="I18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="I19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="I20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="I21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="I22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="I23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="I3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="I4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="I5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="I6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="I7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="I8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="I9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="I10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="I11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="I12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="I14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="I16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="I17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="I18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="I19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="I20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="I21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="I22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2007,11 +1973,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" customWidth="1"/>
+    <col min="5" max="5" width="16.21875" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" customWidth="1"/>
     <col min="9" max="9" width="36.109375" customWidth="1"/>
     <col min="10" max="10" width="14.21875" customWidth="1"/>
     <col min="11" max="11" width="14.109375" customWidth="1"/>
@@ -2036,34 +2005,34 @@
         <v>4</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="K1" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="L1" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="M1" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>148</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="O1" s="20" t="s">
-        <v>150</v>
       </c>
       <c r="P1" s="20" t="s">
         <v>11</v>
@@ -2071,38 +2040,38 @@
     </row>
     <row r="2" spans="1:16" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3">
         <v>70</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" s="3">
         <v>9</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J2" s="21">
         <f t="shared" ref="J2:J13" si="0">AVERAGE(L2:O2)</f>
         <v>9.375</v>
       </c>
       <c r="K2" s="21">
-        <f t="shared" ref="K2:K14" si="1">RANK(J2, $J$2:$J$22)</f>
+        <f t="shared" ref="K2:K15" si="1">RANK(J2, $J$2:$J$22)</f>
         <v>2</v>
       </c>
       <c r="L2" s="2">
@@ -2118,36 +2087,36 @@
         <v>9</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F3" s="3">
         <v>60</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="4">
         <v>46150</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J3" s="21">
         <f t="shared" si="0"/>
@@ -2170,36 +2139,36 @@
         <v>7</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3">
         <v>120</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H4" s="3">
         <v>9</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J4" s="21">
         <f t="shared" si="0"/>
@@ -2222,36 +2191,36 @@
         <v>8</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>167</v>
       </c>
       <c r="F5" s="3">
         <v>60</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H5" s="3">
         <v>8</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J5" s="21">
         <f t="shared" si="0"/>
@@ -2274,36 +2243,36 @@
         <v>10</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>173</v>
       </c>
       <c r="F6" s="3">
         <v>90</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H6" s="3">
         <v>9</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="J6" s="21">
         <f t="shared" si="0"/>
@@ -2326,36 +2295,36 @@
         <v>9</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F7" s="3">
         <v>90</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H7" s="4">
         <v>46149</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J7" s="21">
         <f t="shared" si="0"/>
@@ -2378,36 +2347,36 @@
         <v>8</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F8" s="3">
         <v>90</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H8" s="4">
         <v>46150</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="0"/>
@@ -2430,36 +2399,36 @@
         <v>9</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F9" s="3">
         <v>80</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H9" s="4">
         <v>46149</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="J9" s="21">
         <f t="shared" si="0"/>
@@ -2482,36 +2451,36 @@
         <v>8</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>192</v>
       </c>
       <c r="F10" s="3">
         <v>70</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H10" s="4">
         <v>46149</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J10" s="21">
         <f t="shared" si="0"/>
@@ -2536,31 +2505,31 @@
     </row>
     <row r="11" spans="1:16" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="E11" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="F11" s="3">
         <v>60</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" s="4">
         <v>46148</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J11" s="21">
         <f t="shared" si="0"/>
@@ -2583,36 +2552,36 @@
         <v>6</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="13.2">
       <c r="A12" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F12" s="2">
         <v>75</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H12" s="17">
         <v>46150</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="J12" s="21">
         <f t="shared" si="0"/>
@@ -2635,36 +2604,36 @@
         <v>8.5</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="13.2">
       <c r="A13" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F13" s="2">
         <v>90</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H13" s="17">
         <v>46150</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="J13" s="21">
         <f t="shared" si="0"/>
@@ -2687,36 +2656,36 @@
         <v>7.5</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F14" s="3">
         <v>360</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H14" s="3">
         <v>10</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J14">
         <v>10</v>
@@ -2738,6 +2707,57 @@
         <v>10</v>
       </c>
       <c r="P14" s="23" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="3">
+        <v>80</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="4">
+        <v>46062</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="1">
+        <v>6</v>
+      </c>
+      <c r="K15" s="21">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="L15" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="M15" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="N15" s="2">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2">
+        <v>8</v>
+      </c>
+      <c r="P15" s="23" t="s">
         <v>214</v>
       </c>
     </row>
@@ -2756,6 +2776,7 @@
     <hyperlink ref="I12" r:id="rId11" location="reserva-roomions" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
     <hyperlink ref="I13" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
     <hyperlink ref="I14" r:id="rId13" xr:uid="{E4DAB110-E83E-4DEC-A2CC-8650550F459C}"/>
+    <hyperlink ref="I15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
